--- a/output/minervini_4h.xlsx
+++ b/output/minervini_4h.xlsx
@@ -8660,10 +8660,10 @@
         <v>1988.900024414062</v>
       </c>
       <c r="I107" t="n">
-        <v>1266.16157090969</v>
+        <v>1266.161452106784</v>
       </c>
       <c r="J107" t="n">
-        <v>52.51607851267466</v>
+        <v>52.51609282313503</v>
       </c>
       <c r="K107" t="n">
         <v>2.993115300029303</v>
@@ -10662,10 +10662,10 @@
         <v>443.3731066930094</v>
       </c>
       <c r="I133" t="n">
-        <v>175.4686165435595</v>
+        <v>175.4686316122085</v>
       </c>
       <c r="J133" t="n">
-        <v>125.0829920397681</v>
+        <v>125.0829727104066</v>
       </c>
       <c r="K133" t="n">
         <v>12.26056285335546</v>
@@ -11355,10 +11355,10 @@
         <v>12865.82946046676</v>
       </c>
       <c r="I142" t="n">
-        <v>6312.244104023675</v>
+        <v>6312.244579991518</v>
       </c>
       <c r="J142" t="n">
-        <v>81.1717007697823</v>
+        <v>81.17168710873</v>
       </c>
       <c r="K142" t="n">
         <v>12.50288090649489</v>
@@ -12048,10 +12048,10 @@
         <v>394.5</v>
       </c>
       <c r="I151" t="n">
-        <v>241.7427848010177</v>
+        <v>241.7427995975111</v>
       </c>
       <c r="J151" t="n">
-        <v>58.01919396040307</v>
+        <v>58.01918428842959</v>
       </c>
       <c r="K151" t="n">
         <v>3.27225130890052</v>
@@ -16049,7 +16049,7 @@
         <v>3.87589463306528</v>
       </c>
       <c r="H203" t="n">
-        <v>2269.472002658311</v>
+        <v>2269.472253037084</v>
       </c>
       <c r="I203" t="n">
         <v>1353.205955540699</v>
@@ -16058,7 +16058,7 @@
         <v>46.68129535544045</v>
       </c>
       <c r="K203" t="n">
-        <v>14.33684189349806</v>
+        <v>14.33685450767357</v>
       </c>
       <c r="L203" t="n">
         <v>60.91794158553546</v>
@@ -25061,10 +25061,10 @@
         <v>531</v>
       </c>
       <c r="I320" t="n">
-        <v>374.3676224032645</v>
+        <v>374.3675923313683</v>
       </c>
       <c r="J320" t="n">
-        <v>28.97750158089127</v>
+        <v>28.97751194129139</v>
       </c>
       <c r="K320" t="n">
         <v>9.972039616410754</v>
@@ -26213,7 +26213,7 @@
         <v>1.72549589427522</v>
       </c>
       <c r="H335" t="n">
-        <v>3039.742428602358</v>
+        <v>3039.742679715149</v>
       </c>
       <c r="I335" t="n">
         <v>2053.692522278021</v>
@@ -26222,7 +26222,7 @@
         <v>24.41005517057211</v>
       </c>
       <c r="K335" t="n">
-        <v>18.97230640322343</v>
+        <v>18.97231623151267</v>
       </c>
       <c r="L335" t="n">
         <v>47.8442280945758</v>
@@ -26444,7 +26444,7 @@
         <v>5.337363461032152</v>
       </c>
       <c r="H338" t="n">
-        <v>297.5473847088064</v>
+        <v>297.5474157032224</v>
       </c>
       <c r="I338" t="n">
         <v>165</v>
@@ -26453,7 +26453,7 @@
         <v>41.13333037405302</v>
       </c>
       <c r="K338" t="n">
-        <v>27.77403312911619</v>
+        <v>27.77404643886696</v>
       </c>
       <c r="L338" t="n">
         <v>46.87065368567455</v>
@@ -27137,7 +27137,7 @@
         <v>3.172218883389966</v>
       </c>
       <c r="H347" t="n">
-        <v>1304.859850069017</v>
+        <v>1304.859727076846</v>
       </c>
       <c r="I347" t="n">
         <v>734.1152411860135</v>
@@ -27146,7 +27146,7 @@
         <v>39.85541963591042</v>
       </c>
       <c r="K347" t="n">
-        <v>27.09261830388225</v>
+        <v>27.09260632451378</v>
       </c>
       <c r="L347" t="n">
         <v>41.1682892906815</v>
@@ -27214,7 +27214,7 @@
         <v>1.075268063604451</v>
       </c>
       <c r="H348" t="n">
-        <v>533.7088183031568</v>
+        <v>533.7087547028075</v>
       </c>
       <c r="I348" t="n">
         <v>363.2227809620478</v>
@@ -27223,7 +27223,7 @@
         <v>21.97747801486656</v>
       </c>
       <c r="K348" t="n">
-        <v>20.46243832706111</v>
+        <v>20.46242397194295</v>
       </c>
       <c r="L348" t="n">
         <v>40.89012517385257</v>
@@ -31837,10 +31837,10 @@
         <v>1093.53919041171</v>
       </c>
       <c r="I408" t="n">
-        <v>491.2850813456647</v>
+        <v>491.2850236715819</v>
       </c>
       <c r="J408" t="n">
-        <v>47.00222734809576</v>
+        <v>47.00224460532571</v>
       </c>
       <c r="K408" t="n">
         <v>51.41777512158614</v>
@@ -35376,7 +35376,7 @@
         <v>-1.290586178552477</v>
       </c>
       <c r="H454" t="n">
-        <v>1766.733188761222</v>
+        <v>1766.733060850261</v>
       </c>
       <c r="I454" t="n">
         <v>894.2209017899434</v>
@@ -35385,7 +35385,7 @@
         <v>49.80638149974889</v>
       </c>
       <c r="K454" t="n">
-        <v>31.88513145414607</v>
+        <v>31.88512190570145</v>
       </c>
       <c r="L454" t="n">
         <v>73.57440890125174</v>
@@ -38995,7 +38995,7 @@
         <v>-0.5888225702531225</v>
       </c>
       <c r="H501" t="n">
-        <v>3287.161645949698</v>
+        <v>3287.161392369851</v>
       </c>
       <c r="I501" t="n">
         <v>1966.020518717901</v>
@@ -39004,7 +39004,7 @@
         <v>19.12388389147057</v>
       </c>
       <c r="K501" t="n">
-        <v>40.35703014302723</v>
+        <v>40.35701931553588</v>
       </c>
       <c r="L501" t="n">
         <v>19.05424200278164</v>
@@ -39383,10 +39383,10 @@
         <v>872.0425606177564</v>
       </c>
       <c r="I506" t="n">
-        <v>406.1171468902937</v>
+        <v>406.117116732523</v>
       </c>
       <c r="J506" t="n">
-        <v>25.44410303972004</v>
+        <v>25.44411235504889</v>
       </c>
       <c r="K506" t="n">
         <v>71.17333197027662</v>
@@ -39691,10 +39691,10 @@
         <v>387.7999877929688</v>
       </c>
       <c r="I510" t="n">
-        <v>217.6006723249054</v>
+        <v>217.6006872017223</v>
       </c>
       <c r="J510" t="n">
-        <v>24.08049897789644</v>
+        <v>24.08049049482182</v>
       </c>
       <c r="K510" t="n">
         <v>43.62962510850694</v>
@@ -40535,7 +40535,7 @@
         <v>0.1647393729975022</v>
       </c>
       <c r="H521" t="n">
-        <v>87.39771312453149</v>
+        <v>87.39772087555167</v>
       </c>
       <c r="I521" t="n">
         <v>71.42454681386315</v>
@@ -40544,7 +40544,7 @@
         <v>4.753901890074053</v>
       </c>
       <c r="K521" t="n">
-        <v>16.81063015371458</v>
+        <v>16.81064051327112</v>
       </c>
       <c r="L521" t="n">
         <v>39.91655076495132</v>
@@ -41305,7 +41305,7 @@
         <v>0.5286217519214098</v>
       </c>
       <c r="H531" t="n">
-        <v>155.8999606999571</v>
+        <v>155.8999783750524</v>
       </c>
       <c r="I531" t="n">
         <v>112.8155071321618</v>
@@ -41314,7 +41314,7 @@
         <v>7.963883820573336</v>
       </c>
       <c r="K531" t="n">
-        <v>27.99668045468675</v>
+        <v>27.99669496625883</v>
       </c>
       <c r="L531" t="n">
         <v>31.43254520166898</v>
@@ -41613,7 +41613,7 @@
         <v>2.185911334104285</v>
       </c>
       <c r="H535" t="n">
-        <v>46547.9774954976</v>
+        <v>46547.97355089381</v>
       </c>
       <c r="I535" t="n">
         <v>29525.27549507192</v>
@@ -41622,7 +41622,7 @@
         <v>21.87862567448789</v>
       </c>
       <c r="K535" t="n">
-        <v>29.35383491870947</v>
+        <v>29.35382395690929</v>
       </c>
       <c r="L535" t="n">
         <v>28.37273991655077</v>
@@ -42460,7 +42460,7 @@
         <v>1.213630845153424</v>
       </c>
       <c r="H546" t="n">
-        <v>124.8273017901132</v>
+        <v>124.8273096544699</v>
       </c>
       <c r="I546" t="n">
         <v>76.65010804466255</v>
@@ -42469,7 +42469,7 @@
         <v>14.15509023029091</v>
       </c>
       <c r="K546" t="n">
-        <v>42.65977347441505</v>
+        <v>42.65978246225137</v>
       </c>
       <c r="L546" t="n">
         <v>20.86230876216968</v>
@@ -44773,10 +44773,10 @@
         <v>484.7737901614043</v>
       </c>
       <c r="I576" t="n">
-        <v>349.5720248388532</v>
+        <v>349.5720548957738</v>
       </c>
       <c r="J576" t="n">
-        <v>14.71169644792205</v>
+        <v>14.71168658477568</v>
       </c>
       <c r="K576" t="n">
         <v>20.89121949162202</v>
@@ -45925,7 +45925,7 @@
         <v>1.553058150552844</v>
       </c>
       <c r="H591" t="n">
-        <v>239.2186728978909</v>
+        <v>239.2186883393384</v>
       </c>
       <c r="I591" t="n">
         <v>156.7443123050878</v>
@@ -45934,7 +45934,7 @@
         <v>16.68684573414505</v>
       </c>
       <c r="K591" t="n">
-        <v>30.7920617172252</v>
+        <v>30.79207015978833</v>
       </c>
       <c r="L591" t="n">
         <v>26.56467315716273</v>
@@ -46926,7 +46926,7 @@
         <v>-0.446131700275032</v>
       </c>
       <c r="H604" t="n">
-        <v>294.6532203195111</v>
+        <v>294.6532543042141</v>
       </c>
       <c r="I604" t="n">
         <v>213.7350670269712</v>
@@ -46935,7 +46935,7 @@
         <v>5.803882598783772</v>
       </c>
       <c r="K604" t="n">
-        <v>30.29681662455992</v>
+        <v>30.29683165272965</v>
       </c>
       <c r="L604" t="n">
         <v>20.72322670375522</v>
@@ -47234,7 +47234,7 @@
         <v>0.7510223845656139</v>
       </c>
       <c r="H608" t="n">
-        <v>408.554305468849</v>
+        <v>408.5542740377988</v>
       </c>
       <c r="I608" t="n">
         <v>243.9284560598348</v>
@@ -47243,7 +47243,7 @@
         <v>14.33680120865899</v>
       </c>
       <c r="K608" t="n">
-        <v>46.48774270697429</v>
+        <v>46.48773143732537</v>
       </c>
       <c r="L608" t="n">
         <v>17.94158553546593</v>
@@ -47388,7 +47388,7 @@
         <v>0.1706315473898767</v>
       </c>
       <c r="H610" t="n">
-        <v>2448.345231432346</v>
+        <v>2448.345479475883</v>
       </c>
       <c r="I610" t="n">
         <v>1761.237851420491</v>
@@ -47397,7 +47397,7 @@
         <v>3.728183160531828</v>
       </c>
       <c r="K610" t="n">
-        <v>34.01637739961159</v>
+        <v>34.01639097690283</v>
       </c>
       <c r="L610" t="n">
         <v>16.82892906815021</v>
@@ -48774,7 +48774,7 @@
         <v>0.6477673935719519</v>
       </c>
       <c r="H628" t="n">
-        <v>372.3009385265751</v>
+        <v>372.3009694554414</v>
       </c>
       <c r="I628" t="n">
         <v>218.8999938964844</v>
@@ -48783,7 +48783,7 @@
         <v>9.365007113565404</v>
       </c>
       <c r="K628" t="n">
-        <v>55.5141804588168</v>
+        <v>55.51419337814305</v>
       </c>
       <c r="L628" t="n">
         <v>5.285118219749652</v>
@@ -52624,7 +52624,7 @@
         <v>-1.006731507353509</v>
       </c>
       <c r="H678" t="n">
-        <v>263.220498300555</v>
+        <v>263.2205288662585</v>
       </c>
       <c r="I678" t="n">
         <v>167.0916913788894</v>
@@ -52633,7 +52633,7 @@
         <v>8.293832838120196</v>
       </c>
       <c r="K678" t="n">
-        <v>45.46587606511259</v>
+        <v>45.46589295690811</v>
       </c>
       <c r="L678" t="n">
         <v>11.82197496522948</v>
@@ -52932,7 +52932,7 @@
         <v>-0.4425166749201459</v>
       </c>
       <c r="H682" t="n">
-        <v>97.9287679734358</v>
+        <v>97.92876001560526</v>
       </c>
       <c r="I682" t="n">
         <v>62.68610889438828</v>
@@ -52941,7 +52941,7 @@
         <v>3.627422773864231</v>
       </c>
       <c r="K682" t="n">
-        <v>50.75241587687098</v>
+        <v>50.75240362651592</v>
       </c>
       <c r="L682" t="n">
         <v>10.84840055632823</v>
@@ -53086,7 +53086,7 @@
         <v>-1.193779559056574</v>
       </c>
       <c r="H684" t="n">
-        <v>1284.135475005729</v>
+        <v>1284.135346691241</v>
       </c>
       <c r="I684" t="n">
         <v>902.8120757721283</v>
@@ -53095,7 +53095,7 @@
         <v>1.349995702865181</v>
       </c>
       <c r="K684" t="n">
-        <v>40.34267486401415</v>
+        <v>40.34266084057276</v>
       </c>
       <c r="L684" t="n">
         <v>10.43115438108484</v>
@@ -55396,7 +55396,7 @@
         <v>-1.971118231218572</v>
       </c>
       <c r="H714" t="n">
-        <v>1343.927192495164</v>
+        <v>1343.927068287785</v>
       </c>
       <c r="I714" t="n">
         <v>680.1500244140625</v>
@@ -55405,7 +55405,7 @@
         <v>4.035867115570957</v>
       </c>
       <c r="K714" t="n">
-        <v>89.92753517017964</v>
+        <v>89.92751761684681</v>
       </c>
       <c r="L714" t="n">
         <v>1.390820584144645</v>

--- a/output/minervini_4h.xlsx
+++ b/output/minervini_4h.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W720"/>
+  <dimension ref="A1:W719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
         <v>5.411601069562333</v>
       </c>
       <c r="L3" t="n">
-        <v>99.86091794158554</v>
+        <v>99.86072423398329</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -738,7 +738,7 @@
         <v>10.91427994260417</v>
       </c>
       <c r="L4" t="n">
-        <v>99.58275382475661</v>
+        <v>99.58217270194986</v>
       </c>
       <c r="M4" t="n">
         <v>9</v>
@@ -815,7 +815,7 @@
         <v>3.954628651973269</v>
       </c>
       <c r="L5" t="n">
-        <v>99.44367176634215</v>
+        <v>99.44289693593315</v>
       </c>
       <c r="M5" t="n">
         <v>9</v>
@@ -892,7 +892,7 @@
         <v>10.1010101010101</v>
       </c>
       <c r="L6" t="n">
-        <v>99.30458970792768</v>
+        <v>99.30362116991644</v>
       </c>
       <c r="M6" t="n">
         <v>9</v>
@@ -969,7 +969,7 @@
         <v>1.659710272866644</v>
       </c>
       <c r="L7" t="n">
-        <v>99.16550764951322</v>
+        <v>99.16434540389972</v>
       </c>
       <c r="M7" t="n">
         <v>9</v>
@@ -1046,7 +1046,7 @@
         <v>10.67515768063296</v>
       </c>
       <c r="L8" t="n">
-        <v>99.02642559109874</v>
+        <v>99.02506963788301</v>
       </c>
       <c r="M8" t="n">
         <v>9</v>
@@ -1123,7 +1123,7 @@
         <v>9.829766320145318</v>
       </c>
       <c r="L9" t="n">
-        <v>98.88734353268428</v>
+        <v>98.88579387186628</v>
       </c>
       <c r="M9" t="n">
         <v>9</v>
@@ -1200,7 +1200,7 @@
         <v>10.51125336281526</v>
       </c>
       <c r="L10" t="n">
-        <v>98.47009735744089</v>
+        <v>98.46796657381616</v>
       </c>
       <c r="M10" t="n">
         <v>9</v>
@@ -1277,7 +1277,7 @@
         <v>8.054915295040544</v>
       </c>
       <c r="L11" t="n">
-        <v>98.33101529902642</v>
+        <v>98.32869080779945</v>
       </c>
       <c r="M11" t="n">
         <v>9</v>
@@ -1354,7 +1354,7 @@
         <v>11.94504986778075</v>
       </c>
       <c r="L12" t="n">
-        <v>98.0528511821975</v>
+        <v>98.05013927576601</v>
       </c>
       <c r="M12" t="n">
         <v>9</v>
@@ -1431,7 +1431,7 @@
         <v>23.82578367824577</v>
       </c>
       <c r="L13" t="n">
-        <v>97.91376912378304</v>
+        <v>97.9108635097493</v>
       </c>
       <c r="M13" t="n">
         <v>9</v>
@@ -1508,7 +1508,7 @@
         <v>1.593625498007967</v>
       </c>
       <c r="L14" t="n">
-        <v>97.63560500695411</v>
+        <v>97.63231197771589</v>
       </c>
       <c r="M14" t="n">
         <v>9</v>
@@ -1585,7 +1585,7 @@
         <v>5.992767349750294</v>
       </c>
       <c r="L15" t="n">
-        <v>97.49652294853965</v>
+        <v>97.49303621169916</v>
       </c>
       <c r="M15" t="n">
         <v>9</v>
@@ -1662,7 +1662,7 @@
         <v>5.031755351888023</v>
       </c>
       <c r="L16" t="n">
-        <v>97.35744089012516</v>
+        <v>97.35376044568244</v>
       </c>
       <c r="M16" t="n">
         <v>9</v>
@@ -1739,7 +1739,7 @@
         <v>1.87677621008111</v>
       </c>
       <c r="L17" t="n">
-        <v>97.07927677329624</v>
+        <v>97.07520891364902</v>
       </c>
       <c r="M17" t="n">
         <v>9</v>
@@ -1807,16 +1807,16 @@
         <v>1489.699951171875</v>
       </c>
       <c r="I18" t="n">
-        <v>651.3127841620155</v>
+        <v>651.3127246301497</v>
       </c>
       <c r="J18" t="n">
-        <v>122.9650617161289</v>
+        <v>122.96508209578</v>
       </c>
       <c r="K18" t="n">
         <v>2.582289027742957</v>
       </c>
       <c r="L18" t="n">
-        <v>96.80111265646731</v>
+        <v>96.7966573816156</v>
       </c>
       <c r="M18" t="n">
         <v>9</v>
@@ -1893,7 +1893,7 @@
         <v>3.212027297958109</v>
       </c>
       <c r="L19" t="n">
-        <v>96.66203059805285</v>
+        <v>96.65738161559888</v>
       </c>
       <c r="M19" t="n">
         <v>9</v>
@@ -1970,7 +1970,7 @@
         <v>5.109542578947801</v>
       </c>
       <c r="L20" t="n">
-        <v>96.38386648122392</v>
+        <v>96.37883008356546</v>
       </c>
       <c r="M20" t="n">
         <v>9</v>
@@ -2047,7 +2047,7 @@
         <v>5.772540264273984</v>
       </c>
       <c r="L21" t="n">
-        <v>95.82753824756607</v>
+        <v>95.82172701949861</v>
       </c>
       <c r="M21" t="n">
         <v>9</v>
@@ -2124,7 +2124,7 @@
         <v>5.656556127834</v>
       </c>
       <c r="L22" t="n">
-        <v>95.68845618915159</v>
+        <v>95.68245125348189</v>
       </c>
       <c r="M22" t="n">
         <v>9</v>
@@ -2201,7 +2201,7 @@
         <v>0.205247100611583</v>
       </c>
       <c r="L23" t="n">
-        <v>95.41029207232266</v>
+        <v>95.40389972144847</v>
       </c>
       <c r="M23" t="n">
         <v>9</v>
@@ -2278,7 +2278,7 @@
         <v>1.705377150508913</v>
       </c>
       <c r="L24" t="n">
-        <v>95.13212795549374</v>
+        <v>95.12534818941504</v>
       </c>
       <c r="M24" t="n">
         <v>9</v>
@@ -2355,7 +2355,7 @@
         <v>3.572255550557002</v>
       </c>
       <c r="L25" t="n">
-        <v>94.85396383866481</v>
+        <v>94.84679665738162</v>
       </c>
       <c r="M25" t="n">
         <v>9</v>
@@ -2432,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>94.71488178025035</v>
+        <v>94.70752089136491</v>
       </c>
       <c r="M26" t="n">
         <v>9</v>
@@ -2509,7 +2509,7 @@
         <v>5.524679141377264</v>
       </c>
       <c r="L27" t="n">
-        <v>94.57579972183588</v>
+        <v>94.5682451253482</v>
       </c>
       <c r="M27" t="n">
         <v>9</v>
@@ -2586,7 +2586,7 @@
         <v>12.00385356454721</v>
       </c>
       <c r="L28" t="n">
-        <v>94.43671766342142</v>
+        <v>94.42896935933148</v>
       </c>
       <c r="M28" t="n">
         <v>9</v>
@@ -2663,7 +2663,7 @@
         <v>2.839116719242907</v>
       </c>
       <c r="L29" t="n">
-        <v>94.29763560500696</v>
+        <v>94.28969359331477</v>
       </c>
       <c r="M29" t="n">
         <v>9</v>
@@ -2740,7 +2740,7 @@
         <v>0.8557457212713837</v>
       </c>
       <c r="L30" t="n">
-        <v>94.01947148817803</v>
+        <v>94.01114206128133</v>
       </c>
       <c r="M30" t="n">
         <v>9</v>
@@ -2817,7 +2817,7 @@
         <v>7.637987787669842</v>
       </c>
       <c r="L31" t="n">
-        <v>93.88038942976355</v>
+        <v>93.87186629526462</v>
       </c>
       <c r="M31" t="n">
         <v>9</v>
@@ -2894,7 +2894,7 @@
         <v>7.536097834169508</v>
       </c>
       <c r="L32" t="n">
-        <v>93.74130737134909</v>
+        <v>93.7325905292479</v>
       </c>
       <c r="M32" t="n">
         <v>9</v>
@@ -2971,7 +2971,7 @@
         <v>13.09867282169648</v>
       </c>
       <c r="L33" t="n">
-        <v>93.60222531293462</v>
+        <v>93.59331476323119</v>
       </c>
       <c r="M33" t="n">
         <v>9</v>
@@ -3048,7 +3048,7 @@
         <v>16.67242229969539</v>
       </c>
       <c r="L34" t="n">
-        <v>93.46314325452016</v>
+        <v>93.45403899721448</v>
       </c>
       <c r="M34" t="n">
         <v>9</v>
@@ -3125,7 +3125,7 @@
         <v>2.25979696759866</v>
       </c>
       <c r="L35" t="n">
-        <v>93.3240611961057</v>
+        <v>93.31476323119777</v>
       </c>
       <c r="M35" t="n">
         <v>9</v>
@@ -3202,7 +3202,7 @@
         <v>4.651166975041154</v>
       </c>
       <c r="L36" t="n">
-        <v>93.04589707927677</v>
+        <v>93.03621169916435</v>
       </c>
       <c r="M36" t="n">
         <v>9</v>
@@ -3279,7 +3279,7 @@
         <v>4.747311321757897</v>
       </c>
       <c r="L37" t="n">
-        <v>92.90681502086231</v>
+        <v>92.89693593314763</v>
       </c>
       <c r="M37" t="n">
         <v>9</v>
@@ -3356,7 +3356,7 @@
         <v>9.584214235377031</v>
       </c>
       <c r="L38" t="n">
-        <v>92.76773296244785</v>
+        <v>92.75766016713092</v>
       </c>
       <c r="M38" t="n">
         <v>9</v>
@@ -3433,7 +3433,7 @@
         <v>9.585798816568047</v>
       </c>
       <c r="L39" t="n">
-        <v>92.62865090403338</v>
+        <v>92.61838440111421</v>
       </c>
       <c r="M39" t="n">
         <v>9</v>
@@ -3510,7 +3510,7 @@
         <v>4.280946946675956</v>
       </c>
       <c r="L40" t="n">
-        <v>92.35048678720446</v>
+        <v>92.33983286908078</v>
       </c>
       <c r="M40" t="n">
         <v>9</v>
@@ -3587,7 +3587,7 @@
         <v>2.499999999999991</v>
       </c>
       <c r="L41" t="n">
-        <v>92.21140472878999</v>
+        <v>92.20055710306406</v>
       </c>
       <c r="M41" t="n">
         <v>9</v>
@@ -3664,7 +3664,7 @@
         <v>3.662534103842185</v>
       </c>
       <c r="L42" t="n">
-        <v>92.07232267037551</v>
+        <v>92.06128133704735</v>
       </c>
       <c r="M42" t="n">
         <v>9</v>
@@ -3741,7 +3741,7 @@
         <v>2.102422585705854</v>
       </c>
       <c r="L43" t="n">
-        <v>91.93324061196105</v>
+        <v>91.92200557103064</v>
       </c>
       <c r="M43" t="n">
         <v>9</v>
@@ -3818,7 +3818,7 @@
         <v>9.051254089422024</v>
       </c>
       <c r="L44" t="n">
-        <v>91.79415855354659</v>
+        <v>91.78272980501393</v>
       </c>
       <c r="M44" t="n">
         <v>9</v>
@@ -3895,7 +3895,7 @@
         <v>1.280218858343085</v>
       </c>
       <c r="L45" t="n">
-        <v>91.51599443671766</v>
+        <v>91.5041782729805</v>
       </c>
       <c r="M45" t="n">
         <v>9</v>
@@ -3972,7 +3972,7 @@
         <v>1.237059133181262</v>
       </c>
       <c r="L46" t="n">
-        <v>91.3769123783032</v>
+        <v>91.36490250696379</v>
       </c>
       <c r="M46" t="n">
         <v>9</v>
@@ -4049,7 +4049,7 @@
         <v>3.577000571865385</v>
       </c>
       <c r="L47" t="n">
-        <v>91.23783031988873</v>
+        <v>91.22562674094708</v>
       </c>
       <c r="M47" t="n">
         <v>9</v>
@@ -4126,7 +4126,7 @@
         <v>3.997346160225579</v>
       </c>
       <c r="L48" t="n">
-        <v>91.09874826147427</v>
+        <v>91.08635097493037</v>
       </c>
       <c r="M48" t="n">
         <v>9</v>
@@ -4203,7 +4203,7 @@
         <v>5.621406457319766</v>
       </c>
       <c r="L49" t="n">
-        <v>90.82058414464534</v>
+        <v>90.80779944289694</v>
       </c>
       <c r="M49" t="n">
         <v>9</v>
@@ -4280,7 +4280,7 @@
         <v>2.547472976920839</v>
       </c>
       <c r="L50" t="n">
-        <v>90.68150208623088</v>
+        <v>90.66852367688021</v>
       </c>
       <c r="M50" t="n">
         <v>9</v>
@@ -4357,7 +4357,7 @@
         <v>1.237935375576993</v>
       </c>
       <c r="L51" t="n">
-        <v>89.98609179415855</v>
+        <v>89.97214484679665</v>
       </c>
       <c r="M51" t="n">
         <v>9</v>
@@ -4434,7 +4434,7 @@
         <v>7.050378055107198</v>
       </c>
       <c r="L52" t="n">
-        <v>89.70792767732962</v>
+        <v>89.69359331476323</v>
       </c>
       <c r="M52" t="n">
         <v>9</v>
@@ -4511,7 +4511,7 @@
         <v>3.737428556082678</v>
       </c>
       <c r="L53" t="n">
-        <v>89.4297635605007</v>
+        <v>89.41504178272982</v>
       </c>
       <c r="M53" t="n">
         <v>9</v>
@@ -4588,7 +4588,7 @@
         <v>2.735602299054962</v>
       </c>
       <c r="L54" t="n">
-        <v>89.29068150208623</v>
+        <v>89.27576601671309</v>
       </c>
       <c r="M54" t="n">
         <v>9</v>
@@ -4665,7 +4665,7 @@
         <v>8.942884305741927</v>
       </c>
       <c r="L55" t="n">
-        <v>89.15159944367177</v>
+        <v>89.13649025069638</v>
       </c>
       <c r="M55" t="n">
         <v>9</v>
@@ -4742,7 +4742,7 @@
         <v>1.165772907437623</v>
       </c>
       <c r="L56" t="n">
-        <v>88.73435326842836</v>
+        <v>88.71866295264624</v>
       </c>
       <c r="M56" t="n">
         <v>9</v>
@@ -4819,7 +4819,7 @@
         <v>3.025718608169448</v>
       </c>
       <c r="L57" t="n">
-        <v>88.45618915159945</v>
+        <v>88.44011142061281</v>
       </c>
       <c r="M57" t="n">
         <v>9</v>
@@ -4896,7 +4896,7 @@
         <v>8.271405137662292</v>
       </c>
       <c r="L58" t="n">
-        <v>88.17802503477051</v>
+        <v>88.16155988857939</v>
       </c>
       <c r="M58" t="n">
         <v>9</v>
@@ -4973,7 +4973,7 @@
         <v>1.310438319023954</v>
       </c>
       <c r="L59" t="n">
-        <v>88.03894297635605</v>
+        <v>88.02228412256268</v>
       </c>
       <c r="M59" t="n">
         <v>9</v>
@@ -5050,7 +5050,7 @@
         <v>4.032967032967028</v>
       </c>
       <c r="L60" t="n">
-        <v>87.76077885952712</v>
+        <v>87.74373259052925</v>
       </c>
       <c r="M60" t="n">
         <v>9</v>
@@ -5127,7 +5127,7 @@
         <v>12.12047389838768</v>
       </c>
       <c r="L61" t="n">
-        <v>86.92628650904032</v>
+        <v>86.90807799442896</v>
       </c>
       <c r="M61" t="n">
         <v>9</v>
@@ -5204,7 +5204,7 @@
         <v>15.56775042118916</v>
       </c>
       <c r="L62" t="n">
-        <v>86.78720445062586</v>
+        <v>86.76880222841226</v>
       </c>
       <c r="M62" t="n">
         <v>9</v>
@@ -5281,7 +5281,7 @@
         <v>11.37930988118569</v>
       </c>
       <c r="L63" t="n">
-        <v>86.50904033379693</v>
+        <v>86.49025069637884</v>
       </c>
       <c r="M63" t="n">
         <v>9</v>
@@ -5358,7 +5358,7 @@
         <v>3.902229845626071</v>
       </c>
       <c r="L64" t="n">
-        <v>86.36995827538247</v>
+        <v>86.35097493036211</v>
       </c>
       <c r="M64" t="n">
         <v>9</v>
@@ -5435,7 +5435,7 @@
         <v>4.386866455445926</v>
       </c>
       <c r="L65" t="n">
-        <v>86.23087621696801</v>
+        <v>86.2116991643454</v>
       </c>
       <c r="M65" t="n">
         <v>9</v>
@@ -5512,7 +5512,7 @@
         <v>0.6516185953135079</v>
       </c>
       <c r="L66" t="n">
-        <v>86.09179415855354</v>
+        <v>86.0724233983287</v>
       </c>
       <c r="M66" t="n">
         <v>9</v>
@@ -5589,7 +5589,7 @@
         <v>3.097824428392504</v>
       </c>
       <c r="L67" t="n">
-        <v>85.81363004172462</v>
+        <v>85.79387186629526</v>
       </c>
       <c r="M67" t="n">
         <v>9</v>
@@ -5648,10 +5648,10 @@
         <v>176.1901991780599</v>
       </c>
       <c r="F68" t="n">
-        <v>173.1223991394043</v>
+        <v>173.1184991455078</v>
       </c>
       <c r="G68" t="n">
-        <v>5.939946866685109</v>
+        <v>5.940088629830664</v>
       </c>
       <c r="H68" t="n">
         <v>234.3899993896484</v>
@@ -5666,7 +5666,7 @@
         <v>1.248379865938842</v>
       </c>
       <c r="L68" t="n">
-        <v>85.53546592489569</v>
+        <v>85.51532033426183</v>
       </c>
       <c r="M68" t="n">
         <v>9</v>
@@ -5743,7 +5743,7 @@
         <v>3.865466418110208</v>
       </c>
       <c r="L69" t="n">
-        <v>85.25730180806676</v>
+        <v>85.23676880222841</v>
       </c>
       <c r="M69" t="n">
         <v>9</v>
@@ -5820,7 +5820,7 @@
         <v>3.005169301992683</v>
       </c>
       <c r="L70" t="n">
-        <v>84.97913769123782</v>
+        <v>84.95821727019499</v>
       </c>
       <c r="M70" t="n">
         <v>9</v>
@@ -5897,7 +5897,7 @@
         <v>2.981390437656595</v>
       </c>
       <c r="L71" t="n">
-        <v>84.56189151599443</v>
+        <v>84.54038997214485</v>
       </c>
       <c r="M71" t="n">
         <v>9</v>
@@ -5974,7 +5974,7 @@
         <v>5.344230607930123</v>
       </c>
       <c r="L72" t="n">
-        <v>84.42280945757997</v>
+        <v>84.40111420612814</v>
       </c>
       <c r="M72" t="n">
         <v>9</v>
@@ -6051,7 +6051,7 @@
         <v>8.369842937320815</v>
       </c>
       <c r="L73" t="n">
-        <v>83.72739916550765</v>
+        <v>83.70473537604457</v>
       </c>
       <c r="M73" t="n">
         <v>9</v>
@@ -6128,7 +6128,7 @@
         <v>4.35939317364531</v>
       </c>
       <c r="L74" t="n">
-        <v>83.03198887343532</v>
+        <v>83.00835654596101</v>
       </c>
       <c r="M74" t="n">
         <v>9</v>
@@ -6205,7 +6205,7 @@
         <v>1.841955440517107</v>
       </c>
       <c r="L75" t="n">
-        <v>82.75382475660639</v>
+        <v>82.72980501392759</v>
       </c>
       <c r="M75" t="n">
         <v>9</v>
@@ -6282,7 +6282,7 @@
         <v>11.81988742964353</v>
       </c>
       <c r="L76" t="n">
-        <v>82.61474269819193</v>
+        <v>82.59052924791087</v>
       </c>
       <c r="M76" t="n">
         <v>9</v>
@@ -6359,7 +6359,7 @@
         <v>12.92748550244012</v>
       </c>
       <c r="L77" t="n">
-        <v>82.05841446453408</v>
+        <v>82.03342618384401</v>
       </c>
       <c r="M77" t="n">
         <v>9</v>
@@ -6436,7 +6436,7 @@
         <v>3.405307318269979</v>
       </c>
       <c r="L78" t="n">
-        <v>81.64116828929068</v>
+        <v>81.61559888579387</v>
       </c>
       <c r="M78" t="n">
         <v>9</v>
@@ -6513,7 +6513,7 @@
         <v>4.829132299629046</v>
       </c>
       <c r="L79" t="n">
-        <v>81.36300417246176</v>
+        <v>81.33704735376045</v>
       </c>
       <c r="M79" t="n">
         <v>9</v>
@@ -6590,7 +6590,7 @@
         <v>6.133486089322826</v>
       </c>
       <c r="L80" t="n">
-        <v>80.52851182197497</v>
+        <v>80.50139275766016</v>
       </c>
       <c r="M80" t="n">
         <v>9</v>
@@ -6667,7 +6667,7 @@
         <v>6.610923753064379</v>
       </c>
       <c r="L81" t="n">
-        <v>80.25034770514604</v>
+        <v>80.22284122562674</v>
       </c>
       <c r="M81" t="n">
         <v>9</v>
@@ -6744,7 +6744,7 @@
         <v>2.453360763677015</v>
       </c>
       <c r="L82" t="n">
-        <v>79.55493741307372</v>
+        <v>79.52646239554318</v>
       </c>
       <c r="M82" t="n">
         <v>9</v>
@@ -6821,7 +6821,7 @@
         <v>4.622871046228716</v>
       </c>
       <c r="L83" t="n">
-        <v>79.13769123783032</v>
+        <v>79.10863509749304</v>
       </c>
       <c r="M83" t="n">
         <v>9</v>
@@ -6898,7 +6898,7 @@
         <v>22.40608228980323</v>
       </c>
       <c r="L84" t="n">
-        <v>78.99860917941585</v>
+        <v>78.96935933147631</v>
       </c>
       <c r="M84" t="n">
         <v>9</v>
@@ -6975,7 +6975,7 @@
         <v>7.030487040851097</v>
       </c>
       <c r="L85" t="n">
-        <v>78.44228094575799</v>
+        <v>78.41225626740948</v>
       </c>
       <c r="M85" t="n">
         <v>9</v>
@@ -7052,7 +7052,7 @@
         <v>9.679574026188376</v>
       </c>
       <c r="L86" t="n">
-        <v>77.88595271210013</v>
+        <v>77.85515320334262</v>
       </c>
       <c r="M86" t="n">
         <v>9</v>
@@ -7129,7 +7129,7 @@
         <v>4.948468774807058</v>
       </c>
       <c r="L87" t="n">
-        <v>77.46870653685674</v>
+        <v>77.43732590529248</v>
       </c>
       <c r="M87" t="n">
         <v>9</v>
@@ -7206,7 +7206,7 @@
         <v>1.587304257087707</v>
       </c>
       <c r="L88" t="n">
-        <v>77.05146036161335</v>
+        <v>77.01949860724234</v>
       </c>
       <c r="M88" t="n">
         <v>9</v>
@@ -7283,7 +7283,7 @@
         <v>0.334243981976301</v>
       </c>
       <c r="L89" t="n">
-        <v>76.91237830319889</v>
+        <v>76.88022284122563</v>
       </c>
       <c r="M89" t="n">
         <v>9</v>
@@ -7360,7 +7360,7 @@
         <v>4.123213785726154</v>
       </c>
       <c r="L90" t="n">
-        <v>76.77329624478443</v>
+        <v>76.74094707520891</v>
       </c>
       <c r="M90" t="n">
         <v>9</v>
@@ -7437,7 +7437,7 @@
         <v>3.045685279187826</v>
       </c>
       <c r="L91" t="n">
-        <v>76.63421418636996</v>
+        <v>76.6016713091922</v>
       </c>
       <c r="M91" t="n">
         <v>9</v>
@@ -7514,7 +7514,7 @@
         <v>9.610259826782141</v>
       </c>
       <c r="L92" t="n">
-        <v>76.49513212795549</v>
+        <v>76.46239554317549</v>
       </c>
       <c r="M92" t="n">
         <v>9</v>
@@ -7591,7 +7591,7 @@
         <v>3.378903865814209</v>
       </c>
       <c r="L93" t="n">
-        <v>76.21696801112657</v>
+        <v>76.18384401114207</v>
       </c>
       <c r="M93" t="n">
         <v>9</v>
@@ -7668,7 +7668,7 @@
         <v>6.791969243912854</v>
       </c>
       <c r="L94" t="n">
-        <v>75.6606397774687</v>
+        <v>75.62674094707521</v>
       </c>
       <c r="M94" t="n">
         <v>9</v>
@@ -7745,7 +7745,7 @@
         <v>15.31853430375929</v>
       </c>
       <c r="L95" t="n">
-        <v>75.52155771905424</v>
+        <v>75.4874651810585</v>
       </c>
       <c r="M95" t="n">
         <v>9</v>
@@ -7822,7 +7822,7 @@
         <v>5.32668572708852</v>
       </c>
       <c r="L96" t="n">
-        <v>74.82614742698192</v>
+        <v>74.79108635097494</v>
       </c>
       <c r="M96" t="n">
         <v>9</v>
@@ -7899,7 +7899,7 @@
         <v>12.20394122936377</v>
       </c>
       <c r="L97" t="n">
-        <v>74.54798331015299</v>
+        <v>74.5125348189415</v>
       </c>
       <c r="M97" t="n">
         <v>9</v>
@@ -7976,7 +7976,7 @@
         <v>3.737219262068914</v>
       </c>
       <c r="L98" t="n">
-        <v>74.40890125173853</v>
+        <v>74.37325905292479</v>
       </c>
       <c r="M98" t="n">
         <v>9</v>
@@ -8053,7 +8053,7 @@
         <v>4.289866617592564</v>
       </c>
       <c r="L99" t="n">
-        <v>74.13073713490959</v>
+        <v>74.09470752089136</v>
       </c>
       <c r="M99" t="n">
         <v>9</v>
@@ -8130,7 +8130,7 @@
         <v>18.70334607493467</v>
       </c>
       <c r="L100" t="n">
-        <v>73.01808066759388</v>
+        <v>72.98050139275766</v>
       </c>
       <c r="M100" t="n">
         <v>9</v>
@@ -8207,7 +8207,7 @@
         <v>2.866212003856083</v>
       </c>
       <c r="L101" t="n">
-        <v>72.87899860917942</v>
+        <v>72.84122562674095</v>
       </c>
       <c r="M101" t="n">
         <v>9</v>
@@ -8284,7 +8284,7 @@
         <v>4.494050761849855</v>
       </c>
       <c r="L102" t="n">
-        <v>72.73991655076495</v>
+        <v>72.70194986072424</v>
       </c>
       <c r="M102" t="n">
         <v>9</v>
@@ -8361,7 +8361,7 @@
         <v>7.596805663034667</v>
       </c>
       <c r="L103" t="n">
-        <v>72.60083449235049</v>
+        <v>72.56267409470752</v>
       </c>
       <c r="M103" t="n">
         <v>9</v>
@@ -8438,7 +8438,7 @@
         <v>2.06437458454658</v>
       </c>
       <c r="L104" t="n">
-        <v>70.79276773296245</v>
+        <v>70.75208913649024</v>
       </c>
       <c r="M104" t="n">
         <v>9</v>
@@ -8515,7 +8515,7 @@
         <v>21.68691523530233</v>
       </c>
       <c r="L105" t="n">
-        <v>99.72183588317107</v>
+        <v>99.72144846796658</v>
       </c>
       <c r="M105" t="n">
         <v>8</v>
@@ -8592,7 +8592,7 @@
         <v>7.991852082772621</v>
       </c>
       <c r="L106" t="n">
-        <v>98.74826147426981</v>
+        <v>98.74651810584957</v>
       </c>
       <c r="M106" t="n">
         <v>8</v>
@@ -8669,7 +8669,7 @@
         <v>14.22544121263874</v>
       </c>
       <c r="L107" t="n">
-        <v>98.60917941585535</v>
+        <v>98.60724233983287</v>
       </c>
       <c r="M107" t="n">
         <v>8</v>
@@ -8746,7 +8746,7 @@
         <v>12.74959429901925</v>
       </c>
       <c r="L108" t="n">
-        <v>98.19193324061196</v>
+        <v>98.18941504178274</v>
       </c>
       <c r="M108" t="n">
         <v>8</v>
@@ -8823,7 +8823,7 @@
         <v>5.622540956370159</v>
       </c>
       <c r="L109" t="n">
-        <v>97.77468706536857</v>
+        <v>97.7715877437326</v>
       </c>
       <c r="M109" t="n">
         <v>8</v>
@@ -8900,7 +8900,7 @@
         <v>5.923913043478257</v>
       </c>
       <c r="L110" t="n">
-        <v>97.2183588317107</v>
+        <v>97.21448467966573</v>
       </c>
       <c r="M110" t="n">
         <v>8</v>
@@ -8977,7 +8977,7 @@
         <v>18.30029837374882</v>
       </c>
       <c r="L111" t="n">
-        <v>96.52294853963839</v>
+        <v>96.51810584958217</v>
       </c>
       <c r="M111" t="n">
         <v>8</v>
@@ -9054,7 +9054,7 @@
         <v>0.4948774227319319</v>
       </c>
       <c r="L112" t="n">
-        <v>96.105702364395</v>
+        <v>96.10027855153204</v>
       </c>
       <c r="M112" t="n">
         <v>8</v>
@@ -9122,16 +9122,16 @@
         <v>2983.800048828125</v>
       </c>
       <c r="I113" t="n">
-        <v>1175.257470329055</v>
+        <v>1175.257587358084</v>
       </c>
       <c r="J113" t="n">
-        <v>109.2307483322371</v>
+        <v>109.2307274975949</v>
       </c>
       <c r="K113" t="n">
         <v>21.34201093241663</v>
       </c>
       <c r="L113" t="n">
-        <v>95.54937413073714</v>
+        <v>95.54317548746518</v>
       </c>
       <c r="M113" t="n">
         <v>8</v>
@@ -9208,7 +9208,7 @@
         <v>2.330222484211042</v>
       </c>
       <c r="L114" t="n">
-        <v>95.2712100139082</v>
+        <v>95.26462395543176</v>
       </c>
       <c r="M114" t="n">
         <v>8</v>
@@ -9285,7 +9285,7 @@
         <v>5.986872990681458</v>
       </c>
       <c r="L115" t="n">
-        <v>94.1585535465925</v>
+        <v>94.15041782729804</v>
       </c>
       <c r="M115" t="n">
         <v>8</v>
@@ -9362,7 +9362,7 @@
         <v>6.970849176172367</v>
       </c>
       <c r="L116" t="n">
-        <v>93.18497913769124</v>
+        <v>93.17548746518106</v>
       </c>
       <c r="M116" t="n">
         <v>8</v>
@@ -9439,7 +9439,7 @@
         <v>11.46907971856157</v>
       </c>
       <c r="L117" t="n">
-        <v>92.48956884561892</v>
+        <v>92.47910863509749</v>
       </c>
       <c r="M117" t="n">
         <v>8</v>
@@ -9516,7 +9516,7 @@
         <v>7.55665632829432</v>
       </c>
       <c r="L118" t="n">
-        <v>90.95966620305981</v>
+        <v>90.94707520891365</v>
       </c>
       <c r="M118" t="n">
         <v>8</v>
@@ -9593,7 +9593,7 @@
         <v>10.08247985533426</v>
       </c>
       <c r="L119" t="n">
-        <v>90.54242002781642</v>
+        <v>90.5292479108635</v>
       </c>
       <c r="M119" t="n">
         <v>8</v>
@@ -9670,7 +9670,7 @@
         <v>15.74556860874883</v>
       </c>
       <c r="L120" t="n">
-        <v>90.40333796940195</v>
+        <v>90.38997214484679</v>
       </c>
       <c r="M120" t="n">
         <v>8</v>
@@ -9747,7 +9747,7 @@
         <v>13.23817156256792</v>
       </c>
       <c r="L121" t="n">
-        <v>90.12517385257301</v>
+        <v>90.11142061281338</v>
       </c>
       <c r="M121" t="n">
         <v>8</v>
@@ -9824,7 +9824,7 @@
         <v>5.629728526924782</v>
       </c>
       <c r="L122" t="n">
-        <v>89.84700973574408</v>
+        <v>89.83286908077994</v>
       </c>
       <c r="M122" t="n">
         <v>8</v>
@@ -9901,7 +9901,7 @@
         <v>7.998390308969561</v>
       </c>
       <c r="L123" t="n">
-        <v>89.01251738525731</v>
+        <v>88.99721448467966</v>
       </c>
       <c r="M123" t="n">
         <v>8</v>
@@ -9978,7 +9978,7 @@
         <v>9.947647882880673</v>
       </c>
       <c r="L124" t="n">
-        <v>88.87343532684284</v>
+        <v>88.85793871866295</v>
       </c>
       <c r="M124" t="n">
         <v>8</v>
@@ -10055,7 +10055,7 @@
         <v>7.822033331007017</v>
       </c>
       <c r="L125" t="n">
-        <v>88.59527121001391</v>
+        <v>88.57938718662952</v>
       </c>
       <c r="M125" t="n">
         <v>8</v>
@@ -10132,7 +10132,7 @@
         <v>3.928866699862699</v>
       </c>
       <c r="L126" t="n">
-        <v>87.89986091794158</v>
+        <v>87.88300835654597</v>
       </c>
       <c r="M126" t="n">
         <v>8</v>
@@ -10209,7 +10209,7 @@
         <v>10.6750329457179</v>
       </c>
       <c r="L127" t="n">
-        <v>87.48261474269819</v>
+        <v>87.46518105849582</v>
       </c>
       <c r="M127" t="n">
         <v>8</v>
@@ -10286,7 +10286,7 @@
         <v>7.588729572731578</v>
       </c>
       <c r="L128" t="n">
-        <v>87.34353268428373</v>
+        <v>87.32590529247911</v>
       </c>
       <c r="M128" t="n">
         <v>8</v>
@@ -10363,7 +10363,7 @@
         <v>13.23144959719722</v>
       </c>
       <c r="L129" t="n">
-        <v>87.20445062586927</v>
+        <v>87.1866295264624</v>
       </c>
       <c r="M129" t="n">
         <v>8</v>
@@ -10440,7 +10440,7 @@
         <v>10.3983993518685</v>
       </c>
       <c r="L130" t="n">
-        <v>86.64812239221141</v>
+        <v>86.62952646239555</v>
       </c>
       <c r="M130" t="n">
         <v>8</v>
@@ -10517,7 +10517,7 @@
         <v>10.82612403188041</v>
       </c>
       <c r="L131" t="n">
-        <v>85.95271210013908</v>
+        <v>85.93314763231199</v>
       </c>
       <c r="M131" t="n">
         <v>8</v>
@@ -10594,7 +10594,7 @@
         <v>6.55487484575481</v>
       </c>
       <c r="L132" t="n">
-        <v>85.1182197496523</v>
+        <v>85.0974930362117</v>
       </c>
       <c r="M132" t="n">
         <v>8</v>
@@ -10671,7 +10671,7 @@
         <v>10.04150726365511</v>
       </c>
       <c r="L133" t="n">
-        <v>84.84005563282336</v>
+        <v>84.81894150417827</v>
       </c>
       <c r="M133" t="n">
         <v>8</v>
@@ -10748,7 +10748,7 @@
         <v>8.375087748231813</v>
       </c>
       <c r="L134" t="n">
-        <v>84.14464534075104</v>
+        <v>84.12256267409471</v>
       </c>
       <c r="M134" t="n">
         <v>8</v>
@@ -10825,7 +10825,7 @@
         <v>14.76510405478102</v>
       </c>
       <c r="L135" t="n">
-        <v>84.00556328233658</v>
+        <v>83.98328690807799</v>
       </c>
       <c r="M135" t="n">
         <v>8</v>
@@ -10902,7 +10902,7 @@
         <v>11.39584163642033</v>
       </c>
       <c r="L136" t="n">
-        <v>83.86648122392212</v>
+        <v>83.84401114206128</v>
       </c>
       <c r="M136" t="n">
         <v>8</v>
@@ -10979,7 +10979,7 @@
         <v>3.446426391601554</v>
       </c>
       <c r="L137" t="n">
-        <v>83.44923504867872</v>
+        <v>83.42618384401113</v>
       </c>
       <c r="M137" t="n">
         <v>8</v>
@@ -11056,7 +11056,7 @@
         <v>13.82920110192838</v>
       </c>
       <c r="L138" t="n">
-        <v>83.31015299026426</v>
+        <v>83.28690807799443</v>
       </c>
       <c r="M138" t="n">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>11.12548102727247</v>
       </c>
       <c r="L139" t="n">
-        <v>82.336578581363</v>
+        <v>82.31197771587743</v>
       </c>
       <c r="M139" t="n">
         <v>8</v>
@@ -11210,7 +11210,7 @@
         <v>5.698985756614405</v>
       </c>
       <c r="L140" t="n">
-        <v>81.91933240611962</v>
+        <v>81.89415041782729</v>
       </c>
       <c r="M140" t="n">
         <v>8</v>
@@ -11287,7 +11287,7 @@
         <v>15.13043478260869</v>
       </c>
       <c r="L141" t="n">
-        <v>81.50208623087622</v>
+        <v>81.47632311977716</v>
       </c>
       <c r="M141" t="n">
         <v>8</v>
@@ -11364,7 +11364,7 @@
         <v>5.127815877584596</v>
       </c>
       <c r="L142" t="n">
-        <v>81.08484005563282</v>
+        <v>81.05849582172702</v>
       </c>
       <c r="M142" t="n">
         <v>8</v>
@@ -11441,7 +11441,7 @@
         <v>8.891082616243962</v>
       </c>
       <c r="L143" t="n">
-        <v>80.94575799721837</v>
+        <v>80.91922005571031</v>
       </c>
       <c r="M143" t="n">
         <v>8</v>
@@ -11518,7 +11518,7 @@
         <v>14.61788868842659</v>
       </c>
       <c r="L144" t="n">
-        <v>80.80667593880389</v>
+        <v>80.77994428969359</v>
       </c>
       <c r="M144" t="n">
         <v>8</v>
@@ -11595,7 +11595,7 @@
         <v>7.933246701934493</v>
       </c>
       <c r="L145" t="n">
-        <v>80.3894297635605</v>
+        <v>80.36211699164345</v>
       </c>
       <c r="M145" t="n">
         <v>8</v>
@@ -11672,7 +11672,7 @@
         <v>17.80259528641939</v>
       </c>
       <c r="L146" t="n">
-        <v>80.11126564673157</v>
+        <v>80.08356545961003</v>
       </c>
       <c r="M146" t="n">
         <v>8</v>
@@ -11749,7 +11749,7 @@
         <v>3.320721022161344</v>
       </c>
       <c r="L147" t="n">
-        <v>79.97218358831711</v>
+        <v>79.94428969359332</v>
       </c>
       <c r="M147" t="n">
         <v>8</v>
@@ -11826,7 +11826,7 @@
         <v>6.371948308090825</v>
       </c>
       <c r="L148" t="n">
-        <v>79.69401947148818</v>
+        <v>79.66573816155989</v>
       </c>
       <c r="M148" t="n">
         <v>8</v>
@@ -11903,7 +11903,7 @@
         <v>7.427227754548116</v>
       </c>
       <c r="L149" t="n">
-        <v>78.85952712100139</v>
+        <v>78.8300835654596</v>
       </c>
       <c r="M149" t="n">
         <v>8</v>
@@ -11980,7 +11980,7 @@
         <v>9.5589917601131</v>
       </c>
       <c r="L150" t="n">
-        <v>78.72044506258693</v>
+        <v>78.69080779944289</v>
       </c>
       <c r="M150" t="n">
         <v>8</v>
@@ -12057,7 +12057,7 @@
         <v>10.66666666666667</v>
       </c>
       <c r="L151" t="n">
-        <v>78.58136300417246</v>
+        <v>78.55153203342618</v>
       </c>
       <c r="M151" t="n">
         <v>8</v>
@@ -12134,7 +12134,7 @@
         <v>10.31416252075292</v>
       </c>
       <c r="L152" t="n">
-        <v>78.30319888734353</v>
+        <v>78.27298050139275</v>
       </c>
       <c r="M152" t="n">
         <v>8</v>
@@ -12211,7 +12211,7 @@
         <v>10.26610754275596</v>
       </c>
       <c r="L153" t="n">
-        <v>77.32962447844228</v>
+        <v>77.29805013927576</v>
       </c>
       <c r="M153" t="n">
         <v>8</v>
@@ -12288,7 +12288,7 @@
         <v>2.284440104166663</v>
       </c>
       <c r="L154" t="n">
-        <v>77.19054242002782</v>
+        <v>77.15877437325905</v>
       </c>
       <c r="M154" t="n">
         <v>8</v>
@@ -12365,7 +12365,7 @@
         <v>11.86011150532185</v>
       </c>
       <c r="L155" t="n">
-        <v>76.35605006954103</v>
+        <v>76.32311977715878</v>
       </c>
       <c r="M155" t="n">
         <v>8</v>
@@ -12442,7 +12442,7 @@
         <v>8.091414453366275</v>
       </c>
       <c r="L156" t="n">
-        <v>75.24339360222531</v>
+        <v>75.20891364902506</v>
       </c>
       <c r="M156" t="n">
         <v>8</v>
@@ -12519,7 +12519,7 @@
         <v>7.834396848253378</v>
       </c>
       <c r="L157" t="n">
-        <v>75.10431154381085</v>
+        <v>75.06963788300835</v>
       </c>
       <c r="M157" t="n">
         <v>8</v>
@@ -12596,7 +12596,7 @@
         <v>19.77499376099896</v>
       </c>
       <c r="L158" t="n">
-        <v>74.68706536856745</v>
+        <v>74.65181058495823</v>
       </c>
       <c r="M158" t="n">
         <v>8</v>
@@ -12673,7 +12673,7 @@
         <v>11.99785138627687</v>
       </c>
       <c r="L159" t="n">
-        <v>73.99165507649514</v>
+        <v>73.95543175487465</v>
       </c>
       <c r="M159" t="n">
         <v>8</v>
@@ -12750,7 +12750,7 @@
         <v>11.36804119676664</v>
       </c>
       <c r="L160" t="n">
-        <v>73.7134909596662</v>
+        <v>73.67688022284122</v>
       </c>
       <c r="M160" t="n">
         <v>8</v>
@@ -12827,7 +12827,7 @@
         <v>6.876546909859949</v>
       </c>
       <c r="L161" t="n">
-        <v>73.57440890125174</v>
+        <v>73.53760445682451</v>
       </c>
       <c r="M161" t="n">
         <v>8</v>
@@ -12895,16 +12895,16 @@
         <v>1988.900024414062</v>
       </c>
       <c r="I162" t="n">
-        <v>1266.16157090969</v>
+        <v>1266.161452106784</v>
       </c>
       <c r="J162" t="n">
-        <v>48.28281343676275</v>
+        <v>48.28282735001928</v>
       </c>
       <c r="K162" t="n">
         <v>5.933423404211058</v>
       </c>
       <c r="L162" t="n">
-        <v>73.43532684283728</v>
+        <v>73.3983286908078</v>
       </c>
       <c r="M162" t="n">
         <v>8</v>
@@ -12981,7 +12981,7 @@
         <v>13.42740420468484</v>
       </c>
       <c r="L163" t="n">
-        <v>73.29624478442281</v>
+        <v>73.25905292479109</v>
       </c>
       <c r="M163" t="n">
         <v>8</v>
@@ -13058,7 +13058,7 @@
         <v>4.334923367959509</v>
       </c>
       <c r="L164" t="n">
-        <v>72.04450625869264</v>
+        <v>72.00557103064067</v>
       </c>
       <c r="M164" t="n">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>22.79025822752938</v>
       </c>
       <c r="L165" t="n">
-        <v>71.62726008344924</v>
+        <v>71.58774373259052</v>
       </c>
       <c r="M165" t="n">
         <v>8</v>
@@ -13212,7 +13212,7 @@
         <v>13.24034652951598</v>
       </c>
       <c r="L166" t="n">
-        <v>71.48817802503477</v>
+        <v>71.44846796657382</v>
       </c>
       <c r="M166" t="n">
         <v>8</v>
@@ -13289,7 +13289,7 @@
         <v>16.91086836297784</v>
       </c>
       <c r="L167" t="n">
-        <v>71.3490959666203</v>
+        <v>71.30919220055711</v>
       </c>
       <c r="M167" t="n">
         <v>8</v>
@@ -13366,7 +13366,7 @@
         <v>6.171832517672637</v>
       </c>
       <c r="L168" t="n">
-        <v>71.07093184979138</v>
+        <v>71.03064066852369</v>
       </c>
       <c r="M168" t="n">
         <v>8</v>
@@ -13443,7 +13443,7 @@
         <v>4.015988968467332</v>
       </c>
       <c r="L169" t="n">
-        <v>70.93184979137691</v>
+        <v>70.89136490250696</v>
       </c>
       <c r="M169" t="n">
         <v>8</v>
@@ -13520,7 +13520,7 @@
         <v>11.12045628585694</v>
       </c>
       <c r="L170" t="n">
-        <v>70.65368567454799</v>
+        <v>70.61281337047353</v>
       </c>
       <c r="M170" t="n">
         <v>8</v>
@@ -13597,7 +13597,7 @@
         <v>9.676068088830858</v>
       </c>
       <c r="L171" t="n">
-        <v>70.51460361613351</v>
+        <v>70.47353760445682</v>
       </c>
       <c r="M171" t="n">
         <v>8</v>
@@ -13674,7 +13674,7 @@
         <v>8.502090296410136</v>
       </c>
       <c r="L172" t="n">
-        <v>70.09735744089014</v>
+        <v>70.05571030640668</v>
       </c>
       <c r="M172" t="n">
         <v>8</v>
@@ -13751,7 +13751,7 @@
         <v>2.682122144980426</v>
       </c>
       <c r="L173" t="n">
-        <v>69.54102920723227</v>
+        <v>69.49860724233984</v>
       </c>
       <c r="M173" t="n">
         <v>8</v>
@@ -13828,7 +13828,7 @@
         <v>5.496766442908929</v>
       </c>
       <c r="L174" t="n">
-        <v>68.42837273991655</v>
+        <v>68.38440111420613</v>
       </c>
       <c r="M174" t="n">
         <v>8</v>
@@ -13905,7 +13905,7 @@
         <v>4.705965475839746</v>
       </c>
       <c r="L175" t="n">
-        <v>67.87204450625869</v>
+        <v>67.82729805013928</v>
       </c>
       <c r="M175" t="n">
         <v>8</v>
@@ -13982,7 +13982,7 @@
         <v>5.777061780376758</v>
       </c>
       <c r="L176" t="n">
-        <v>67.59388038942976</v>
+        <v>67.54874651810584</v>
       </c>
       <c r="M176" t="n">
         <v>8</v>
@@ -14059,7 +14059,7 @@
         <v>2.327514546965914</v>
       </c>
       <c r="L177" t="n">
-        <v>67.4547983310153</v>
+        <v>67.40947075208913</v>
       </c>
       <c r="M177" t="n">
         <v>8</v>
@@ -14136,7 +14136,7 @@
         <v>4.365137599869895</v>
       </c>
       <c r="L178" t="n">
-        <v>67.31571627260084</v>
+        <v>67.27019498607241</v>
       </c>
       <c r="M178" t="n">
         <v>8</v>
@@ -14213,7 +14213,7 @@
         <v>13.16270566727604</v>
       </c>
       <c r="L179" t="n">
-        <v>67.17663421418636</v>
+        <v>67.1309192200557</v>
       </c>
       <c r="M179" t="n">
         <v>8</v>
@@ -14290,7 +14290,7 @@
         <v>14.15957000992447</v>
       </c>
       <c r="L180" t="n">
-        <v>66.48122392211405</v>
+        <v>66.43454038997214</v>
       </c>
       <c r="M180" t="n">
         <v>8</v>
@@ -14367,7 +14367,7 @@
         <v>4.855687606112058</v>
       </c>
       <c r="L181" t="n">
-        <v>66.20305980528511</v>
+        <v>66.15598885793872</v>
       </c>
       <c r="M181" t="n">
         <v>8</v>
@@ -14444,7 +14444,7 @@
         <v>10.89841845835475</v>
       </c>
       <c r="L182" t="n">
-        <v>66.06397774687065</v>
+        <v>66.01671309192201</v>
       </c>
       <c r="M182" t="n">
         <v>8</v>
@@ -14521,7 +14521,7 @@
         <v>1.962264150943405</v>
       </c>
       <c r="L183" t="n">
-        <v>65.92489568845619</v>
+        <v>65.87743732590529</v>
       </c>
       <c r="M183" t="n">
         <v>8</v>
@@ -14598,7 +14598,7 @@
         <v>9.778945799527383</v>
       </c>
       <c r="L184" t="n">
-        <v>65.78581363004173</v>
+        <v>65.73816155988858</v>
       </c>
       <c r="M184" t="n">
         <v>8</v>
@@ -14675,7 +14675,7 @@
         <v>3.456764933577228</v>
       </c>
       <c r="L185" t="n">
-        <v>65.64673157162726</v>
+        <v>65.59888579387186</v>
       </c>
       <c r="M185" t="n">
         <v>8</v>
@@ -14752,7 +14752,7 @@
         <v>4.669169744784307</v>
       </c>
       <c r="L186" t="n">
-        <v>65.5076495132128</v>
+        <v>65.45961002785515</v>
       </c>
       <c r="M186" t="n">
         <v>8</v>
@@ -14817,7 +14817,7 @@
         <v>4.212245529702208</v>
       </c>
       <c r="H187" t="n">
-        <v>2269.472002658311</v>
+        <v>2269.472253037084</v>
       </c>
       <c r="I187" t="n">
         <v>1353.205955540699</v>
@@ -14826,10 +14826,10 @@
         <v>52.08327982695642</v>
       </c>
       <c r="K187" t="n">
-        <v>10.27560751498111</v>
+        <v>10.27561968110222</v>
       </c>
       <c r="L187" t="n">
-        <v>65.22948539638386</v>
+        <v>65.18105849582173</v>
       </c>
       <c r="M187" t="n">
         <v>8</v>
@@ -14906,7 +14906,7 @@
         <v>10.48434681457255</v>
       </c>
       <c r="L188" t="n">
-        <v>64.25591098748261</v>
+        <v>64.20612813370474</v>
       </c>
       <c r="M188" t="n">
         <v>8</v>
@@ -14983,7 +14983,7 @@
         <v>3.691937326835637</v>
       </c>
       <c r="L189" t="n">
-        <v>63.97774687065368</v>
+        <v>63.92757660167131</v>
       </c>
       <c r="M189" t="n">
         <v>8</v>
@@ -15060,7 +15060,7 @@
         <v>13.02174590126215</v>
       </c>
       <c r="L190" t="n">
-        <v>63.69958275382476</v>
+        <v>63.64902506963789</v>
       </c>
       <c r="M190" t="n">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>12.15132530032315</v>
       </c>
       <c r="L191" t="n">
-        <v>58.69262865090403</v>
+        <v>58.63509749303621</v>
       </c>
       <c r="M191" t="n">
         <v>8</v>
@@ -15214,7 +15214,7 @@
         <v>4.935173910205237</v>
       </c>
       <c r="L192" t="n">
-        <v>57.02364394993046</v>
+        <v>56.96378830083565</v>
       </c>
       <c r="M192" t="n">
         <v>8</v>
@@ -15291,7 +15291,7 @@
         <v>8.385305791398245</v>
       </c>
       <c r="L193" t="n">
-        <v>55.49374130737134</v>
+        <v>55.43175487465181</v>
       </c>
       <c r="M193" t="n">
         <v>8</v>
@@ -15356,7 +15356,7 @@
         <v>1.955326403346302</v>
       </c>
       <c r="H194" t="n">
-        <v>6552.654210942315</v>
+        <v>6552.654707500795</v>
       </c>
       <c r="I194" t="n">
         <v>4229.809203861739</v>
@@ -15365,10 +15365,10 @@
         <v>33.41027285221385</v>
       </c>
       <c r="K194" t="n">
-        <v>16.12004626869246</v>
+        <v>16.12005506824021</v>
       </c>
       <c r="L194" t="n">
-        <v>55.07649513212796</v>
+        <v>55.01392757660167</v>
       </c>
       <c r="M194" t="n">
         <v>8</v>
@@ -15445,7 +15445,7 @@
         <v>23.17766199241169</v>
       </c>
       <c r="L195" t="n">
-        <v>52.29485396383866</v>
+        <v>52.22841225626741</v>
       </c>
       <c r="M195" t="n">
         <v>8</v>
@@ -15522,7 +15522,7 @@
         <v>15.11145656297557</v>
       </c>
       <c r="L196" t="n">
-        <v>49.51321279554937</v>
+        <v>49.44289693593314</v>
       </c>
       <c r="M196" t="n">
         <v>8</v>
@@ -15599,7 +15599,7 @@
         <v>19.19886590683419</v>
       </c>
       <c r="L197" t="n">
-        <v>49.23504867872045</v>
+        <v>49.16434540389972</v>
       </c>
       <c r="M197" t="n">
         <v>8</v>
@@ -15676,7 +15676,7 @@
         <v>18.92806674164547</v>
       </c>
       <c r="L198" t="n">
-        <v>46.59248956884562</v>
+        <v>46.51810584958218</v>
       </c>
       <c r="M198" t="n">
         <v>8</v>
@@ -15753,7 +15753,7 @@
         <v>27.71624632621594</v>
       </c>
       <c r="L199" t="n">
-        <v>95.96662030598053</v>
+        <v>95.96100278551532</v>
       </c>
       <c r="M199" t="n">
         <v>7</v>
@@ -15830,7 +15830,7 @@
         <v>19.52451216101434</v>
       </c>
       <c r="L200" t="n">
-        <v>94.99304589707927</v>
+        <v>94.98607242339833</v>
       </c>
       <c r="M200" t="n">
         <v>7</v>
@@ -15907,7 +15907,7 @@
         <v>18.12898599459618</v>
       </c>
       <c r="L201" t="n">
-        <v>89.56884561891516</v>
+        <v>89.55431754874652</v>
       </c>
       <c r="M201" t="n">
         <v>7</v>
@@ -15984,7 +15984,7 @@
         <v>23.36250600742533</v>
       </c>
       <c r="L202" t="n">
-        <v>85.39638386648123</v>
+        <v>85.37604456824512</v>
       </c>
       <c r="M202" t="n">
         <v>7</v>
@@ -16061,7 +16061,7 @@
         <v>16.56609983543609</v>
       </c>
       <c r="L203" t="n">
-        <v>84.70097357440891</v>
+        <v>84.67966573816156</v>
       </c>
       <c r="M203" t="n">
         <v>7</v>
@@ -16138,7 +16138,7 @@
         <v>9.449088135100547</v>
       </c>
       <c r="L204" t="n">
-        <v>83.58831710709318</v>
+        <v>83.56545961002786</v>
       </c>
       <c r="M204" t="n">
         <v>7</v>
@@ -16215,7 +16215,7 @@
         <v>22.20400087011052</v>
       </c>
       <c r="L205" t="n">
-        <v>83.17107093184978</v>
+        <v>83.14763231197772</v>
       </c>
       <c r="M205" t="n">
         <v>7</v>
@@ -16292,7 +16292,7 @@
         <v>19.66140636050977</v>
       </c>
       <c r="L206" t="n">
-        <v>82.89290681502086</v>
+        <v>82.8690807799443</v>
       </c>
       <c r="M206" t="n">
         <v>7</v>
@@ -16369,7 +16369,7 @@
         <v>12.38482063018396</v>
       </c>
       <c r="L207" t="n">
-        <v>78.02503477051459</v>
+        <v>77.99442896935933</v>
       </c>
       <c r="M207" t="n">
         <v>7</v>
@@ -16446,7 +16446,7 @@
         <v>17.24065306221008</v>
       </c>
       <c r="L208" t="n">
-        <v>75.79972183588318</v>
+        <v>75.76601671309191</v>
       </c>
       <c r="M208" t="n">
         <v>7</v>
@@ -16523,7 +16523,7 @@
         <v>14.10480010483608</v>
       </c>
       <c r="L209" t="n">
-        <v>73.85257301808068</v>
+        <v>73.81615598885793</v>
       </c>
       <c r="M209" t="n">
         <v>7</v>
@@ -16600,7 +16600,7 @@
         <v>12.11986216687462</v>
       </c>
       <c r="L210" t="n">
-        <v>72.46175243393603</v>
+        <v>72.42339832869081</v>
       </c>
       <c r="M210" t="n">
         <v>7</v>
@@ -16677,7 +16677,7 @@
         <v>20.69456724543797</v>
       </c>
       <c r="L211" t="n">
-        <v>71.90542420027816</v>
+        <v>71.86629526462396</v>
       </c>
       <c r="M211" t="n">
         <v>7</v>
@@ -16754,7 +16754,7 @@
         <v>10.08978949652777</v>
       </c>
       <c r="L212" t="n">
-        <v>71.7663421418637</v>
+        <v>71.72701949860725</v>
       </c>
       <c r="M212" t="n">
         <v>7</v>
@@ -16831,7 +16831,7 @@
         <v>15.4433916199882</v>
       </c>
       <c r="L213" t="n">
-        <v>71.21001390820584</v>
+        <v>71.1699164345404</v>
       </c>
       <c r="M213" t="n">
         <v>7</v>
@@ -16908,7 +16908,7 @@
         <v>8.522701444212677</v>
       </c>
       <c r="L214" t="n">
-        <v>69.95827538247566</v>
+        <v>69.91643454038997</v>
       </c>
       <c r="M214" t="n">
         <v>7</v>
@@ -16985,7 +16985,7 @@
         <v>11.73017759156154</v>
       </c>
       <c r="L215" t="n">
-        <v>69.81919332406119</v>
+        <v>69.77715877437326</v>
       </c>
       <c r="M215" t="n">
         <v>7</v>
@@ -17062,7 +17062,7 @@
         <v>6.846843181071693</v>
       </c>
       <c r="L216" t="n">
-        <v>69.4019471488178</v>
+        <v>69.35933147632312</v>
       </c>
       <c r="M216" t="n">
         <v>7</v>
@@ -17139,7 +17139,7 @@
         <v>15.33158530475798</v>
       </c>
       <c r="L217" t="n">
-        <v>69.26286509040334</v>
+        <v>69.22005571030641</v>
       </c>
       <c r="M217" t="n">
         <v>7</v>
@@ -17216,7 +17216,7 @@
         <v>30.50957471700362</v>
       </c>
       <c r="L218" t="n">
-        <v>69.12378303198888</v>
+        <v>69.08077994428969</v>
       </c>
       <c r="M218" t="n">
         <v>7</v>
@@ -17293,7 +17293,7 @@
         <v>6.078488840346163</v>
       </c>
       <c r="L219" t="n">
-        <v>68.84561891515995</v>
+        <v>68.80222841225627</v>
       </c>
       <c r="M219" t="n">
         <v>7</v>
@@ -17370,7 +17370,7 @@
         <v>24.86865148861646</v>
       </c>
       <c r="L220" t="n">
-        <v>68.56745479833101</v>
+        <v>68.52367688022284</v>
       </c>
       <c r="M220" t="n">
         <v>7</v>
@@ -17447,7 +17447,7 @@
         <v>10.26132149959391</v>
       </c>
       <c r="L221" t="n">
-        <v>68.15020862308762</v>
+        <v>68.10584958217271</v>
       </c>
       <c r="M221" t="n">
         <v>7</v>
@@ -17524,7 +17524,7 @@
         <v>13.67363875986523</v>
       </c>
       <c r="L222" t="n">
-        <v>67.73296244784423</v>
+        <v>67.68802228412257</v>
       </c>
       <c r="M222" t="n">
         <v>7</v>
@@ -17601,7 +17601,7 @@
         <v>4.982491959539015</v>
       </c>
       <c r="L223" t="n">
-        <v>67.03755215577191</v>
+        <v>66.99164345403899</v>
       </c>
       <c r="M223" t="n">
         <v>7</v>
@@ -17678,7 +17678,7 @@
         <v>1.119025211485369</v>
       </c>
       <c r="L224" t="n">
-        <v>66.62030598052851</v>
+        <v>66.57381615598887</v>
       </c>
       <c r="M224" t="n">
         <v>7</v>
@@ -17755,7 +17755,7 @@
         <v>16.81373800141073</v>
       </c>
       <c r="L225" t="n">
-        <v>64.95132127955495</v>
+        <v>64.9025069637883</v>
       </c>
       <c r="M225" t="n">
         <v>7</v>
@@ -17832,7 +17832,7 @@
         <v>31.13374564557483</v>
       </c>
       <c r="L226" t="n">
-        <v>64.67315716272601</v>
+        <v>64.62395543175488</v>
       </c>
       <c r="M226" t="n">
         <v>7</v>
@@ -17909,7 +17909,7 @@
         <v>6.052304413998155</v>
       </c>
       <c r="L227" t="n">
-        <v>64.39499304589708</v>
+        <v>64.34540389972145</v>
       </c>
       <c r="M227" t="n">
         <v>7</v>
@@ -17986,7 +17986,7 @@
         <v>7.589285714285721</v>
       </c>
       <c r="L228" t="n">
-        <v>63.83866481223922</v>
+        <v>63.7883008356546</v>
       </c>
       <c r="M228" t="n">
         <v>7</v>
@@ -18063,7 +18063,7 @@
         <v>7.860888059077009</v>
       </c>
       <c r="L229" t="n">
-        <v>63.56050069541029</v>
+        <v>63.50974930362116</v>
       </c>
       <c r="M229" t="n">
         <v>7</v>
@@ -18140,7 +18140,7 @@
         <v>16.22385582905401</v>
       </c>
       <c r="L230" t="n">
-        <v>63.42141863699583</v>
+        <v>63.37047353760445</v>
       </c>
       <c r="M230" t="n">
         <v>7</v>
@@ -18217,7 +18217,7 @@
         <v>10.92880946855845</v>
       </c>
       <c r="L231" t="n">
-        <v>63.14325452016691</v>
+        <v>63.09192200557104</v>
       </c>
       <c r="M231" t="n">
         <v>7</v>
@@ -18294,7 +18294,7 @@
         <v>8.473163634015712</v>
       </c>
       <c r="L232" t="n">
-        <v>62.7260083449235</v>
+        <v>62.67409470752089</v>
       </c>
       <c r="M232" t="n">
         <v>7</v>
@@ -18371,7 +18371,7 @@
         <v>28.27356470421858</v>
       </c>
       <c r="L233" t="n">
-        <v>62.16968011126565</v>
+        <v>62.11699164345404</v>
       </c>
       <c r="M233" t="n">
         <v>7</v>
@@ -18448,7 +18448,7 @@
         <v>13.15925020222794</v>
       </c>
       <c r="L234" t="n">
-        <v>61.75243393602226</v>
+        <v>61.6991643454039</v>
       </c>
       <c r="M234" t="n">
         <v>7</v>
@@ -18525,7 +18525,7 @@
         <v>11.3723722189047</v>
       </c>
       <c r="L235" t="n">
-        <v>61.33518776077887</v>
+        <v>61.28133704735376</v>
       </c>
       <c r="M235" t="n">
         <v>7</v>
@@ -18602,7 +18602,7 @@
         <v>19.43291803996383</v>
       </c>
       <c r="L236" t="n">
-        <v>60.91794158553546</v>
+        <v>60.86350974930362</v>
       </c>
       <c r="M236" t="n">
         <v>7</v>
@@ -18679,7 +18679,7 @@
         <v>10.31925037628971</v>
       </c>
       <c r="L237" t="n">
-        <v>60.778859527121</v>
+        <v>60.72423398328691</v>
       </c>
       <c r="M237" t="n">
         <v>7</v>
@@ -18756,7 +18756,7 @@
         <v>16.79704360135934</v>
       </c>
       <c r="L238" t="n">
-        <v>60.08344923504868</v>
+        <v>60.02785515320335</v>
       </c>
       <c r="M238" t="n">
         <v>7</v>
@@ -18833,7 +18833,7 @@
         <v>20.99594648302705</v>
       </c>
       <c r="L239" t="n">
-        <v>59.94436717663422</v>
+        <v>59.88857938718662</v>
       </c>
       <c r="M239" t="n">
         <v>7</v>
@@ -18910,7 +18910,7 @@
         <v>21.86733026181937</v>
       </c>
       <c r="L240" t="n">
-        <v>59.80528511821975</v>
+        <v>59.74930362116991</v>
       </c>
       <c r="M240" t="n">
         <v>7</v>
@@ -18987,7 +18987,7 @@
         <v>12.35484596397298</v>
       </c>
       <c r="L241" t="n">
-        <v>59.66620305980529</v>
+        <v>59.61002785515321</v>
       </c>
       <c r="M241" t="n">
         <v>7</v>
@@ -19064,7 +19064,7 @@
         <v>7.516339869281041</v>
       </c>
       <c r="L242" t="n">
-        <v>59.52712100139082</v>
+        <v>59.47075208913649</v>
       </c>
       <c r="M242" t="n">
         <v>7</v>
@@ -19141,7 +19141,7 @@
         <v>4.786744400122744</v>
       </c>
       <c r="L243" t="n">
-        <v>59.38803894297635</v>
+        <v>59.33147632311978</v>
       </c>
       <c r="M243" t="n">
         <v>7</v>
@@ -19218,7 +19218,7 @@
         <v>12.24881777473588</v>
       </c>
       <c r="L244" t="n">
-        <v>59.10987482614743</v>
+        <v>59.05292479108635</v>
       </c>
       <c r="M244" t="n">
         <v>7</v>
@@ -19295,7 +19295,7 @@
         <v>23.23800551727764</v>
       </c>
       <c r="L245" t="n">
-        <v>58.55354659248957</v>
+        <v>58.4958217270195</v>
       </c>
       <c r="M245" t="n">
         <v>7</v>
@@ -19372,7 +19372,7 @@
         <v>9.375</v>
       </c>
       <c r="L246" t="n">
-        <v>58.27538247566064</v>
+        <v>58.21727019498607</v>
       </c>
       <c r="M246" t="n">
         <v>7</v>
@@ -19449,7 +19449,7 @@
         <v>15.16497421979663</v>
       </c>
       <c r="L247" t="n">
-        <v>57.44089012517385</v>
+        <v>57.38161559888579</v>
       </c>
       <c r="M247" t="n">
         <v>7</v>
@@ -19526,7 +19526,7 @@
         <v>8.097209712662323</v>
       </c>
       <c r="L248" t="n">
-        <v>57.16272600834492</v>
+        <v>57.10306406685237</v>
       </c>
       <c r="M248" t="n">
         <v>7</v>
@@ -19603,7 +19603,7 @@
         <v>13.60619127150649</v>
       </c>
       <c r="L249" t="n">
-        <v>56.88456189151599</v>
+        <v>56.82451253481894</v>
       </c>
       <c r="M249" t="n">
         <v>7</v>
@@ -19680,7 +19680,7 @@
         <v>35.30684789975356</v>
       </c>
       <c r="L250" t="n">
-        <v>56.18915159944368</v>
+        <v>56.12813370473538</v>
       </c>
       <c r="M250" t="n">
         <v>7</v>
@@ -19757,7 +19757,7 @@
         <v>12.00191259229673</v>
       </c>
       <c r="L251" t="n">
-        <v>56.05006954102921</v>
+        <v>55.98885793871866</v>
       </c>
       <c r="M251" t="n">
         <v>7</v>
@@ -19834,7 +19834,7 @@
         <v>18.09716895971747</v>
       </c>
       <c r="L252" t="n">
-        <v>55.77190542420028</v>
+        <v>55.71030640668524</v>
       </c>
       <c r="M252" t="n">
         <v>7</v>
@@ -19911,7 +19911,7 @@
         <v>6.576896804672172</v>
       </c>
       <c r="L253" t="n">
-        <v>55.63282336578581</v>
+        <v>55.57103064066852</v>
       </c>
       <c r="M253" t="n">
         <v>7</v>
@@ -19988,7 +19988,7 @@
         <v>19.54693087340067</v>
       </c>
       <c r="L254" t="n">
-        <v>55.35465924895689</v>
+        <v>55.29247910863509</v>
       </c>
       <c r="M254" t="n">
         <v>7</v>
@@ -20065,7 +20065,7 @@
         <v>14.91716800715337</v>
       </c>
       <c r="L255" t="n">
-        <v>54.1029207232267</v>
+        <v>54.03899721448467</v>
       </c>
       <c r="M255" t="n">
         <v>7</v>
@@ -20142,7 +20142,7 @@
         <v>14.60075376194421</v>
       </c>
       <c r="L256" t="n">
-        <v>53.40751043115438</v>
+        <v>53.34261838440112</v>
       </c>
       <c r="M256" t="n">
         <v>7</v>
@@ -20219,7 +20219,7 @@
         <v>4.874257888513234</v>
       </c>
       <c r="L257" t="n">
-        <v>52.99026425591099</v>
+        <v>52.92479108635098</v>
       </c>
       <c r="M257" t="n">
         <v>7</v>
@@ -20296,7 +20296,7 @@
         <v>11.24931276402388</v>
       </c>
       <c r="L258" t="n">
-        <v>52.71210013908206</v>
+        <v>52.64623955431755</v>
       </c>
       <c r="M258" t="n">
         <v>7</v>
@@ -20373,7 +20373,7 @@
         <v>17.12704674015166</v>
       </c>
       <c r="L259" t="n">
-        <v>52.1557719054242</v>
+        <v>52.0891364902507</v>
       </c>
       <c r="M259" t="n">
         <v>7</v>
@@ -20450,7 +20450,7 @@
         <v>10.33468860689963</v>
       </c>
       <c r="L260" t="n">
-        <v>51.59944367176634</v>
+        <v>51.53203342618384</v>
       </c>
       <c r="M260" t="n">
         <v>7</v>
@@ -20515,7 +20515,7 @@
         <v>0.6702086201100244</v>
       </c>
       <c r="H261" t="n">
-        <v>198.2251564414815</v>
+        <v>198.2251721274962</v>
       </c>
       <c r="I261" t="n">
         <v>164.6038301743624</v>
@@ -20524,10 +20524,10 @@
         <v>15.67166674967189</v>
       </c>
       <c r="K261" t="n">
-        <v>4.109854409581271</v>
+        <v>4.109862648034635</v>
       </c>
       <c r="L261" t="n">
-        <v>51.46036161335188</v>
+        <v>51.39275766016713</v>
       </c>
       <c r="M261" t="n">
         <v>7</v>
@@ -20604,7 +20604,7 @@
         <v>26.80955568237016</v>
       </c>
       <c r="L262" t="n">
-        <v>51.18219749652295</v>
+        <v>51.11420612813371</v>
       </c>
       <c r="M262" t="n">
         <v>7</v>
@@ -20681,7 +20681,7 @@
         <v>10.39240858478714</v>
       </c>
       <c r="L263" t="n">
-        <v>50.2086230876217</v>
+        <v>50.13927576601671</v>
       </c>
       <c r="M263" t="n">
         <v>7</v>
@@ -20758,7 +20758,7 @@
         <v>15.5343546064586</v>
       </c>
       <c r="L264" t="n">
-        <v>49.37413073713491</v>
+        <v>49.30362116991643</v>
       </c>
       <c r="M264" t="n">
         <v>7</v>
@@ -20835,7 +20835,7 @@
         <v>20.770085626782</v>
       </c>
       <c r="L265" t="n">
-        <v>48.67872044506258</v>
+        <v>48.60724233983287</v>
       </c>
       <c r="M265" t="n">
         <v>7</v>
@@ -20912,7 +20912,7 @@
         <v>30.98158995159472</v>
       </c>
       <c r="L266" t="n">
-        <v>48.40055632823366</v>
+        <v>48.32869080779944</v>
       </c>
       <c r="M266" t="n">
         <v>7</v>
@@ -20989,7 +20989,7 @@
         <v>9.588330632528752</v>
       </c>
       <c r="L267" t="n">
-        <v>47.00973574408901</v>
+        <v>46.93593314763231</v>
       </c>
       <c r="M267" t="n">
         <v>7</v>
@@ -21066,7 +21066,7 @@
         <v>37.13383233342689</v>
       </c>
       <c r="L268" t="n">
-        <v>46.73157162726008</v>
+        <v>46.65738161559889</v>
       </c>
       <c r="M268" t="n">
         <v>7</v>
@@ -21143,7 +21143,7 @@
         <v>30.40317123292966</v>
       </c>
       <c r="L269" t="n">
-        <v>46.03616133518776</v>
+        <v>45.96100278551532</v>
       </c>
       <c r="M269" t="n">
         <v>7</v>
@@ -21220,7 +21220,7 @@
         <v>21.35369193428083</v>
       </c>
       <c r="L270" t="n">
-        <v>43.11543810848401</v>
+        <v>43.03621169916435</v>
       </c>
       <c r="M270" t="n">
         <v>7</v>
@@ -21297,7 +21297,7 @@
         <v>22.90167640847631</v>
       </c>
       <c r="L271" t="n">
-        <v>42.55910987482615</v>
+        <v>42.4791086350975</v>
       </c>
       <c r="M271" t="n">
         <v>7</v>
@@ -21374,7 +21374,7 @@
         <v>68.69066671595827</v>
       </c>
       <c r="L272" t="n">
-        <v>42.28094575799722</v>
+        <v>42.20055710306407</v>
       </c>
       <c r="M272" t="n">
         <v>7</v>
@@ -21451,7 +21451,7 @@
         <v>22.21972301424997</v>
       </c>
       <c r="L273" t="n">
-        <v>42.14186369958276</v>
+        <v>42.06128133704735</v>
       </c>
       <c r="M273" t="n">
         <v>7</v>
@@ -21528,7 +21528,7 @@
         <v>52.30048813698082</v>
       </c>
       <c r="L274" t="n">
-        <v>40.89012517385257</v>
+        <v>40.80779944289694</v>
       </c>
       <c r="M274" t="n">
         <v>7</v>
@@ -21605,7 +21605,7 @@
         <v>21.67465573162914</v>
       </c>
       <c r="L275" t="n">
-        <v>39.22114047287899</v>
+        <v>39.13649025069638</v>
       </c>
       <c r="M275" t="n">
         <v>7</v>
@@ -21682,7 +21682,7 @@
         <v>35.61487978492606</v>
       </c>
       <c r="L276" t="n">
-        <v>38.38664812239222</v>
+        <v>38.3008356545961</v>
       </c>
       <c r="M276" t="n">
         <v>7</v>
@@ -21759,7 +21759,7 @@
         <v>34.42773277877651</v>
       </c>
       <c r="L277" t="n">
-        <v>33.79694019471488</v>
+        <v>33.70473537604457</v>
       </c>
       <c r="M277" t="n">
         <v>7</v>
@@ -21836,7 +21836,7 @@
         <v>127.7290654570593</v>
       </c>
       <c r="L278" t="n">
-        <v>24.61752433936022</v>
+        <v>24.5125348189415</v>
       </c>
       <c r="M278" t="n">
         <v>7</v>
@@ -21913,7 +21913,7 @@
         <v>61.96475094098821</v>
       </c>
       <c r="L279" t="n">
-        <v>18.08066759388039</v>
+        <v>17.96657381615599</v>
       </c>
       <c r="M279" t="n">
         <v>7</v>
@@ -21990,7 +21990,7 @@
         <v>39.21678845793517</v>
       </c>
       <c r="L280" t="n">
-        <v>96.94019471488178</v>
+        <v>96.93593314763231</v>
       </c>
       <c r="M280" t="n">
         <v>6</v>
@@ -22067,7 +22067,7 @@
         <v>18.35443037974684</v>
       </c>
       <c r="L281" t="n">
-        <v>96.24478442280946</v>
+        <v>96.23955431754875</v>
       </c>
       <c r="M281" t="n">
         <v>6</v>
@@ -22135,16 +22135,16 @@
         <v>2295</v>
       </c>
       <c r="I282" t="n">
-        <v>1123.303677487793</v>
+        <v>1123.303556351769</v>
       </c>
       <c r="J282" t="n">
-        <v>74.12922606774384</v>
+        <v>74.12924484567969</v>
       </c>
       <c r="K282" t="n">
         <v>17.33128834355828</v>
       </c>
       <c r="L282" t="n">
-        <v>84.28372739916551</v>
+        <v>84.26183844011142</v>
       </c>
       <c r="M282" t="n">
         <v>6</v>
@@ -22221,7 +22221,7 @@
         <v>14.04456703889516</v>
       </c>
       <c r="L283" t="n">
-        <v>79.41585535465924</v>
+        <v>79.38718662952647</v>
       </c>
       <c r="M283" t="n">
         <v>6</v>
@@ -22298,7 +22298,7 @@
         <v>24.11340242636444</v>
       </c>
       <c r="L284" t="n">
-        <v>79.27677329624478</v>
+        <v>79.24791086350976</v>
       </c>
       <c r="M284" t="n">
         <v>6</v>
@@ -22375,7 +22375,7 @@
         <v>12.48758943916355</v>
       </c>
       <c r="L285" t="n">
-        <v>77.74687065368568</v>
+        <v>77.71587743732591</v>
       </c>
       <c r="M285" t="n">
         <v>6</v>
@@ -22452,7 +22452,7 @@
         <v>10.44928522804629</v>
       </c>
       <c r="L286" t="n">
-        <v>77.60778859527122</v>
+        <v>77.57660167130919</v>
       </c>
       <c r="M286" t="n">
         <v>6</v>
@@ -22529,7 +22529,7 @@
         <v>19.85948347055337</v>
       </c>
       <c r="L287" t="n">
-        <v>74.26981919332405</v>
+        <v>74.23398328690809</v>
       </c>
       <c r="M287" t="n">
         <v>6</v>
@@ -22606,7 +22606,7 @@
         <v>27.06952443755033</v>
       </c>
       <c r="L288" t="n">
-        <v>73.15716272600834</v>
+        <v>73.11977715877437</v>
       </c>
       <c r="M288" t="n">
         <v>6</v>
@@ -22683,7 +22683,7 @@
         <v>25.09554140127388</v>
       </c>
       <c r="L289" t="n">
-        <v>72.18358831710709</v>
+        <v>72.14484679665738</v>
       </c>
       <c r="M289" t="n">
         <v>6</v>
@@ -22760,7 +22760,7 @@
         <v>15.77649572764499</v>
       </c>
       <c r="L290" t="n">
-        <v>70.23643949930459</v>
+        <v>70.19498607242339</v>
       </c>
       <c r="M290" t="n">
         <v>6</v>
@@ -22837,7 +22837,7 @@
         <v>13.49080225385933</v>
       </c>
       <c r="L291" t="n">
-        <v>68.98470097357441</v>
+        <v>68.94150417827298</v>
       </c>
       <c r="M291" t="n">
         <v>6</v>
@@ -22914,7 +22914,7 @@
         <v>11.4042164966746</v>
       </c>
       <c r="L292" t="n">
-        <v>68.2892906815021</v>
+        <v>68.24512534818942</v>
       </c>
       <c r="M292" t="n">
         <v>6</v>
@@ -22991,7 +22991,7 @@
         <v>9.025792600842465</v>
       </c>
       <c r="L293" t="n">
-        <v>65.36856745479834</v>
+        <v>65.32033426183844</v>
       </c>
       <c r="M293" t="n">
         <v>6</v>
@@ -23068,7 +23068,7 @@
         <v>19.11586577290763</v>
       </c>
       <c r="L294" t="n">
-        <v>64.81223922114047</v>
+        <v>64.76323119777159</v>
       </c>
       <c r="M294" t="n">
         <v>6</v>
@@ -23145,7 +23145,7 @@
         <v>9.835784600524056</v>
       </c>
       <c r="L295" t="n">
-        <v>64.53407510431154</v>
+        <v>64.48467966573817</v>
       </c>
       <c r="M295" t="n">
         <v>6</v>
@@ -23222,7 +23222,7 @@
         <v>22.1216855053916</v>
       </c>
       <c r="L296" t="n">
-        <v>64.11682892906815</v>
+        <v>64.06685236768801</v>
       </c>
       <c r="M296" t="n">
         <v>6</v>
@@ -23299,7 +23299,7 @@
         <v>13.47222222222222</v>
       </c>
       <c r="L297" t="n">
-        <v>63.00417246175244</v>
+        <v>62.95264623955432</v>
       </c>
       <c r="M297" t="n">
         <v>6</v>
@@ -23376,7 +23376,7 @@
         <v>18.36864055976641</v>
       </c>
       <c r="L298" t="n">
-        <v>62.44784422809457</v>
+        <v>62.39554317548747</v>
       </c>
       <c r="M298" t="n">
         <v>6</v>
@@ -23453,7 +23453,7 @@
         <v>7.788310922278163</v>
       </c>
       <c r="L299" t="n">
-        <v>62.30876216968011</v>
+        <v>62.25626740947076</v>
       </c>
       <c r="M299" t="n">
         <v>6</v>
@@ -23530,7 +23530,7 @@
         <v>7.004783434899409</v>
       </c>
       <c r="L300" t="n">
-        <v>62.03059805285118</v>
+        <v>61.97771587743732</v>
       </c>
       <c r="M300" t="n">
         <v>6</v>
@@ -23607,7 +23607,7 @@
         <v>6.230894631012873</v>
       </c>
       <c r="L301" t="n">
-        <v>61.05702364394993</v>
+        <v>61.00278551532033</v>
       </c>
       <c r="M301" t="n">
         <v>6</v>
@@ -23684,7 +23684,7 @@
         <v>4.502619219653181</v>
       </c>
       <c r="L302" t="n">
-        <v>60.22253129346314</v>
+        <v>60.16713091922006</v>
       </c>
       <c r="M302" t="n">
         <v>6</v>
@@ -23761,7 +23761,7 @@
         <v>24.02234636871508</v>
       </c>
       <c r="L303" t="n">
-        <v>59.24895688456188</v>
+        <v>59.19220055710307</v>
       </c>
       <c r="M303" t="n">
         <v>6</v>
@@ -23838,7 +23838,7 @@
         <v>19.07727070603009</v>
       </c>
       <c r="L304" t="n">
-        <v>57.30180806675938</v>
+        <v>57.24233983286909</v>
       </c>
       <c r="M304" t="n">
         <v>6</v>
@@ -23915,7 +23915,7 @@
         <v>32.73217150016004</v>
       </c>
       <c r="L305" t="n">
-        <v>56.74547983310153</v>
+        <v>56.68523676880223</v>
       </c>
       <c r="M305" t="n">
         <v>6</v>
@@ -23992,7 +23992,7 @@
         <v>12.33800773411493</v>
       </c>
       <c r="L306" t="n">
-        <v>56.60639777468707</v>
+        <v>56.54596100278552</v>
       </c>
       <c r="M306" t="n">
         <v>6</v>
@@ -24069,7 +24069,7 @@
         <v>26.86957572934712</v>
       </c>
       <c r="L307" t="n">
-        <v>55.91098748261474</v>
+        <v>55.84958217270195</v>
       </c>
       <c r="M307" t="n">
         <v>6</v>
@@ -24146,7 +24146,7 @@
         <v>19.85855839514428</v>
       </c>
       <c r="L308" t="n">
-        <v>54.79833101529903</v>
+        <v>54.73537604456824</v>
       </c>
       <c r="M308" t="n">
         <v>6</v>
@@ -24223,7 +24223,7 @@
         <v>29.71207865168539</v>
       </c>
       <c r="L309" t="n">
-        <v>53.26842837273992</v>
+        <v>53.2033426183844</v>
       </c>
       <c r="M309" t="n">
         <v>6</v>
@@ -24300,7 +24300,7 @@
         <v>3.121644638984411</v>
       </c>
       <c r="L310" t="n">
-        <v>52.57301808066759</v>
+        <v>52.50696378830083</v>
       </c>
       <c r="M310" t="n">
         <v>6</v>
@@ -24377,7 +24377,7 @@
         <v>10.47444663312216</v>
       </c>
       <c r="L311" t="n">
-        <v>50.76495132127955</v>
+        <v>50.69637883008357</v>
       </c>
       <c r="M311" t="n">
         <v>6</v>
@@ -24454,7 +24454,7 @@
         <v>39.8456765442241</v>
       </c>
       <c r="L312" t="n">
-        <v>50.62586926286509</v>
+        <v>50.55710306406686</v>
       </c>
       <c r="M312" t="n">
         <v>6</v>
@@ -24531,7 +24531,7 @@
         <v>13.0749014454665</v>
       </c>
       <c r="L313" t="n">
-        <v>48.81780250347705</v>
+        <v>48.74651810584958</v>
       </c>
       <c r="M313" t="n">
         <v>6</v>
@@ -24608,7 +24608,7 @@
         <v>11.32632486441696</v>
       </c>
       <c r="L314" t="n">
-        <v>48.12239221140473</v>
+        <v>48.05013927576602</v>
       </c>
       <c r="M314" t="n">
         <v>6</v>
@@ -24685,7 +24685,7 @@
         <v>24.06145214917252</v>
       </c>
       <c r="L315" t="n">
-        <v>47.56606397774687</v>
+        <v>47.49303621169916</v>
       </c>
       <c r="M315" t="n">
         <v>6</v>
@@ -24762,7 +24762,7 @@
         <v>13.4691019832776</v>
       </c>
       <c r="L316" t="n">
-        <v>47.14881780250348</v>
+        <v>47.07520891364902</v>
       </c>
       <c r="M316" t="n">
         <v>6</v>
@@ -24839,7 +24839,7 @@
         <v>16.52003928580747</v>
       </c>
       <c r="L317" t="n">
-        <v>45.75799721835883</v>
+        <v>45.68245125348189</v>
       </c>
       <c r="M317" t="n">
         <v>6</v>
@@ -24898,10 +24898,10 @@
         <v>1639.652666015625</v>
       </c>
       <c r="F318" t="n">
-        <v>1611.805001220703</v>
+        <v>1611.811500854492</v>
       </c>
       <c r="G318" t="n">
-        <v>4.61887860420529</v>
+        <v>4.618859118274066</v>
       </c>
       <c r="H318" t="n">
         <v>2136.764168606618</v>
@@ -24916,7 +24916,7 @@
         <v>26.2862983810058</v>
       </c>
       <c r="L318" t="n">
-        <v>45.47983310152991</v>
+        <v>45.40389972144847</v>
       </c>
       <c r="M318" t="n">
         <v>6</v>
@@ -24993,7 +24993,7 @@
         <v>30.35645134178779</v>
       </c>
       <c r="L319" t="n">
-        <v>45.34075104311544</v>
+        <v>45.26462395543175</v>
       </c>
       <c r="M319" t="n">
         <v>6</v>
@@ -25070,7 +25070,7 @@
         <v>24.05764293719643</v>
       </c>
       <c r="L320" t="n">
-        <v>44.92350486787204</v>
+        <v>44.84679665738162</v>
       </c>
       <c r="M320" t="n">
         <v>6</v>
@@ -25147,7 +25147,7 @@
         <v>21.02317304857171</v>
       </c>
       <c r="L321" t="n">
-        <v>43.25452016689847</v>
+        <v>43.17548746518106</v>
       </c>
       <c r="M321" t="n">
         <v>6</v>
@@ -25224,7 +25224,7 @@
         <v>29.82594650675674</v>
       </c>
       <c r="L322" t="n">
-        <v>42.97635605006954</v>
+        <v>42.89693593314763</v>
       </c>
       <c r="M322" t="n">
         <v>6</v>
@@ -25301,7 +25301,7 @@
         <v>16.5192781028874</v>
       </c>
       <c r="L323" t="n">
-        <v>42.69819193324062</v>
+        <v>42.61838440111421</v>
       </c>
       <c r="M323" t="n">
         <v>6</v>
@@ -25378,7 +25378,7 @@
         <v>32.11294639963192</v>
       </c>
       <c r="L324" t="n">
-        <v>41.58553546592489</v>
+        <v>41.5041782729805</v>
       </c>
       <c r="M324" t="n">
         <v>6</v>
@@ -25455,7 +25455,7 @@
         <v>35.22424388145684</v>
       </c>
       <c r="L325" t="n">
-        <v>41.1682892906815</v>
+        <v>41.08635097493036</v>
       </c>
       <c r="M325" t="n">
         <v>6</v>
@@ -25532,7 +25532,7 @@
         <v>40.17297954880765</v>
       </c>
       <c r="L326" t="n">
-        <v>40.19471488178025</v>
+        <v>40.11142061281337</v>
       </c>
       <c r="M326" t="n">
         <v>6</v>
@@ -25609,7 +25609,7 @@
         <v>19.95177817962628</v>
       </c>
       <c r="L327" t="n">
-        <v>38.80389429763561</v>
+        <v>38.71866295264624</v>
       </c>
       <c r="M327" t="n">
         <v>6</v>
@@ -25674,7 +25674,7 @@
         <v>4.989549523405223</v>
       </c>
       <c r="H328" t="n">
-        <v>297.5473847088064</v>
+        <v>297.5474157032224</v>
       </c>
       <c r="I328" t="n">
         <v>165</v>
@@ -25683,10 +25683,10 @@
         <v>36.94545861446497</v>
       </c>
       <c r="K328" t="n">
-        <v>31.6814373640864</v>
+        <v>31.68145108085707</v>
       </c>
       <c r="L328" t="n">
-        <v>38.52573018080668</v>
+        <v>38.44011142061282</v>
       </c>
       <c r="M328" t="n">
         <v>6</v>
@@ -25763,7 +25763,7 @@
         <v>22.12633612892303</v>
       </c>
       <c r="L329" t="n">
-        <v>34.77051460361614</v>
+        <v>34.67966573816156</v>
       </c>
       <c r="M329" t="n">
         <v>6</v>
@@ -25828,7 +25828,7 @@
         <v>0.7850969841931787</v>
       </c>
       <c r="H330" t="n">
-        <v>533.7087547028075</v>
+        <v>533.7088183031568</v>
       </c>
       <c r="I330" t="n">
         <v>363.2227809620478</v>
@@ -25837,10 +25837,10 @@
         <v>17.90284708071401</v>
       </c>
       <c r="K330" t="n">
-        <v>24.62551189791185</v>
+        <v>24.62552674913177</v>
       </c>
       <c r="L330" t="n">
-        <v>32.68428372739917</v>
+        <v>32.59052924791087</v>
       </c>
       <c r="M330" t="n">
         <v>6</v>
@@ -25917,7 +25917,7 @@
         <v>46.56781490940496</v>
       </c>
       <c r="L331" t="n">
-        <v>31.43254520166898</v>
+        <v>31.33704735376044</v>
       </c>
       <c r="M331" t="n">
         <v>6</v>
@@ -25994,7 +25994,7 @@
         <v>44.61451002646275</v>
       </c>
       <c r="L332" t="n">
-        <v>29.34631432545202</v>
+        <v>29.24791086350975</v>
       </c>
       <c r="M332" t="n">
         <v>6</v>
@@ -26071,7 +26071,7 @@
         <v>40.48768249729573</v>
       </c>
       <c r="L333" t="n">
-        <v>27.12100139082058</v>
+        <v>27.01949860724234</v>
       </c>
       <c r="M333" t="n">
         <v>6</v>
@@ -26148,7 +26148,7 @@
         <v>43.36665875644052</v>
       </c>
       <c r="L334" t="n">
-        <v>25.8692628650904</v>
+        <v>25.76601671309192</v>
       </c>
       <c r="M334" t="n">
         <v>6</v>
@@ -26225,7 +26225,7 @@
         <v>96.34420334231071</v>
       </c>
       <c r="L335" t="n">
-        <v>11.82197496522948</v>
+        <v>11.6991643454039</v>
       </c>
       <c r="M335" t="n">
         <v>6</v>
@@ -26302,7 +26302,7 @@
         <v>45.49580898938863</v>
       </c>
       <c r="L336" t="n">
-        <v>91.65507649513212</v>
+        <v>91.64345403899722</v>
       </c>
       <c r="M336" t="n">
         <v>5</v>
@@ -26379,7 +26379,7 @@
         <v>22.68339801749148</v>
       </c>
       <c r="L337" t="n">
-        <v>88.31710709318497</v>
+        <v>88.3008356545961</v>
       </c>
       <c r="M337" t="n">
         <v>5</v>
@@ -26456,7 +26456,7 @@
         <v>22.51419384958024</v>
       </c>
       <c r="L338" t="n">
-        <v>87.62169680111266</v>
+        <v>87.60445682451254</v>
       </c>
       <c r="M338" t="n">
         <v>5</v>
@@ -26533,7 +26533,7 @@
         <v>30.87917921756487</v>
       </c>
       <c r="L339" t="n">
-        <v>82.47566063977747</v>
+        <v>82.45125348189416</v>
       </c>
       <c r="M339" t="n">
         <v>5</v>
@@ -26610,7 +26610,7 @@
         <v>12.09888196226217</v>
       </c>
       <c r="L340" t="n">
-        <v>76.07788595271209</v>
+        <v>76.04456824512535</v>
       </c>
       <c r="M340" t="n">
         <v>5</v>
@@ -26687,7 +26687,7 @@
         <v>15.01028791736032</v>
       </c>
       <c r="L341" t="n">
-        <v>75.38247566063978</v>
+        <v>75.34818941504177</v>
       </c>
       <c r="M341" t="n">
         <v>5</v>
@@ -26755,16 +26755,16 @@
         <v>1093.53919041171</v>
       </c>
       <c r="I342" t="n">
-        <v>491.2850813456647</v>
+        <v>491.2850236715819</v>
       </c>
       <c r="J342" t="n">
-        <v>54.78793089423857</v>
+        <v>54.78794906546609</v>
       </c>
       <c r="K342" t="n">
         <v>43.80158759389907</v>
       </c>
       <c r="L342" t="n">
-        <v>74.96522948539638</v>
+        <v>74.93036211699165</v>
       </c>
       <c r="M342" t="n">
         <v>5</v>
@@ -26841,7 +26841,7 @@
         <v>15.71681330260637</v>
       </c>
       <c r="L343" t="n">
-        <v>72.32267037552155</v>
+        <v>72.28412256267409</v>
       </c>
       <c r="M343" t="n">
         <v>5</v>
@@ -26918,7 +26918,7 @@
         <v>22.55048583693513</v>
       </c>
       <c r="L344" t="n">
-        <v>70.37552155771905</v>
+        <v>70.33426183844011</v>
       </c>
       <c r="M344" t="n">
         <v>5</v>
@@ -26995,7 +26995,7 @@
         <v>25.32946381633856</v>
       </c>
       <c r="L345" t="n">
-        <v>68.70653685674549</v>
+        <v>68.66295264623955</v>
       </c>
       <c r="M345" t="n">
         <v>5</v>
@@ -27072,7 +27072,7 @@
         <v>10.7655316289583</v>
       </c>
       <c r="L346" t="n">
-        <v>68.01112656467315</v>
+        <v>67.96657381615599</v>
       </c>
       <c r="M346" t="n">
         <v>5</v>
@@ -27149,7 +27149,7 @@
         <v>17.40349684519131</v>
       </c>
       <c r="L347" t="n">
-        <v>66.89847009735745</v>
+        <v>66.85236768802228</v>
       </c>
       <c r="M347" t="n">
         <v>5</v>
@@ -27226,7 +27226,7 @@
         <v>25.63490523767051</v>
       </c>
       <c r="L348" t="n">
-        <v>60.50069541029207</v>
+        <v>60.44568245125348</v>
       </c>
       <c r="M348" t="n">
         <v>5</v>
@@ -27303,7 +27303,7 @@
         <v>22.6445849727285</v>
       </c>
       <c r="L349" t="n">
-        <v>60.36161335187761</v>
+        <v>60.30640668523677</v>
       </c>
       <c r="M349" t="n">
         <v>5</v>
@@ -27380,7 +27380,7 @@
         <v>11.91975434913941</v>
       </c>
       <c r="L350" t="n">
-        <v>58.8317107093185</v>
+        <v>58.77437325905292</v>
       </c>
       <c r="M350" t="n">
         <v>5</v>
@@ -27457,7 +27457,7 @@
         <v>21.62886597938145</v>
       </c>
       <c r="L351" t="n">
-        <v>58.41446453407511</v>
+        <v>58.35654596100278</v>
       </c>
       <c r="M351" t="n">
         <v>5</v>
@@ -27534,7 +27534,7 @@
         <v>20.90961976414705</v>
       </c>
       <c r="L352" t="n">
-        <v>54.5201668984701</v>
+        <v>54.45682451253482</v>
       </c>
       <c r="M352" t="n">
         <v>5</v>
@@ -27611,7 +27611,7 @@
         <v>30.54830547259668</v>
       </c>
       <c r="L353" t="n">
-        <v>54.38108484005564</v>
+        <v>54.31754874651811</v>
       </c>
       <c r="M353" t="n">
         <v>5</v>
@@ -27688,7 +27688,7 @@
         <v>20.15261256956517</v>
       </c>
       <c r="L354" t="n">
-        <v>54.24200278164116</v>
+        <v>54.1782729805014</v>
       </c>
       <c r="M354" t="n">
         <v>5</v>
@@ -27765,7 +27765,7 @@
         <v>4.336907539370261</v>
       </c>
       <c r="L355" t="n">
-        <v>53.96383866481224</v>
+        <v>53.89972144846796</v>
       </c>
       <c r="M355" t="n">
         <v>5</v>
@@ -27842,7 +27842,7 @@
         <v>21.96450977516207</v>
       </c>
       <c r="L356" t="n">
-        <v>53.68567454798331</v>
+        <v>53.62116991643454</v>
       </c>
       <c r="M356" t="n">
         <v>5</v>
@@ -27919,7 +27919,7 @@
         <v>18.69435695965884</v>
       </c>
       <c r="L357" t="n">
-        <v>50.34770514603616</v>
+        <v>50.27855153203342</v>
       </c>
       <c r="M357" t="n">
         <v>5</v>
@@ -27996,7 +27996,7 @@
         <v>19.15977047287662</v>
       </c>
       <c r="L358" t="n">
-        <v>47.70514603616133</v>
+        <v>47.63231197771588</v>
       </c>
       <c r="M358" t="n">
         <v>5</v>
@@ -28061,7 +28061,7 @@
         <v>2.187140415571798</v>
       </c>
       <c r="H359" t="n">
-        <v>561.4378970396333</v>
+        <v>561.4379586860567</v>
       </c>
       <c r="I359" t="n">
         <v>420.1655789001589</v>
@@ -28070,10 +28070,10 @@
         <v>20.90471602403978</v>
       </c>
       <c r="K359" t="n">
-        <v>10.51927107079396</v>
+        <v>10.51928320591669</v>
       </c>
       <c r="L359" t="n">
-        <v>47.28789986091794</v>
+        <v>47.21448467966574</v>
       </c>
       <c r="M359" t="n">
         <v>5</v>
@@ -28150,7 +28150,7 @@
         <v>16.37918945449446</v>
       </c>
       <c r="L360" t="n">
-        <v>46.45340751043116</v>
+        <v>46.37883008356546</v>
       </c>
       <c r="M360" t="n">
         <v>5</v>
@@ -28227,7 +28227,7 @@
         <v>15.16610518191275</v>
       </c>
       <c r="L361" t="n">
-        <v>45.8970792767733</v>
+        <v>45.82172701949861</v>
       </c>
       <c r="M361" t="n">
         <v>5</v>
@@ -28304,7 +28304,7 @@
         <v>29.82900601346316</v>
       </c>
       <c r="L362" t="n">
-        <v>44.78442280945758</v>
+        <v>44.70752089136491</v>
       </c>
       <c r="M362" t="n">
         <v>5</v>
@@ -28381,7 +28381,7 @@
         <v>31.37141141121398</v>
       </c>
       <c r="L363" t="n">
-        <v>44.64534075104311</v>
+        <v>44.56824512534819</v>
       </c>
       <c r="M363" t="n">
         <v>5</v>
@@ -28458,7 +28458,7 @@
         <v>10.20703407302013</v>
       </c>
       <c r="L364" t="n">
-        <v>43.94993045897079</v>
+        <v>43.87186629526462</v>
       </c>
       <c r="M364" t="n">
         <v>5</v>
@@ -28535,7 +28535,7 @@
         <v>27.62327779526135</v>
       </c>
       <c r="L365" t="n">
-        <v>43.67176634214186</v>
+        <v>43.5933147632312</v>
       </c>
       <c r="M365" t="n">
         <v>5</v>
@@ -28612,7 +28612,7 @@
         <v>20.73063502602604</v>
       </c>
       <c r="L366" t="n">
-        <v>43.5326842837274</v>
+        <v>43.45403899721448</v>
       </c>
       <c r="M366" t="n">
         <v>5</v>
@@ -28689,7 +28689,7 @@
         <v>30.30769767342032</v>
       </c>
       <c r="L367" t="n">
-        <v>39.77746870653686</v>
+        <v>39.69359331476323</v>
       </c>
       <c r="M367" t="n">
         <v>5</v>
@@ -28766,7 +28766,7 @@
         <v>32.18207153456751</v>
       </c>
       <c r="L368" t="n">
-        <v>38.66481223922114</v>
+        <v>38.57938718662952</v>
       </c>
       <c r="M368" t="n">
         <v>5</v>
@@ -28843,7 +28843,7 @@
         <v>54.69097988518266</v>
       </c>
       <c r="L369" t="n">
-        <v>37.96940194714882</v>
+        <v>37.88300835654596</v>
       </c>
       <c r="M369" t="n">
         <v>5</v>
@@ -28920,7 +28920,7 @@
         <v>20.89932751663768</v>
       </c>
       <c r="L370" t="n">
-        <v>37.13490959666203</v>
+        <v>37.04735376044568</v>
       </c>
       <c r="M370" t="n">
         <v>5</v>
@@ -28997,7 +28997,7 @@
         <v>31.46072910098452</v>
       </c>
       <c r="L371" t="n">
-        <v>35.32684283727399</v>
+        <v>35.23676880222841</v>
       </c>
       <c r="M371" t="n">
         <v>5</v>
@@ -29074,7 +29074,7 @@
         <v>21.59381130598323</v>
       </c>
       <c r="L372" t="n">
-        <v>33.10152990264255</v>
+        <v>33.00835654596101</v>
       </c>
       <c r="M372" t="n">
         <v>5</v>
@@ -29151,7 +29151,7 @@
         <v>39.31653307252141</v>
       </c>
       <c r="L373" t="n">
-        <v>32.1279554937413</v>
+        <v>32.03342618384401</v>
       </c>
       <c r="M373" t="n">
         <v>5</v>
@@ -29228,7 +29228,7 @@
         <v>44.51976308919286</v>
       </c>
       <c r="L374" t="n">
-        <v>31.57162726008345</v>
+        <v>31.47632311977716</v>
       </c>
       <c r="M374" t="n">
         <v>5</v>
@@ -29305,7 +29305,7 @@
         <v>54.88311315169474</v>
       </c>
       <c r="L375" t="n">
-        <v>29.90264255910988</v>
+        <v>29.8050139275766</v>
       </c>
       <c r="M375" t="n">
         <v>5</v>
@@ -29382,7 +29382,7 @@
         <v>42.19613487450833</v>
       </c>
       <c r="L376" t="n">
-        <v>27.67732962447844</v>
+        <v>27.57660167130919</v>
       </c>
       <c r="M376" t="n">
         <v>5</v>
@@ -29459,7 +29459,7 @@
         <v>49.97518250236843</v>
       </c>
       <c r="L377" t="n">
-        <v>19.05424200278164</v>
+        <v>18.94150417827298</v>
       </c>
       <c r="M377" t="n">
         <v>5</v>
@@ -29536,7 +29536,7 @@
         <v>44.6584956062654</v>
       </c>
       <c r="L378" t="n">
-        <v>16.55076495132128</v>
+        <v>16.43454038997215</v>
       </c>
       <c r="M378" t="n">
         <v>5</v>
@@ -29613,7 +29613,7 @@
         <v>26.91543920156176</v>
       </c>
       <c r="L379" t="n">
-        <v>90.26425591098747</v>
+        <v>90.25069637883009</v>
       </c>
       <c r="M379" t="n">
         <v>4</v>
@@ -29690,7 +29690,7 @@
         <v>18.51726796559461</v>
       </c>
       <c r="L380" t="n">
-        <v>87.0653685674548</v>
+        <v>87.04735376044567</v>
       </c>
       <c r="M380" t="n">
         <v>4</v>
@@ -29767,7 +29767,7 @@
         <v>25.60856615821536</v>
       </c>
       <c r="L381" t="n">
-        <v>85.67454798331016</v>
+        <v>85.65459610027855</v>
       </c>
       <c r="M381" t="n">
         <v>4</v>
@@ -29844,7 +29844,7 @@
         <v>34.48206522750719</v>
       </c>
       <c r="L382" t="n">
-        <v>82.19749652294854</v>
+        <v>82.17270194986072</v>
       </c>
       <c r="M382" t="n">
         <v>4</v>
@@ -29921,7 +29921,7 @@
         <v>54.12163761464548</v>
       </c>
       <c r="L383" t="n">
-        <v>81.78025034770513</v>
+        <v>81.75487465181058</v>
       </c>
       <c r="M383" t="n">
         <v>4</v>
@@ -29998,7 +29998,7 @@
         <v>44.64464243533324</v>
       </c>
       <c r="L384" t="n">
-        <v>81.22392211404728</v>
+        <v>81.19777158774373</v>
       </c>
       <c r="M384" t="n">
         <v>4</v>
@@ -30075,7 +30075,7 @@
         <v>31.90530329811769</v>
       </c>
       <c r="L385" t="n">
-        <v>80.66759388038943</v>
+        <v>80.64066852367688</v>
       </c>
       <c r="M385" t="n">
         <v>4</v>
@@ -30152,7 +30152,7 @@
         <v>25.37462067024694</v>
       </c>
       <c r="L386" t="n">
-        <v>79.83310152990263</v>
+        <v>79.80501392757661</v>
       </c>
       <c r="M386" t="n">
         <v>4</v>
@@ -30229,7 +30229,7 @@
         <v>30.0696621533957</v>
       </c>
       <c r="L387" t="n">
-        <v>78.16411682892907</v>
+        <v>78.13370473537604</v>
       </c>
       <c r="M387" t="n">
         <v>4</v>
@@ -30306,7 +30306,7 @@
         <v>29.17737973460191</v>
       </c>
       <c r="L388" t="n">
-        <v>66.75938803894297</v>
+        <v>66.71309192200557</v>
       </c>
       <c r="M388" t="n">
         <v>4</v>
@@ -30383,7 +30383,7 @@
         <v>13.91237509607994</v>
       </c>
       <c r="L389" t="n">
-        <v>66.34214186369958</v>
+        <v>66.29526462395543</v>
       </c>
       <c r="M389" t="n">
         <v>4</v>
@@ -30460,7 +30460,7 @@
         <v>20.15533370613114</v>
       </c>
       <c r="L390" t="n">
-        <v>65.09040333796941</v>
+        <v>65.04178272980501</v>
       </c>
       <c r="M390" t="n">
         <v>4</v>
@@ -30537,7 +30537,7 @@
         <v>19.7459584295612</v>
       </c>
       <c r="L391" t="n">
-        <v>63.28233657858136</v>
+        <v>63.23119777158774</v>
       </c>
       <c r="M391" t="n">
         <v>4</v>
@@ -30614,7 +30614,7 @@
         <v>10.10280042538108</v>
       </c>
       <c r="L392" t="n">
-        <v>62.86509040333797</v>
+        <v>62.8133704735376</v>
       </c>
       <c r="M392" t="n">
         <v>4</v>
@@ -30691,7 +30691,7 @@
         <v>11.98235155527738</v>
       </c>
       <c r="L393" t="n">
-        <v>61.61335187760779</v>
+        <v>61.55988857938719</v>
       </c>
       <c r="M393" t="n">
         <v>4</v>
@@ -30768,7 +30768,7 @@
         <v>19.36211656766149</v>
       </c>
       <c r="L394" t="n">
-        <v>61.47426981919332</v>
+        <v>61.42061281337048</v>
       </c>
       <c r="M394" t="n">
         <v>4</v>
@@ -30845,7 +30845,7 @@
         <v>13.17365269461077</v>
       </c>
       <c r="L395" t="n">
-        <v>57.85813630041725</v>
+        <v>57.79944289693594</v>
       </c>
       <c r="M395" t="n">
         <v>4</v>
@@ -30922,7 +30922,7 @@
         <v>13.96822230439272</v>
       </c>
       <c r="L396" t="n">
-        <v>57.71905424200278</v>
+        <v>57.66016713091921</v>
       </c>
       <c r="M396" t="n">
         <v>4</v>
@@ -30999,7 +30999,7 @@
         <v>22.00442895656123</v>
       </c>
       <c r="L397" t="n">
-        <v>57.57997218358831</v>
+        <v>57.5208913649025</v>
       </c>
       <c r="M397" t="n">
         <v>4</v>
@@ -31076,7 +31076,7 @@
         <v>9.071943686075578</v>
       </c>
       <c r="L398" t="n">
-        <v>56.4673157162726</v>
+        <v>56.40668523676881</v>
       </c>
       <c r="M398" t="n">
         <v>4</v>
@@ -31153,7 +31153,7 @@
         <v>14.57778082953558</v>
       </c>
       <c r="L399" t="n">
-        <v>55.21557719054242</v>
+        <v>55.15320334261838</v>
       </c>
       <c r="M399" t="n">
         <v>4</v>
@@ -31230,7 +31230,7 @@
         <v>22.57631147621142</v>
       </c>
       <c r="L400" t="n">
-        <v>54.93741307371349</v>
+        <v>54.87465181058496</v>
       </c>
       <c r="M400" t="n">
         <v>4</v>
@@ -31307,7 +31307,7 @@
         <v>22</v>
       </c>
       <c r="L401" t="n">
-        <v>54.65924895688457</v>
+        <v>54.59610027855153</v>
       </c>
       <c r="M401" t="n">
         <v>4</v>
@@ -31384,7 +31384,7 @@
         <v>12.28897100043183</v>
       </c>
       <c r="L402" t="n">
-        <v>51.7385257301808</v>
+        <v>51.67130919220055</v>
       </c>
       <c r="M402" t="n">
         <v>4</v>
@@ -31461,7 +31461,7 @@
         <v>16.46808428876692</v>
       </c>
       <c r="L403" t="n">
-        <v>50.48678720445062</v>
+        <v>50.41782729805014</v>
       </c>
       <c r="M403" t="n">
         <v>4</v>
@@ -31538,7 +31538,7 @@
         <v>15.12865333079141</v>
       </c>
       <c r="L404" t="n">
-        <v>49.93045897079277</v>
+        <v>49.86072423398329</v>
       </c>
       <c r="M404" t="n">
         <v>4</v>
@@ -31615,7 +31615,7 @@
         <v>14.13335187810614</v>
       </c>
       <c r="L405" t="n">
-        <v>47.42698191933241</v>
+        <v>47.35376044568245</v>
       </c>
       <c r="M405" t="n">
         <v>4</v>
@@ -31692,7 +31692,7 @@
         <v>20.06957452502007</v>
       </c>
       <c r="L406" t="n">
-        <v>45.61891515994436</v>
+        <v>45.54317548746518</v>
       </c>
       <c r="M406" t="n">
         <v>4</v>
@@ -31769,7 +31769,7 @@
         <v>16.71051391840523</v>
       </c>
       <c r="L407" t="n">
-        <v>39.91655076495132</v>
+        <v>39.83286908077994</v>
       </c>
       <c r="M407" t="n">
         <v>4</v>
@@ -31834,7 +31834,7 @@
         <v>1.497014507617345</v>
       </c>
       <c r="H408" t="n">
-        <v>3039.742428602358</v>
+        <v>3039.742679715149</v>
       </c>
       <c r="I408" t="n">
         <v>2053.692522278021</v>
@@ -31843,10 +31843,10 @@
         <v>20.51463269947789</v>
       </c>
       <c r="K408" t="n">
-        <v>22.81787590312558</v>
+        <v>22.81788604909691</v>
       </c>
       <c r="L408" t="n">
-        <v>39.36022253129347</v>
+        <v>39.27576601671309</v>
       </c>
       <c r="M408" t="n">
         <v>4</v>
@@ -31923,7 +31923,7 @@
         <v>29.05247808480673</v>
       </c>
       <c r="L409" t="n">
-        <v>37.69123783031989</v>
+        <v>37.60445682451253</v>
       </c>
       <c r="M409" t="n">
         <v>4</v>
@@ -32000,7 +32000,7 @@
         <v>43.92874936507387</v>
       </c>
       <c r="L410" t="n">
-        <v>36.30041724617524</v>
+        <v>36.2116991643454</v>
       </c>
       <c r="M410" t="n">
         <v>4</v>
@@ -32077,7 +32077,7 @@
         <v>33.67933107764605</v>
       </c>
       <c r="L411" t="n">
-        <v>35.04867872044507</v>
+        <v>34.95821727019499</v>
       </c>
       <c r="M411" t="n">
         <v>4</v>
@@ -32154,7 +32154,7 @@
         <v>21.36021259164547</v>
       </c>
       <c r="L412" t="n">
-        <v>34.63143254520167</v>
+        <v>34.54038997214484</v>
       </c>
       <c r="M412" t="n">
         <v>4</v>
@@ -32231,7 +32231,7 @@
         <v>19.87363742682027</v>
       </c>
       <c r="L413" t="n">
-        <v>34.4923504867872</v>
+        <v>34.40111420612813</v>
       </c>
       <c r="M413" t="n">
         <v>4</v>
@@ -32308,7 +32308,7 @@
         <v>19.67151811056789</v>
       </c>
       <c r="L414" t="n">
-        <v>32.96244784422809</v>
+        <v>32.86908077994429</v>
       </c>
       <c r="M414" t="n">
         <v>4</v>
@@ -32385,7 +32385,7 @@
         <v>34.2873448477826</v>
       </c>
       <c r="L415" t="n">
-        <v>31.98887343532684</v>
+        <v>31.8941504178273</v>
       </c>
       <c r="M415" t="n">
         <v>4</v>
@@ -32462,7 +32462,7 @@
         <v>44.21976745312703</v>
       </c>
       <c r="L416" t="n">
-        <v>31.29346314325452</v>
+        <v>31.19777158774373</v>
       </c>
       <c r="M416" t="n">
         <v>4</v>
@@ -32539,7 +32539,7 @@
         <v>33.77903878577256</v>
       </c>
       <c r="L417" t="n">
-        <v>29.48539638386648</v>
+        <v>29.38718662952646</v>
       </c>
       <c r="M417" t="n">
         <v>4</v>
@@ -32616,7 +32616,7 @@
         <v>22.79321955849236</v>
       </c>
       <c r="L418" t="n">
-        <v>26.70375521557719</v>
+        <v>26.6016713091922</v>
       </c>
       <c r="M418" t="n">
         <v>4</v>
@@ -32693,7 +32693,7 @@
         <v>38.17426850608938</v>
       </c>
       <c r="L419" t="n">
-        <v>24.06119610570236</v>
+        <v>23.95543175487465</v>
       </c>
       <c r="M419" t="n">
         <v>4</v>
@@ -32770,7 +32770,7 @@
         <v>46.08903959557138</v>
       </c>
       <c r="L420" t="n">
-        <v>22.67037552155772</v>
+        <v>22.56267409470752</v>
       </c>
       <c r="M420" t="n">
         <v>4</v>
@@ -32847,7 +32847,7 @@
         <v>37.94413890797632</v>
       </c>
       <c r="L421" t="n">
-        <v>21.83588317107093</v>
+        <v>21.72701949860724</v>
       </c>
       <c r="M421" t="n">
         <v>4</v>
@@ -32924,7 +32924,7 @@
         <v>52.57432922407541</v>
       </c>
       <c r="L422" t="n">
-        <v>17.94158553546593</v>
+        <v>17.82729805013928</v>
       </c>
       <c r="M422" t="n">
         <v>4</v>
@@ -33001,7 +33001,7 @@
         <v>71.67692485391962</v>
       </c>
       <c r="L423" t="n">
-        <v>11.68289290681502</v>
+        <v>11.55988857938719</v>
       </c>
       <c r="M423" t="n">
         <v>4</v>
@@ -33078,7 +33078,7 @@
         <v>114.1467481934408</v>
       </c>
       <c r="L424" t="n">
-        <v>10.70931849791377</v>
+        <v>10.5849582172702</v>
       </c>
       <c r="M424" t="n">
         <v>4</v>
@@ -33155,7 +33155,7 @@
         <v>83.50694400752768</v>
       </c>
       <c r="L425" t="n">
-        <v>10.5702364394993</v>
+        <v>10.44568245125348</v>
       </c>
       <c r="M425" t="n">
         <v>4</v>
@@ -33232,7 +33232,7 @@
         <v>104.9118561912833</v>
       </c>
       <c r="L426" t="n">
-        <v>7.232267037552156</v>
+        <v>7.103064066852367</v>
       </c>
       <c r="M426" t="n">
         <v>4</v>
@@ -33309,7 +33309,7 @@
         <v>29.31732190780603</v>
       </c>
       <c r="L427" t="n">
-        <v>75.93880389429764</v>
+        <v>75.90529247910864</v>
       </c>
       <c r="M427" t="n">
         <v>3</v>
@@ -33386,7 +33386,7 @@
         <v>29.71956910760984</v>
       </c>
       <c r="L428" t="n">
-        <v>69.68011126564673</v>
+        <v>69.63788300835655</v>
       </c>
       <c r="M428" t="n">
         <v>3</v>
@@ -33463,7 +33463,7 @@
         <v>44.49999636700077</v>
       </c>
       <c r="L429" t="n">
-        <v>58.97079276773296</v>
+        <v>58.91364902506964</v>
       </c>
       <c r="M429" t="n">
         <v>3</v>
@@ -33540,7 +33540,7 @@
         <v>35.80363490359915</v>
       </c>
       <c r="L430" t="n">
-        <v>58.13630041724618</v>
+        <v>58.07799442896936</v>
       </c>
       <c r="M430" t="n">
         <v>3</v>
@@ -33617,7 +33617,7 @@
         <v>11.32812450042291</v>
       </c>
       <c r="L431" t="n">
-        <v>56.32823365785814</v>
+        <v>56.26740947075209</v>
       </c>
       <c r="M431" t="n">
         <v>3</v>
@@ -33694,7 +33694,7 @@
         <v>31.49817494227061</v>
       </c>
       <c r="L432" t="n">
-        <v>53.82475660639777</v>
+        <v>53.76044568245126</v>
       </c>
       <c r="M432" t="n">
         <v>3</v>
@@ -33771,7 +33771,7 @@
         <v>59.33751586225575</v>
       </c>
       <c r="L433" t="n">
-        <v>53.54659248956884</v>
+        <v>53.48189415041783</v>
       </c>
       <c r="M433" t="n">
         <v>3</v>
@@ -33848,7 +33848,7 @@
         <v>26.43964124335929</v>
       </c>
       <c r="L434" t="n">
-        <v>52.85118219749653</v>
+        <v>52.78551532033426</v>
       </c>
       <c r="M434" t="n">
         <v>3</v>
@@ -33925,7 +33925,7 @@
         <v>26.27877730655046</v>
       </c>
       <c r="L435" t="n">
-        <v>52.01668984700974</v>
+        <v>51.94986072423399</v>
       </c>
       <c r="M435" t="n">
         <v>3</v>
@@ -34002,7 +34002,7 @@
         <v>10.92183109597984</v>
       </c>
       <c r="L436" t="n">
-        <v>51.87760778859527</v>
+        <v>51.81058495821726</v>
       </c>
       <c r="M436" t="n">
         <v>3</v>
@@ -34079,7 +34079,7 @@
         <v>37.95556448884663</v>
       </c>
       <c r="L437" t="n">
-        <v>51.32127955493742</v>
+        <v>51.25348189415042</v>
       </c>
       <c r="M437" t="n">
         <v>3</v>
@@ -34156,7 +34156,7 @@
         <v>14.43546778436049</v>
       </c>
       <c r="L438" t="n">
-        <v>51.04311543810849</v>
+        <v>50.97493036211699</v>
       </c>
       <c r="M438" t="n">
         <v>3</v>
@@ -34233,7 +34233,7 @@
         <v>39.8437758735602</v>
       </c>
       <c r="L439" t="n">
-        <v>50.90403337969403</v>
+        <v>50.83565459610028</v>
       </c>
       <c r="M439" t="n">
         <v>3</v>
@@ -34310,7 +34310,7 @@
         <v>12.51887286464301</v>
       </c>
       <c r="L440" t="n">
-        <v>50.06954102920723</v>
+        <v>50</v>
       </c>
       <c r="M440" t="n">
         <v>3</v>
@@ -34387,7 +34387,7 @@
         <v>18.66598564499429</v>
       </c>
       <c r="L441" t="n">
-        <v>49.7913769123783</v>
+        <v>49.72144846796657</v>
       </c>
       <c r="M441" t="n">
         <v>3</v>
@@ -34464,7 +34464,7 @@
         <v>11.89590291056504</v>
       </c>
       <c r="L442" t="n">
-        <v>48.53963838664812</v>
+        <v>48.46796657381616</v>
       </c>
       <c r="M442" t="n">
         <v>3</v>
@@ -34541,7 +34541,7 @@
         <v>12.05723714626292</v>
       </c>
       <c r="L443" t="n">
-        <v>46.87065368567455</v>
+        <v>46.7966573816156</v>
       </c>
       <c r="M443" t="n">
         <v>3</v>
@@ -34618,7 +34618,7 @@
         <v>28.70284909057332</v>
       </c>
       <c r="L444" t="n">
-        <v>46.17524339360223</v>
+        <v>46.10027855153203</v>
       </c>
       <c r="M444" t="n">
         <v>3</v>
@@ -34695,7 +34695,7 @@
         <v>18.28805927674355</v>
       </c>
       <c r="L445" t="n">
-        <v>44.50625869262866</v>
+        <v>44.42896935933148</v>
       </c>
       <c r="M445" t="n">
         <v>3</v>
@@ -34772,7 +34772,7 @@
         <v>14.09312299277212</v>
       </c>
       <c r="L446" t="n">
-        <v>44.36717663421418</v>
+        <v>44.28969359331476</v>
       </c>
       <c r="M446" t="n">
         <v>3</v>
@@ -34849,7 +34849,7 @@
         <v>12.61231651029055</v>
       </c>
       <c r="L447" t="n">
-        <v>43.81084840055633</v>
+        <v>43.73259052924791</v>
       </c>
       <c r="M447" t="n">
         <v>3</v>
@@ -34926,7 +34926,7 @@
         <v>30.71390427740537</v>
       </c>
       <c r="L448" t="n">
-        <v>42.42002781641168</v>
+        <v>42.33983286908078</v>
       </c>
       <c r="M448" t="n">
         <v>3</v>
@@ -35003,7 +35003,7 @@
         <v>31.80794542612728</v>
       </c>
       <c r="L449" t="n">
-        <v>41.86369958275382</v>
+        <v>41.78272980501393</v>
       </c>
       <c r="M449" t="n">
         <v>3</v>
@@ -35080,7 +35080,7 @@
         <v>39.47924745092555</v>
       </c>
       <c r="L450" t="n">
-        <v>41.02920723226704</v>
+        <v>40.94707520891365</v>
       </c>
       <c r="M450" t="n">
         <v>3</v>
@@ -35157,7 +35157,7 @@
         <v>16.43056854776464</v>
       </c>
       <c r="L451" t="n">
-        <v>40.75104311543811</v>
+        <v>40.66852367688023</v>
       </c>
       <c r="M451" t="n">
         <v>3</v>
@@ -35234,7 +35234,7 @@
         <v>12.62058891585924</v>
       </c>
       <c r="L452" t="n">
-        <v>40.61196105702364</v>
+        <v>40.52924791086351</v>
       </c>
       <c r="M452" t="n">
         <v>3</v>
@@ -35311,7 +35311,7 @@
         <v>17.12177894050613</v>
       </c>
       <c r="L453" t="n">
-        <v>40.33379694019472</v>
+        <v>40.25069637883008</v>
       </c>
       <c r="M453" t="n">
         <v>3</v>
@@ -35388,7 +35388,7 @@
         <v>14.86748194403864</v>
       </c>
       <c r="L454" t="n">
-        <v>40.05563282336578</v>
+        <v>39.97214484679666</v>
       </c>
       <c r="M454" t="n">
         <v>3</v>
@@ -35465,7 +35465,7 @@
         <v>21.89279918279057</v>
       </c>
       <c r="L455" t="n">
-        <v>38.24756606397774</v>
+        <v>38.16155988857939</v>
       </c>
       <c r="M455" t="n">
         <v>3</v>
@@ -35530,7 +35530,7 @@
         <v>1.894306887326658</v>
       </c>
       <c r="H456" t="n">
-        <v>796.6710965617623</v>
+        <v>796.6711586352184</v>
       </c>
       <c r="I456" t="n">
         <v>553.7186859929476</v>
@@ -35539,10 +35539,10 @@
         <v>23.29365605258378</v>
       </c>
       <c r="K456" t="n">
-        <v>16.69416761635694</v>
+        <v>16.69417670870423</v>
       </c>
       <c r="L456" t="n">
-        <v>37.27399165507649</v>
+        <v>37.1866295264624</v>
       </c>
       <c r="M456" t="n">
         <v>3</v>
@@ -35619,7 +35619,7 @@
         <v>19.34684866865111</v>
       </c>
       <c r="L457" t="n">
-        <v>36.99582753824757</v>
+        <v>36.90807799442896</v>
       </c>
       <c r="M457" t="n">
         <v>3</v>
@@ -35696,7 +35696,7 @@
         <v>44.46002628388293</v>
       </c>
       <c r="L458" t="n">
-        <v>36.8567454798331</v>
+        <v>36.76880222841226</v>
       </c>
       <c r="M458" t="n">
         <v>3</v>
@@ -35773,7 +35773,7 @@
         <v>27.37953438431908</v>
       </c>
       <c r="L459" t="n">
-        <v>36.57858136300417</v>
+        <v>36.49025069637883</v>
       </c>
       <c r="M459" t="n">
         <v>3</v>
@@ -35850,7 +35850,7 @@
         <v>26.08886942646402</v>
       </c>
       <c r="L460" t="n">
-        <v>36.43949930458971</v>
+        <v>36.35097493036212</v>
       </c>
       <c r="M460" t="n">
         <v>3</v>
@@ -35915,7 +35915,7 @@
         <v>1.937363239293077</v>
       </c>
       <c r="H461" t="n">
-        <v>1341.921323996723</v>
+        <v>1341.921447537333</v>
       </c>
       <c r="I461" t="n">
         <v>885.652283987356</v>
@@ -35924,10 +35924,10 @@
         <v>23.81834218829759</v>
       </c>
       <c r="K461" t="n">
-        <v>22.37108826121443</v>
+        <v>22.37109952700069</v>
       </c>
       <c r="L461" t="n">
-        <v>35.18776077885953</v>
+        <v>35.0974930362117</v>
       </c>
       <c r="M461" t="n">
         <v>3</v>
@@ -36004,7 +36004,7 @@
         <v>19.08453166177884</v>
       </c>
       <c r="L462" t="n">
-        <v>32.5452016689847</v>
+        <v>32.45125348189415</v>
       </c>
       <c r="M462" t="n">
         <v>3</v>
@@ -36069,19 +36069,19 @@
         <v>1.119664698217915</v>
       </c>
       <c r="H463" t="n">
-        <v>45150.85152546577</v>
+        <v>45150.8475731383</v>
       </c>
       <c r="I463" t="n">
-        <v>29525.27356749276</v>
+        <v>29525.27549507192</v>
       </c>
       <c r="J463" t="n">
-        <v>22.94551621010616</v>
+        <v>22.94550818351841</v>
       </c>
       <c r="K463" t="n">
-        <v>24.38251108943739</v>
+        <v>24.38250020148292</v>
       </c>
       <c r="L463" t="n">
-        <v>32.40611961057024</v>
+        <v>32.31197771587744</v>
       </c>
       <c r="M463" t="n">
         <v>3</v>
@@ -36158,7 +36158,7 @@
         <v>86.46951506720598</v>
       </c>
       <c r="L464" t="n">
-        <v>30.45897079276773</v>
+        <v>30.36211699164346</v>
       </c>
       <c r="M464" t="n">
         <v>3</v>
@@ -36235,7 +36235,7 @@
         <v>24.59016449361571</v>
       </c>
       <c r="L465" t="n">
-        <v>30.04172461752434</v>
+        <v>29.94428969359331</v>
       </c>
       <c r="M465" t="n">
         <v>3</v>
@@ -36312,7 +36312,7 @@
         <v>40.95397809762729</v>
       </c>
       <c r="L466" t="n">
-        <v>28.92906815020863</v>
+        <v>28.83008356545961</v>
       </c>
       <c r="M466" t="n">
         <v>3</v>
@@ -36389,7 +36389,7 @@
         <v>46.66823239459561</v>
       </c>
       <c r="L467" t="n">
-        <v>28.37273991655077</v>
+        <v>28.27298050139276</v>
       </c>
       <c r="M467" t="n">
         <v>3</v>
@@ -36466,7 +36466,7 @@
         <v>37.051747259438</v>
       </c>
       <c r="L468" t="n">
-        <v>26.98191933240612</v>
+        <v>26.88022284122563</v>
       </c>
       <c r="M468" t="n">
         <v>3</v>
@@ -36543,7 +36543,7 @@
         <v>33.08567255174329</v>
       </c>
       <c r="L469" t="n">
-        <v>26.84283727399166</v>
+        <v>26.74094707520891</v>
       </c>
       <c r="M469" t="n">
         <v>3</v>
@@ -36620,7 +36620,7 @@
         <v>39.26086321671161</v>
       </c>
       <c r="L470" t="n">
-        <v>26.28650904033379</v>
+        <v>26.18384401114206</v>
       </c>
       <c r="M470" t="n">
         <v>3</v>
@@ -36697,7 +36697,7 @@
         <v>28.8171143063024</v>
       </c>
       <c r="L471" t="n">
-        <v>25.73018080667594</v>
+        <v>25.62674094707521</v>
       </c>
       <c r="M471" t="n">
         <v>3</v>
@@ -36774,7 +36774,7 @@
         <v>32.26360141003739</v>
       </c>
       <c r="L472" t="n">
-        <v>25.03477051460361</v>
+        <v>24.93036211699165</v>
       </c>
       <c r="M472" t="n">
         <v>3</v>
@@ -36851,7 +36851,7 @@
         <v>82.90259189097964</v>
       </c>
       <c r="L473" t="n">
-        <v>24.47844228094576</v>
+        <v>24.37325905292479</v>
       </c>
       <c r="M473" t="n">
         <v>3</v>
@@ -36928,7 +36928,7 @@
         <v>23.85584762868787</v>
       </c>
       <c r="L474" t="n">
-        <v>24.33936022253129</v>
+        <v>24.23398328690808</v>
       </c>
       <c r="M474" t="n">
         <v>3</v>
@@ -37005,7 +37005,7 @@
         <v>38.52356731226734</v>
       </c>
       <c r="L475" t="n">
-        <v>23.9221140472879</v>
+        <v>23.81615598885794</v>
       </c>
       <c r="M475" t="n">
         <v>3</v>
@@ -37082,7 +37082,7 @@
         <v>45.9536648277528</v>
       </c>
       <c r="L476" t="n">
-        <v>23.64394993045897</v>
+        <v>23.53760445682451</v>
       </c>
       <c r="M476" t="n">
         <v>3</v>
@@ -37159,7 +37159,7 @@
         <v>35.47570531674555</v>
       </c>
       <c r="L477" t="n">
-        <v>22.80945757997218</v>
+        <v>22.70194986072423</v>
       </c>
       <c r="M477" t="n">
         <v>3</v>
@@ -37236,7 +37236,7 @@
         <v>46.70446978951366</v>
       </c>
       <c r="L478" t="n">
-        <v>18.21974965229485</v>
+        <v>18.1058495821727</v>
       </c>
       <c r="M478" t="n">
         <v>3</v>
@@ -37301,7 +37301,7 @@
         <v>-0.9446371981490786</v>
       </c>
       <c r="H479" t="n">
-        <v>3287.161392369851</v>
+        <v>3287.161645949698</v>
       </c>
       <c r="I479" t="n">
         <v>1966.020518717901</v>
@@ -37310,10 +37310,10 @@
         <v>17.19104546795396</v>
       </c>
       <c r="K479" t="n">
-        <v>42.67193543271921</v>
+        <v>42.67194643878896</v>
       </c>
       <c r="L479" t="n">
-        <v>17.52433936022253</v>
+        <v>17.40947075208914</v>
       </c>
       <c r="M479" t="n">
         <v>3</v>
@@ -37390,7 +37390,7 @@
         <v>50.64171775777073</v>
       </c>
       <c r="L480" t="n">
-        <v>16.68984700973574</v>
+        <v>16.57381615598886</v>
       </c>
       <c r="M480" t="n">
         <v>3</v>
@@ -37467,7 +37467,7 @@
         <v>76.48002048540721</v>
       </c>
       <c r="L481" t="n">
-        <v>13.63004172461753</v>
+        <v>13.50974930362117</v>
       </c>
       <c r="M481" t="n">
         <v>3</v>
@@ -37544,7 +37544,7 @@
         <v>62.57822466968648</v>
       </c>
       <c r="L482" t="n">
-        <v>11.12656467315716</v>
+        <v>11.00278551532034</v>
       </c>
       <c r="M482" t="n">
         <v>3</v>
@@ -37621,7 +37621,7 @@
         <v>98.58492271587369</v>
       </c>
       <c r="L483" t="n">
-        <v>8.484005563282336</v>
+        <v>8.356545961002785</v>
       </c>
       <c r="M483" t="n">
         <v>3</v>
@@ -37698,7 +37698,7 @@
         <v>37.84782266149374</v>
       </c>
       <c r="L484" t="n">
-        <v>61.19610570236439</v>
+        <v>61.14206128133704</v>
       </c>
       <c r="M484" t="n">
         <v>2</v>
@@ -37775,7 +37775,7 @@
         <v>15.10035581623805</v>
       </c>
       <c r="L485" t="n">
-        <v>60.63977746870653</v>
+        <v>60.58495821727019</v>
       </c>
       <c r="M485" t="n">
         <v>2</v>
@@ -37852,7 +37852,7 @@
         <v>16.46048988874487</v>
       </c>
       <c r="L486" t="n">
-        <v>57.99721835883172</v>
+        <v>57.93871866295265</v>
       </c>
       <c r="M486" t="n">
         <v>2</v>
@@ -37920,16 +37920,16 @@
         <v>478.7148398145708</v>
       </c>
       <c r="I487" t="n">
-        <v>355.1754992566601</v>
+        <v>355.1755291130353</v>
       </c>
       <c r="J487" t="n">
-        <v>16.94218969855566</v>
+        <v>16.94217986828976</v>
       </c>
       <c r="K487" t="n">
         <v>15.25576809435825</v>
       </c>
       <c r="L487" t="n">
-        <v>53.12934631432545</v>
+        <v>53.06406685236769</v>
       </c>
       <c r="M487" t="n">
         <v>2</v>
@@ -38006,7 +38006,7 @@
         <v>14.52853095912585</v>
       </c>
       <c r="L488" t="n">
-        <v>49.09596662030598</v>
+        <v>49.02506963788301</v>
       </c>
       <c r="M488" t="n">
         <v>2</v>
@@ -38083,7 +38083,7 @@
         <v>31.80957146534591</v>
       </c>
       <c r="L489" t="n">
-        <v>47.98331015299026</v>
+        <v>47.9108635097493</v>
       </c>
       <c r="M489" t="n">
         <v>2</v>
@@ -38160,7 +38160,7 @@
         <v>38.6740319635984</v>
       </c>
       <c r="L490" t="n">
-        <v>47.8442280945758</v>
+        <v>47.77158774373259</v>
       </c>
       <c r="M490" t="n">
         <v>2</v>
@@ -38237,7 +38237,7 @@
         <v>19.60663275696091</v>
       </c>
       <c r="L491" t="n">
-        <v>45.20166898470097</v>
+        <v>45.12534818941504</v>
       </c>
       <c r="M491" t="n">
         <v>2</v>
@@ -38314,7 +38314,7 @@
         <v>12.34961353039177</v>
       </c>
       <c r="L492" t="n">
-        <v>44.22809457579972</v>
+        <v>44.15041782729805</v>
       </c>
       <c r="M492" t="n">
         <v>2</v>
@@ -38391,7 +38391,7 @@
         <v>32.68438318226765</v>
       </c>
       <c r="L493" t="n">
-        <v>43.39360222531293</v>
+        <v>43.31476323119777</v>
       </c>
       <c r="M493" t="n">
         <v>2</v>
@@ -38468,7 +38468,7 @@
         <v>12.05815175631362</v>
       </c>
       <c r="L494" t="n">
-        <v>42.83727399165508</v>
+        <v>42.75766016713091</v>
       </c>
       <c r="M494" t="n">
         <v>2</v>
@@ -38545,7 +38545,7 @@
         <v>14.77052388134494</v>
       </c>
       <c r="L495" t="n">
-        <v>41.72461752433936</v>
+        <v>41.64345403899721</v>
       </c>
       <c r="M495" t="n">
         <v>2</v>
@@ -38610,7 +38610,7 @@
         <v>1.868406815897994</v>
       </c>
       <c r="H496" t="n">
-        <v>859.7877065596524</v>
+        <v>859.7877679261235</v>
       </c>
       <c r="I496" t="n">
         <v>502</v>
@@ -38619,10 +38619,10 @@
         <v>24.27290350317479</v>
       </c>
       <c r="K496" t="n">
-        <v>37.81962654596813</v>
+        <v>37.81963638270347</v>
       </c>
       <c r="L496" t="n">
-        <v>40.47287899860918</v>
+        <v>40.38997214484679</v>
       </c>
       <c r="M496" t="n">
         <v>2</v>
@@ -38699,7 +38699,7 @@
         <v>28.23856487734386</v>
       </c>
       <c r="L497" t="n">
-        <v>38.94297635605007</v>
+        <v>38.85793871866296</v>
       </c>
       <c r="M497" t="n">
         <v>2</v>
@@ -38776,7 +38776,7 @@
         <v>13.20874611178033</v>
       </c>
       <c r="L498" t="n">
-        <v>36.71766342141864</v>
+        <v>36.62952646239555</v>
       </c>
       <c r="M498" t="n">
         <v>2</v>
@@ -38853,7 +38853,7 @@
         <v>18.11980219864351</v>
       </c>
       <c r="L499" t="n">
-        <v>34.90959666203059</v>
+        <v>34.81894150417828</v>
       </c>
       <c r="M499" t="n">
         <v>2</v>
@@ -38930,7 +38930,7 @@
         <v>35.63497266778386</v>
       </c>
       <c r="L500" t="n">
-        <v>34.21418636995828</v>
+        <v>34.12256267409471</v>
       </c>
       <c r="M500" t="n">
         <v>2</v>
@@ -39007,7 +39007,7 @@
         <v>33.73416346122715</v>
       </c>
       <c r="L501" t="n">
-        <v>33.93602225312934</v>
+        <v>33.84401114206128</v>
       </c>
       <c r="M501" t="n">
         <v>2</v>
@@ -39084,7 +39084,7 @@
         <v>22.22293788171115</v>
       </c>
       <c r="L502" t="n">
-        <v>33.51877607788595</v>
+        <v>33.42618384401114</v>
       </c>
       <c r="M502" t="n">
         <v>2</v>
@@ -39161,7 +39161,7 @@
         <v>30.20926624114764</v>
       </c>
       <c r="L503" t="n">
-        <v>32.82336578581363</v>
+        <v>32.72980501392757</v>
       </c>
       <c r="M503" t="n">
         <v>2</v>
@@ -39238,7 +39238,7 @@
         <v>27.49571274090126</v>
       </c>
       <c r="L504" t="n">
-        <v>32.26703755215577</v>
+        <v>32.17270194986072</v>
       </c>
       <c r="M504" t="n">
         <v>2</v>
@@ -39315,7 +39315,7 @@
         <v>26.58059535071981</v>
       </c>
       <c r="L505" t="n">
-        <v>31.84979137691238</v>
+        <v>31.75487465181058</v>
       </c>
       <c r="M505" t="n">
         <v>2</v>
@@ -39392,7 +39392,7 @@
         <v>67.40271935096153</v>
       </c>
       <c r="L506" t="n">
-        <v>31.15438108484005</v>
+        <v>31.05849582172702</v>
       </c>
       <c r="M506" t="n">
         <v>2</v>
@@ -39469,7 +39469,7 @@
         <v>21.29904687862339</v>
       </c>
       <c r="L507" t="n">
-        <v>31.01529902642559</v>
+        <v>30.9192200557103</v>
       </c>
       <c r="M507" t="n">
         <v>2</v>
@@ -39546,7 +39546,7 @@
         <v>24.8924330281288</v>
       </c>
       <c r="L508" t="n">
-        <v>30.73713490959666</v>
+        <v>30.64066852367688</v>
       </c>
       <c r="M508" t="n">
         <v>2</v>
@@ -39623,7 +39623,7 @@
         <v>69.1544810392073</v>
       </c>
       <c r="L509" t="n">
-        <v>30.31988873435327</v>
+        <v>30.22284122562674</v>
       </c>
       <c r="M509" t="n">
         <v>2</v>
@@ -39700,7 +39700,7 @@
         <v>29.22372087617855</v>
       </c>
       <c r="L510" t="n">
-        <v>29.76356050069541</v>
+        <v>29.66573816155989</v>
       </c>
       <c r="M510" t="n">
         <v>2</v>
@@ -39777,7 +39777,7 @@
         <v>35.57000951905604</v>
       </c>
       <c r="L511" t="n">
-        <v>28.51182197496523</v>
+        <v>28.41225626740947</v>
       </c>
       <c r="M511" t="n">
         <v>2</v>
@@ -39842,7 +39842,7 @@
         <v>0.3168148596166542</v>
       </c>
       <c r="H512" t="n">
-        <v>163308.5022863474</v>
+        <v>163308.4863287346</v>
       </c>
       <c r="I512" t="n">
         <v>121787.4350540836</v>
@@ -39851,10 +39851,10 @@
         <v>6.698199155186857</v>
       </c>
       <c r="K512" t="n">
-        <v>25.67509506818073</v>
+        <v>25.67508278789843</v>
       </c>
       <c r="L512" t="n">
-        <v>27.53824756606398</v>
+        <v>27.43732590529248</v>
       </c>
       <c r="M512" t="n">
         <v>2</v>
@@ -39931,7 +39931,7 @@
         <v>31.32525195115374</v>
       </c>
       <c r="L513" t="n">
-        <v>27.39916550764951</v>
+        <v>27.29805013927577</v>
       </c>
       <c r="M513" t="n">
         <v>2</v>
@@ -40008,7 +40008,7 @@
         <v>25.55984410438146</v>
       </c>
       <c r="L514" t="n">
-        <v>27.26008344923505</v>
+        <v>27.15877437325905</v>
       </c>
       <c r="M514" t="n">
         <v>2</v>
@@ -40085,7 +40085,7 @@
         <v>43.31893746124087</v>
       </c>
       <c r="L515" t="n">
-        <v>26.56467315716273</v>
+        <v>26.46239554317549</v>
       </c>
       <c r="M515" t="n">
         <v>2</v>
@@ -40162,7 +40162,7 @@
         <v>28.17725069400121</v>
       </c>
       <c r="L516" t="n">
-        <v>25.31293463143254</v>
+        <v>25.20891364902507</v>
       </c>
       <c r="M516" t="n">
         <v>2</v>
@@ -40239,7 +40239,7 @@
         <v>28.20628343961589</v>
       </c>
       <c r="L517" t="n">
-        <v>24.75660639777469</v>
+        <v>24.65181058495822</v>
       </c>
       <c r="M517" t="n">
         <v>2</v>
@@ -40316,7 +40316,7 @@
         <v>60.84970008144697</v>
       </c>
       <c r="L518" t="n">
-        <v>23.50486787204451</v>
+        <v>23.3983286908078</v>
       </c>
       <c r="M518" t="n">
         <v>2</v>
@@ -40393,7 +40393,7 @@
         <v>25.17882292089531</v>
       </c>
       <c r="L519" t="n">
-        <v>22.94853963838665</v>
+        <v>22.84122562674095</v>
       </c>
       <c r="M519" t="n">
         <v>2</v>
@@ -40470,7 +40470,7 @@
         <v>22.16419766444611</v>
       </c>
       <c r="L520" t="n">
-        <v>22.53129346314325</v>
+        <v>22.42339832869081</v>
       </c>
       <c r="M520" t="n">
         <v>2</v>
@@ -40547,7 +40547,7 @@
         <v>34.21101693805109</v>
       </c>
       <c r="L521" t="n">
-        <v>21.69680111265647</v>
+        <v>21.58774373259053</v>
       </c>
       <c r="M521" t="n">
         <v>2</v>
@@ -40624,7 +40624,7 @@
         <v>33.96601114697426</v>
       </c>
       <c r="L522" t="n">
-        <v>21.41863699582754</v>
+        <v>21.3091922005571</v>
       </c>
       <c r="M522" t="n">
         <v>2</v>
@@ -40701,7 +40701,7 @@
         <v>41.43981570964848</v>
       </c>
       <c r="L523" t="n">
-        <v>20.30598052851182</v>
+        <v>20.1949860724234</v>
       </c>
       <c r="M523" t="n">
         <v>2</v>
@@ -40778,7 +40778,7 @@
         <v>44.14239244100266</v>
       </c>
       <c r="L524" t="n">
-        <v>20.16689847009736</v>
+        <v>20.05571030640668</v>
       </c>
       <c r="M524" t="n">
         <v>2</v>
@@ -40855,7 +40855,7 @@
         <v>38.75407899455616</v>
       </c>
       <c r="L525" t="n">
-        <v>18.63699582753825</v>
+        <v>18.52367688022284</v>
       </c>
       <c r="M525" t="n">
         <v>2</v>
@@ -40932,7 +40932,7 @@
         <v>35.38607491624675</v>
       </c>
       <c r="L526" t="n">
-        <v>17.663421418637</v>
+        <v>17.54874651810585</v>
       </c>
       <c r="M526" t="n">
         <v>2</v>
@@ -41009,7 +41009,7 @@
         <v>44.1652003901351</v>
       </c>
       <c r="L527" t="n">
-        <v>17.10709318497914</v>
+        <v>16.991643454039</v>
       </c>
       <c r="M527" t="n">
         <v>2</v>
@@ -41086,7 +41086,7 @@
         <v>49.77640469649931</v>
       </c>
       <c r="L528" t="n">
-        <v>16.41168289290681</v>
+        <v>16.29526462395543</v>
       </c>
       <c r="M528" t="n">
         <v>2</v>
@@ -41163,7 +41163,7 @@
         <v>56.22218029819204</v>
       </c>
       <c r="L529" t="n">
-        <v>15.15994436717663</v>
+        <v>15.04178272980501</v>
       </c>
       <c r="M529" t="n">
         <v>2</v>
@@ -41240,7 +41240,7 @@
         <v>49.68134153159869</v>
       </c>
       <c r="L530" t="n">
-        <v>14.88178025034771</v>
+        <v>14.76323119777159</v>
       </c>
       <c r="M530" t="n">
         <v>2</v>
@@ -41317,7 +41317,7 @@
         <v>44.864664974904</v>
       </c>
       <c r="L531" t="n">
-        <v>14.60361613351878</v>
+        <v>14.48467966573816</v>
       </c>
       <c r="M531" t="n">
         <v>2</v>
@@ -41382,7 +41382,7 @@
         <v>0.01071732198507647</v>
       </c>
       <c r="H532" t="n">
-        <v>1608.140814494163</v>
+        <v>1608.140938678776</v>
       </c>
       <c r="I532" t="n">
         <v>1123.599975585938</v>
@@ -41391,10 +41391,10 @@
         <v>2.705591409274422</v>
       </c>
       <c r="K532" t="n">
-        <v>39.35362343970215</v>
+        <v>39.35363420093376</v>
       </c>
       <c r="L532" t="n">
-        <v>14.18636995827538</v>
+        <v>14.06685236768802</v>
       </c>
       <c r="M532" t="n">
         <v>2</v>
@@ -41471,7 +41471,7 @@
         <v>79.52751046887991</v>
       </c>
       <c r="L533" t="n">
-        <v>12.9346314325452</v>
+        <v>12.8133704735376</v>
       </c>
       <c r="M533" t="n">
         <v>2</v>
@@ -41548,7 +41548,7 @@
         <v>45.37694027320427</v>
       </c>
       <c r="L534" t="n">
-        <v>12.37830319888734</v>
+        <v>12.25626740947075</v>
       </c>
       <c r="M534" t="n">
         <v>2</v>
@@ -41625,7 +41625,7 @@
         <v>74.58543628860153</v>
       </c>
       <c r="L535" t="n">
-        <v>12.23922114047288</v>
+        <v>12.11699164345404</v>
       </c>
       <c r="M535" t="n">
         <v>2</v>
@@ -41690,7 +41690,7 @@
         <v>1.271699251172875</v>
       </c>
       <c r="H536" t="n">
-        <v>872.0425606177564</v>
+        <v>872.0426229622601</v>
       </c>
       <c r="I536" t="n">
         <v>406.1171468902937</v>
@@ -41699,10 +41699,10 @@
         <v>23.56040409407345</v>
       </c>
       <c r="K536" t="n">
-        <v>73.78289793373636</v>
+        <v>73.78291035791038</v>
       </c>
       <c r="L536" t="n">
-        <v>10.29207232267037</v>
+        <v>10.16713091922006</v>
       </c>
       <c r="M536" t="n">
         <v>2</v>
@@ -41779,7 +41779,7 @@
         <v>85.74891953732407</v>
       </c>
       <c r="L537" t="n">
-        <v>10.15299026425591</v>
+        <v>10.02785515320334</v>
       </c>
       <c r="M537" t="n">
         <v>2</v>
@@ -41856,7 +41856,7 @@
         <v>62.59868717038039</v>
       </c>
       <c r="L538" t="n">
-        <v>9.318497913769123</v>
+        <v>9.192200557103064</v>
       </c>
       <c r="M538" t="n">
         <v>2</v>
@@ -41933,7 +41933,7 @@
         <v>81.87000955822181</v>
       </c>
       <c r="L539" t="n">
-        <v>8.344923504867872</v>
+        <v>8.217270194986073</v>
       </c>
       <c r="M539" t="n">
         <v>2</v>
@@ -42010,7 +42010,7 @@
         <v>77.01488776528463</v>
       </c>
       <c r="L540" t="n">
-        <v>5.84144645340751</v>
+        <v>5.710306406685237</v>
       </c>
       <c r="M540" t="n">
         <v>2</v>
@@ -42087,7 +42087,7 @@
         <v>77.24813462516875</v>
       </c>
       <c r="L541" t="n">
-        <v>5.702364394993046</v>
+        <v>5.571030640668524</v>
       </c>
       <c r="M541" t="n">
         <v>2</v>
@@ -42164,7 +42164,7 @@
         <v>368.1259710338487</v>
       </c>
       <c r="L542" t="n">
-        <v>0.1390820584144645</v>
+        <v>0.1392757660167131</v>
       </c>
       <c r="M542" t="n">
         <v>2</v>
@@ -42241,7 +42241,7 @@
         <v>37.31210368951341</v>
       </c>
       <c r="L543" t="n">
-        <v>62.58692628650904</v>
+        <v>62.53481894150418</v>
       </c>
       <c r="M543" t="n">
         <v>1</v>
@@ -42318,7 +42318,7 @@
         <v>42.02527197584256</v>
       </c>
       <c r="L544" t="n">
-        <v>61.89151599443672</v>
+        <v>61.83844011142061</v>
       </c>
       <c r="M544" t="n">
         <v>1</v>
@@ -42395,7 +42395,7 @@
         <v>23.15187700355848</v>
       </c>
       <c r="L545" t="n">
-        <v>48.95688456189152</v>
+        <v>48.8857938718663</v>
       </c>
       <c r="M545" t="n">
         <v>1</v>
@@ -42472,7 +42472,7 @@
         <v>25.77544507925111</v>
       </c>
       <c r="L546" t="n">
-        <v>48.2614742698192</v>
+        <v>48.18941504178273</v>
       </c>
       <c r="M546" t="n">
         <v>1</v>
@@ -42549,7 +42549,7 @@
         <v>14.61995163872982</v>
       </c>
       <c r="L547" t="n">
-        <v>46.31432545201669</v>
+        <v>46.23955431754874</v>
       </c>
       <c r="M547" t="n">
         <v>1</v>
@@ -42626,7 +42626,7 @@
         <v>16.6419528457955</v>
       </c>
       <c r="L548" t="n">
-        <v>45.06258692628651</v>
+        <v>44.98607242339833</v>
       </c>
       <c r="M548" t="n">
         <v>1</v>
@@ -42703,7 +42703,7 @@
         <v>19.23373627579366</v>
       </c>
       <c r="L549" t="n">
-        <v>44.08901251738526</v>
+        <v>44.01114206128134</v>
       </c>
       <c r="M549" t="n">
         <v>1</v>
@@ -42771,16 +42771,16 @@
         <v>409.9712889887167</v>
       </c>
       <c r="I550" t="n">
-        <v>309.838511773213</v>
+        <v>309.8384816659088</v>
       </c>
       <c r="J550" t="n">
-        <v>7.3139675559035</v>
+        <v>7.313977983705233</v>
       </c>
       <c r="K550" t="n">
         <v>23.29963578608019</v>
       </c>
       <c r="L550" t="n">
-        <v>41.44645340751043</v>
+        <v>41.36490250696379</v>
       </c>
       <c r="M550" t="n">
         <v>1</v>
@@ -42857,7 +42857,7 @@
         <v>39.61627913856931</v>
       </c>
       <c r="L551" t="n">
-        <v>39.49930458970793</v>
+        <v>39.4150417827298</v>
       </c>
       <c r="M551" t="n">
         <v>1</v>
@@ -42934,7 +42934,7 @@
         <v>97.36134209916072</v>
       </c>
       <c r="L552" t="n">
-        <v>39.08205841446453</v>
+        <v>38.99721448467967</v>
       </c>
       <c r="M552" t="n">
         <v>1</v>
@@ -43011,7 +43011,7 @@
         <v>26.00354224215176</v>
       </c>
       <c r="L553" t="n">
-        <v>37.83031988873435</v>
+        <v>37.74373259052925</v>
       </c>
       <c r="M553" t="n">
         <v>1</v>
@@ -43088,7 +43088,7 @@
         <v>35.06544851604918</v>
       </c>
       <c r="L554" t="n">
-        <v>36.16133518776078</v>
+        <v>36.07242339832869</v>
       </c>
       <c r="M554" t="n">
         <v>1</v>
@@ -43165,7 +43165,7 @@
         <v>19.94594019767666</v>
       </c>
       <c r="L555" t="n">
-        <v>35.88317107093185</v>
+        <v>35.79387186629526</v>
       </c>
       <c r="M555" t="n">
         <v>1</v>
@@ -43242,7 +43242,7 @@
         <v>25.31805406690331</v>
       </c>
       <c r="L556" t="n">
-        <v>35.74408901251739</v>
+        <v>35.65459610027855</v>
       </c>
       <c r="M556" t="n">
         <v>1</v>
@@ -43319,7 +43319,7 @@
         <v>85.99043493099296</v>
       </c>
       <c r="L557" t="n">
-        <v>34.35326842837274</v>
+        <v>34.26183844011142</v>
       </c>
       <c r="M557" t="n">
         <v>1</v>
@@ -43396,7 +43396,7 @@
         <v>49.66401187519624</v>
       </c>
       <c r="L558" t="n">
-        <v>34.07510431154381</v>
+        <v>33.98328690807799</v>
       </c>
       <c r="M558" t="n">
         <v>1</v>
@@ -43473,7 +43473,7 @@
         <v>22.16165872444784</v>
       </c>
       <c r="L559" t="n">
-        <v>33.37969401947149</v>
+        <v>33.28690807799443</v>
       </c>
       <c r="M559" t="n">
         <v>1</v>
@@ -43550,7 +43550,7 @@
         <v>19.65616160144748</v>
       </c>
       <c r="L560" t="n">
-        <v>30.87621696801113</v>
+        <v>30.7799442896936</v>
       </c>
       <c r="M560" t="n">
         <v>1</v>
@@ -43627,7 +43627,7 @@
         <v>36.82569031321674</v>
       </c>
       <c r="L561" t="n">
-        <v>29.62447844228094</v>
+        <v>29.52646239554317</v>
       </c>
       <c r="M561" t="n">
         <v>1</v>
@@ -43704,7 +43704,7 @@
         <v>32.09382871680404</v>
       </c>
       <c r="L562" t="n">
-        <v>29.06815020862309</v>
+        <v>28.96935933147632</v>
       </c>
       <c r="M562" t="n">
         <v>1</v>
@@ -43781,7 +43781,7 @@
         <v>34.01378973599138</v>
       </c>
       <c r="L563" t="n">
-        <v>28.65090403337969</v>
+        <v>28.55153203342618</v>
       </c>
       <c r="M563" t="n">
         <v>1</v>
@@ -43858,7 +43858,7 @@
         <v>35.17545634000307</v>
       </c>
       <c r="L564" t="n">
-        <v>28.2336578581363</v>
+        <v>28.13370473537605</v>
       </c>
       <c r="M564" t="n">
         <v>1</v>
@@ -43935,7 +43935,7 @@
         <v>29.04937964622247</v>
       </c>
       <c r="L565" t="n">
-        <v>27.81641168289291</v>
+        <v>27.7158774373259</v>
       </c>
       <c r="M565" t="n">
         <v>1</v>
@@ -44012,7 +44012,7 @@
         <v>22.15324148901414</v>
       </c>
       <c r="L566" t="n">
-        <v>26.42559109874826</v>
+        <v>26.32311977715878</v>
       </c>
       <c r="M566" t="n">
         <v>1</v>
@@ -44089,7 +44089,7 @@
         <v>29.45564673527139</v>
       </c>
       <c r="L567" t="n">
-        <v>26.14742698191933</v>
+        <v>26.04456824512535</v>
       </c>
       <c r="M567" t="n">
         <v>1</v>
@@ -44154,7 +44154,7 @@
         <v>-0.06088461488257257</v>
       </c>
       <c r="H568" t="n">
-        <v>155.8999606999571</v>
+        <v>155.8999783750524</v>
       </c>
       <c r="I568" t="n">
         <v>112.8155071321618</v>
@@ -44163,10 +44163,10 @@
         <v>5.402179793251238</v>
       </c>
       <c r="K568" t="n">
-        <v>31.10752325175028</v>
+        <v>31.10753811601292</v>
       </c>
       <c r="L568" t="n">
-        <v>26.00834492350487</v>
+        <v>25.90529247910863</v>
       </c>
       <c r="M568" t="n">
         <v>1</v>
@@ -44243,7 +44243,7 @@
         <v>35.63829604207663</v>
       </c>
       <c r="L569" t="n">
-        <v>25.45201668984701</v>
+        <v>25.34818941504178</v>
       </c>
       <c r="M569" t="n">
         <v>1</v>
@@ -44320,7 +44320,7 @@
         <v>58.10000357421075</v>
       </c>
       <c r="L570" t="n">
-        <v>25.17385257301808</v>
+        <v>25.06963788300835</v>
       </c>
       <c r="M570" t="n">
         <v>1</v>
@@ -44397,7 +44397,7 @@
         <v>36.48754312359201</v>
       </c>
       <c r="L571" t="n">
-        <v>24.89568845618915</v>
+        <v>24.79108635097493</v>
       </c>
       <c r="M571" t="n">
         <v>1</v>
@@ -44462,7 +44462,7 @@
         <v>0.9253055751860639</v>
       </c>
       <c r="H572" t="n">
-        <v>239.2186728978909</v>
+        <v>239.2186883393384</v>
       </c>
       <c r="I572" t="n">
         <v>156.7443123050878</v>
@@ -44471,10 +44471,10 @@
         <v>14.96429713985419</v>
       </c>
       <c r="K572" t="n">
-        <v>32.75176301284863</v>
+        <v>32.75177158190954</v>
       </c>
       <c r="L572" t="n">
-        <v>24.20027816411683</v>
+        <v>24.09470752089137</v>
       </c>
       <c r="M572" t="n">
         <v>1</v>
@@ -44551,7 +44551,7 @@
         <v>42.29194935101081</v>
       </c>
       <c r="L573" t="n">
-        <v>23.22670375521558</v>
+        <v>23.11977715877437</v>
       </c>
       <c r="M573" t="n">
         <v>1</v>
@@ -44628,7 +44628,7 @@
         <v>32.28200756723054</v>
       </c>
       <c r="L574" t="n">
-        <v>23.08762169680111</v>
+        <v>22.98050139275766</v>
       </c>
       <c r="M574" t="n">
         <v>1</v>
@@ -44705,7 +44705,7 @@
         <v>34.96783578518276</v>
       </c>
       <c r="L575" t="n">
-        <v>22.25312934631433</v>
+        <v>22.14484679665738</v>
       </c>
       <c r="M575" t="n">
         <v>1</v>
@@ -44782,7 +44782,7 @@
         <v>35.61191194988658</v>
       </c>
       <c r="L576" t="n">
-        <v>22.11404728789986</v>
+        <v>22.00557103064067</v>
       </c>
       <c r="M576" t="n">
         <v>1</v>
@@ -44859,7 +44859,7 @@
         <v>36.70367669357005</v>
       </c>
       <c r="L577" t="n">
-        <v>21.27955493741307</v>
+        <v>21.16991643454039</v>
       </c>
       <c r="M577" t="n">
         <v>1</v>
@@ -44936,7 +44936,7 @@
         <v>44.48384890390822</v>
       </c>
       <c r="L578" t="n">
-        <v>21.14047287899861</v>
+        <v>21.03064066852368</v>
       </c>
       <c r="M578" t="n">
         <v>1</v>
@@ -45013,7 +45013,7 @@
         <v>46.07688492292974</v>
       </c>
       <c r="L579" t="n">
-        <v>20.58414464534075</v>
+        <v>20.47353760445682</v>
       </c>
       <c r="M579" t="n">
         <v>1</v>
@@ -45090,7 +45090,7 @@
         <v>38.17975168687051</v>
       </c>
       <c r="L580" t="n">
-        <v>19.88873435326843</v>
+        <v>19.77715877437326</v>
       </c>
       <c r="M580" t="n">
         <v>1</v>
@@ -45167,7 +45167,7 @@
         <v>71.04002155153506</v>
       </c>
       <c r="L581" t="n">
-        <v>19.74965229485396</v>
+        <v>19.63788300835655</v>
       </c>
       <c r="M581" t="n">
         <v>1</v>
@@ -45244,7 +45244,7 @@
         <v>40.70955845212572</v>
       </c>
       <c r="L582" t="n">
-        <v>19.19332406119611</v>
+        <v>19.0807799442897</v>
       </c>
       <c r="M582" t="n">
         <v>1</v>
@@ -45321,7 +45321,7 @@
         <v>42.42354600270473</v>
       </c>
       <c r="L583" t="n">
-        <v>18.91515994436718</v>
+        <v>18.80222841225627</v>
       </c>
       <c r="M583" t="n">
         <v>1</v>
@@ -45398,7 +45398,7 @@
         <v>42.01907402173241</v>
       </c>
       <c r="L584" t="n">
-        <v>18.77607788595271</v>
+        <v>18.66295264623956</v>
       </c>
       <c r="M584" t="n">
         <v>1</v>
@@ -45475,7 +45475,7 @@
         <v>36.67652490858882</v>
       </c>
       <c r="L585" t="n">
-        <v>18.49791376912378</v>
+        <v>18.38440111420613</v>
       </c>
       <c r="M585" t="n">
         <v>1</v>
@@ -45552,7 +45552,7 @@
         <v>50.68352259416046</v>
       </c>
       <c r="L586" t="n">
-        <v>18.35883171070932</v>
+        <v>18.24512534818941</v>
       </c>
       <c r="M586" t="n">
         <v>1</v>
@@ -45629,7 +45629,7 @@
         <v>42.30433036149772</v>
       </c>
       <c r="L587" t="n">
-        <v>17.80250347705146</v>
+        <v>17.68802228412256</v>
       </c>
       <c r="M587" t="n">
         <v>1</v>
@@ -45706,7 +45706,7 @@
         <v>55.44229636338653</v>
       </c>
       <c r="L588" t="n">
-        <v>17.2461752433936</v>
+        <v>17.13091922005571</v>
       </c>
       <c r="M588" t="n">
         <v>1</v>
@@ -45771,7 +45771,7 @@
         <v>0.4879661801902468</v>
       </c>
       <c r="H589" t="n">
-        <v>408.5542426067486</v>
+        <v>408.5542740377988</v>
       </c>
       <c r="I589" t="n">
         <v>243.9284560598348</v>
@@ -45780,10 +45780,10 @@
         <v>11.118641986764</v>
       </c>
       <c r="K589" t="n">
-        <v>50.73021988800357</v>
+        <v>50.73023148403812</v>
       </c>
       <c r="L589" t="n">
-        <v>16.96801112656467</v>
+        <v>16.85236768802228</v>
       </c>
       <c r="M589" t="n">
         <v>1</v>
@@ -45860,7 +45860,7 @@
         <v>48.97145886353971</v>
       </c>
       <c r="L590" t="n">
-        <v>16.82892906815021</v>
+        <v>16.71309192200557</v>
       </c>
       <c r="M590" t="n">
         <v>1</v>
@@ -45937,7 +45937,7 @@
         <v>43.28539053088549</v>
       </c>
       <c r="L591" t="n">
-        <v>16.27260083449235</v>
+        <v>16.15598885793872</v>
       </c>
       <c r="M591" t="n">
         <v>1</v>
@@ -46014,7 +46014,7 @@
         <v>36.20810602355371</v>
       </c>
       <c r="L592" t="n">
-        <v>16.13351877607789</v>
+        <v>16.016713091922</v>
       </c>
       <c r="M592" t="n">
         <v>1</v>
@@ -46091,7 +46091,7 @@
         <v>40.76856012744719</v>
       </c>
       <c r="L593" t="n">
-        <v>15.99443671766342</v>
+        <v>15.87743732590529</v>
       </c>
       <c r="M593" t="n">
         <v>1</v>
@@ -46168,7 +46168,7 @@
         <v>34.68792702042578</v>
       </c>
       <c r="L594" t="n">
-        <v>15.85535465924896</v>
+        <v>15.73816155988858</v>
       </c>
       <c r="M594" t="n">
         <v>1</v>
@@ -46245,7 +46245,7 @@
         <v>43.72057954912112</v>
       </c>
       <c r="L595" t="n">
-        <v>15.02086230876217</v>
+        <v>14.9025069637883</v>
       </c>
       <c r="M595" t="n">
         <v>1</v>
@@ -46322,7 +46322,7 @@
         <v>37.89746917585983</v>
       </c>
       <c r="L596" t="n">
-        <v>14.46453407510431</v>
+        <v>14.34540389972145</v>
       </c>
       <c r="M596" t="n">
         <v>1</v>
@@ -46399,7 +46399,7 @@
         <v>58.38732509877806</v>
       </c>
       <c r="L597" t="n">
-        <v>13.49095966620306</v>
+        <v>13.37047353760446</v>
       </c>
       <c r="M597" t="n">
         <v>1</v>
@@ -46476,7 +46476,7 @@
         <v>33.84787321166374</v>
       </c>
       <c r="L598" t="n">
-        <v>13.21279554937413</v>
+        <v>13.09192200557103</v>
       </c>
       <c r="M598" t="n">
         <v>1</v>
@@ -46553,7 +46553,7 @@
         <v>63.04561970961365</v>
       </c>
       <c r="L599" t="n">
-        <v>10.9874826147427</v>
+        <v>10.86350974930362</v>
       </c>
       <c r="M599" t="n">
         <v>1</v>
@@ -46630,7 +46630,7 @@
         <v>51.13477476235229</v>
       </c>
       <c r="L600" t="n">
-        <v>10.84840055632823</v>
+        <v>10.72423398328691</v>
       </c>
       <c r="M600" t="n">
         <v>1</v>
@@ -46707,7 +46707,7 @@
         <v>79.29218528189597</v>
       </c>
       <c r="L601" t="n">
-        <v>10.01390820584145</v>
+        <v>9.888579387186629</v>
       </c>
       <c r="M601" t="n">
         <v>1</v>
@@ -46784,7 +46784,7 @@
         <v>46.43999234966676</v>
       </c>
       <c r="L602" t="n">
-        <v>9.874826147426981</v>
+        <v>9.749303621169917</v>
       </c>
       <c r="M602" t="n">
         <v>1</v>
@@ -46861,7 +46861,7 @@
         <v>61.90700569798546</v>
       </c>
       <c r="L603" t="n">
-        <v>9.457579972183588</v>
+        <v>9.331476323119778</v>
       </c>
       <c r="M603" t="n">
         <v>1</v>
@@ -46938,7 +46938,7 @@
         <v>60.58277862750931</v>
       </c>
       <c r="L604" t="n">
-        <v>9.179415855354661</v>
+        <v>9.052924791086351</v>
       </c>
       <c r="M604" t="n">
         <v>1</v>
@@ -47015,7 +47015,7 @@
         <v>61.85437716757327</v>
       </c>
       <c r="L605" t="n">
-        <v>9.040333796940194</v>
+        <v>8.913649025069638</v>
       </c>
       <c r="M605" t="n">
         <v>1</v>
@@ -47092,7 +47092,7 @@
         <v>103.0838286805296</v>
       </c>
       <c r="L606" t="n">
-        <v>8.90125173852573</v>
+        <v>8.774373259052924</v>
       </c>
       <c r="M606" t="n">
         <v>1</v>
@@ -47169,7 +47169,7 @@
         <v>53.45459793805056</v>
       </c>
       <c r="L607" t="n">
-        <v>8.762169680111267</v>
+        <v>8.635097493036211</v>
       </c>
       <c r="M607" t="n">
         <v>1</v>
@@ -47246,7 +47246,7 @@
         <v>88.6045126868554</v>
       </c>
       <c r="L608" t="n">
-        <v>8.623087621696801</v>
+        <v>8.495821727019498</v>
       </c>
       <c r="M608" t="n">
         <v>1</v>
@@ -47323,7 +47323,7 @@
         <v>85.28116629503819</v>
       </c>
       <c r="L609" t="n">
-        <v>8.066759388038943</v>
+        <v>7.938718662952645</v>
       </c>
       <c r="M609" t="n">
         <v>1</v>
@@ -47400,7 +47400,7 @@
         <v>43.66519166842892</v>
       </c>
       <c r="L610" t="n">
-        <v>7.788595271210013</v>
+        <v>7.66016713091922</v>
       </c>
       <c r="M610" t="n">
         <v>1</v>
@@ -47477,7 +47477,7 @@
         <v>95.66985975640272</v>
       </c>
       <c r="L611" t="n">
-        <v>7.649513212795549</v>
+        <v>7.520891364902507</v>
       </c>
       <c r="M611" t="n">
         <v>1</v>
@@ -47554,7 +47554,7 @@
         <v>69.16722754344886</v>
       </c>
       <c r="L612" t="n">
-        <v>5.980528511821975</v>
+        <v>5.849582172701949</v>
       </c>
       <c r="M612" t="n">
         <v>1</v>
@@ -47631,7 +47631,7 @@
         <v>135.5102517306261</v>
       </c>
       <c r="L613" t="n">
-        <v>3.477051460361613</v>
+        <v>3.342618384401114</v>
       </c>
       <c r="M613" t="n">
         <v>1</v>
@@ -47708,7 +47708,7 @@
         <v>130.05032603184</v>
       </c>
       <c r="L614" t="n">
-        <v>2.920723226703755</v>
+        <v>2.785515320334262</v>
       </c>
       <c r="M614" t="n">
         <v>1</v>
@@ -47785,7 +47785,7 @@
         <v>218.8925968565838</v>
       </c>
       <c r="L615" t="n">
-        <v>2.781641168289291</v>
+        <v>2.646239554317549</v>
       </c>
       <c r="M615" t="n">
         <v>1</v>
@@ -47862,7 +47862,7 @@
         <v>117.0366385887776</v>
       </c>
       <c r="L616" t="n">
-        <v>2.225312934631432</v>
+        <v>2.089136490250696</v>
       </c>
       <c r="M616" t="n">
         <v>1</v>
@@ -47939,7 +47939,7 @@
         <v>114.1129029363632</v>
       </c>
       <c r="L617" t="n">
-        <v>1.808066759388039</v>
+        <v>1.81058495821727</v>
       </c>
       <c r="M617" t="n">
         <v>1</v>
@@ -48016,7 +48016,7 @@
         <v>30.23531383751219</v>
       </c>
       <c r="L618" t="n">
-        <v>52.43393602225312</v>
+        <v>52.36768802228412</v>
       </c>
       <c r="M618" t="n">
         <v>0</v>
@@ -48093,7 +48093,7 @@
         <v>25.64797795459033</v>
       </c>
       <c r="L619" t="n">
-        <v>49.65229485396384</v>
+        <v>49.58217270194986</v>
       </c>
       <c r="M619" t="n">
         <v>0</v>
@@ -48170,7 +48170,7 @@
         <v>26.18361682775174</v>
       </c>
       <c r="L620" t="n">
-        <v>42.00278164116829</v>
+        <v>41.92200557103064</v>
       </c>
       <c r="M620" t="n">
         <v>0</v>
@@ -48247,7 +48247,7 @@
         <v>25.48658299732234</v>
       </c>
       <c r="L621" t="n">
-        <v>41.30737134909597</v>
+        <v>41.22562674094708</v>
       </c>
       <c r="M621" t="n">
         <v>0</v>
@@ -48324,7 +48324,7 @@
         <v>30.49095679572507</v>
       </c>
       <c r="L622" t="n">
-        <v>39.63838664812239</v>
+        <v>39.55431754874652</v>
       </c>
       <c r="M622" t="n">
         <v>0</v>
@@ -48401,7 +48401,7 @@
         <v>32.41567129676086</v>
       </c>
       <c r="L623" t="n">
-        <v>38.10848400556328</v>
+        <v>38.02228412256267</v>
       </c>
       <c r="M623" t="n">
         <v>0</v>
@@ -48478,7 +48478,7 @@
         <v>64.91209697307691</v>
       </c>
       <c r="L624" t="n">
-        <v>37.55215577190543</v>
+        <v>37.46518105849582</v>
       </c>
       <c r="M624" t="n">
         <v>0</v>
@@ -48555,7 +48555,7 @@
         <v>34.41771962890689</v>
       </c>
       <c r="L625" t="n">
-        <v>37.41307371349096</v>
+        <v>37.32590529247911</v>
       </c>
       <c r="M625" t="n">
         <v>0</v>
@@ -48632,7 +48632,7 @@
         <v>25.55351605923581</v>
       </c>
       <c r="L626" t="n">
-        <v>36.02225312934632</v>
+        <v>35.93314763231198</v>
       </c>
       <c r="M626" t="n">
         <v>0</v>
@@ -48709,7 +48709,7 @@
         <v>51.14285714285713</v>
       </c>
       <c r="L627" t="n">
-        <v>35.60500695410292</v>
+        <v>35.51532033426184</v>
       </c>
       <c r="M627" t="n">
         <v>0</v>
@@ -48786,7 +48786,7 @@
         <v>65.1567944250871</v>
       </c>
       <c r="L628" t="n">
-        <v>35.46592489568845</v>
+        <v>35.37604456824512</v>
       </c>
       <c r="M628" t="n">
         <v>0</v>
@@ -48863,7 +48863,7 @@
         <v>30.76687291769411</v>
       </c>
       <c r="L629" t="n">
-        <v>33.65785813630042</v>
+        <v>33.56545961002785</v>
       </c>
       <c r="M629" t="n">
         <v>0</v>
@@ -48940,7 +48940,7 @@
         <v>41.21450249874694</v>
       </c>
       <c r="L630" t="n">
-        <v>33.24061196105703</v>
+        <v>33.14763231197772</v>
       </c>
       <c r="M630" t="n">
         <v>0</v>
@@ -49017,7 +49017,7 @@
         <v>34.09136004417175</v>
       </c>
       <c r="L631" t="n">
-        <v>31.71070931849792</v>
+        <v>31.61559888579387</v>
       </c>
       <c r="M631" t="n">
         <v>0</v>
@@ -49094,7 +49094,7 @@
         <v>25.05357233546868</v>
       </c>
       <c r="L632" t="n">
-        <v>30.5980528511822</v>
+        <v>30.50139275766017</v>
       </c>
       <c r="M632" t="n">
         <v>0</v>
@@ -49171,7 +49171,7 @@
         <v>31.92547324544068</v>
       </c>
       <c r="L633" t="n">
-        <v>30.1808066759388</v>
+        <v>30.08356545961003</v>
       </c>
       <c r="M633" t="n">
         <v>0</v>
@@ -49248,7 +49248,7 @@
         <v>34.23231437886432</v>
       </c>
       <c r="L634" t="n">
-        <v>29.20723226703755</v>
+        <v>29.10863509749304</v>
       </c>
       <c r="M634" t="n">
         <v>0</v>
@@ -49325,7 +49325,7 @@
         <v>48.03881314711276</v>
       </c>
       <c r="L635" t="n">
-        <v>28.78998609179416</v>
+        <v>28.6908077994429</v>
       </c>
       <c r="M635" t="n">
         <v>0</v>
@@ -49402,7 +49402,7 @@
         <v>34.77453802712694</v>
       </c>
       <c r="L636" t="n">
-        <v>28.09457579972184</v>
+        <v>27.99442896935933</v>
       </c>
       <c r="M636" t="n">
         <v>0</v>
@@ -49479,7 +49479,7 @@
         <v>25.93437603195845</v>
       </c>
       <c r="L637" t="n">
-        <v>27.95549374130737</v>
+        <v>27.85515320334262</v>
       </c>
       <c r="M637" t="n">
         <v>0</v>
@@ -49556,7 +49556,7 @@
         <v>37.18059956018131</v>
       </c>
       <c r="L638" t="n">
-        <v>25.59109874826148</v>
+        <v>25.48746518105849</v>
       </c>
       <c r="M638" t="n">
         <v>0</v>
@@ -49633,7 +49633,7 @@
         <v>37.18977997357062</v>
       </c>
       <c r="L639" t="n">
-        <v>23.78303198887344</v>
+        <v>23.67688022284123</v>
       </c>
       <c r="M639" t="n">
         <v>0</v>
@@ -49710,7 +49710,7 @@
         <v>75.12195866282394</v>
       </c>
       <c r="L640" t="n">
-        <v>23.36578581363004</v>
+        <v>23.25905292479109</v>
       </c>
       <c r="M640" t="n">
         <v>0</v>
@@ -49787,7 +49787,7 @@
         <v>46.59707776077489</v>
       </c>
       <c r="L641" t="n">
-        <v>22.39221140472879</v>
+        <v>22.2841225626741</v>
       </c>
       <c r="M641" t="n">
         <v>0</v>
@@ -49864,7 +49864,7 @@
         <v>25.56370768289145</v>
       </c>
       <c r="L642" t="n">
-        <v>21.9749652294854</v>
+        <v>21.86629526462395</v>
       </c>
       <c r="M642" t="n">
         <v>0</v>
@@ -49941,7 +49941,7 @@
         <v>43.70408453593028</v>
       </c>
       <c r="L643" t="n">
-        <v>21.557719054242</v>
+        <v>21.44846796657382</v>
       </c>
       <c r="M643" t="n">
         <v>0</v>
@@ -50018,7 +50018,7 @@
         <v>45.8852867830424</v>
       </c>
       <c r="L644" t="n">
-        <v>21.00139082058415</v>
+        <v>20.89136490250696</v>
       </c>
       <c r="M644" t="n">
         <v>0</v>
@@ -50083,7 +50083,7 @@
         <v>-0.4524468136095527</v>
       </c>
       <c r="H645" t="n">
-        <v>294.6532543042141</v>
+        <v>294.6532203195111</v>
       </c>
       <c r="I645" t="n">
         <v>213.7350670269712</v>
@@ -50092,10 +50092,10 @@
         <v>3.445826264725671</v>
       </c>
       <c r="K645" t="n">
-        <v>33.26695891915173</v>
+        <v>33.26694354841357</v>
       </c>
       <c r="L645" t="n">
-        <v>20.86230876216968</v>
+        <v>20.75208913649025</v>
       </c>
       <c r="M645" t="n">
         <v>0</v>
@@ -50172,7 +50172,7 @@
         <v>31.28647214854112</v>
       </c>
       <c r="L646" t="n">
-        <v>20.72322670375522</v>
+        <v>20.61281337047354</v>
       </c>
       <c r="M646" t="n">
         <v>0</v>
@@ -50249,7 +50249,7 @@
         <v>42.98527603281293</v>
       </c>
       <c r="L647" t="n">
-        <v>20.44506258692628</v>
+        <v>20.33426183844011</v>
       </c>
       <c r="M647" t="n">
         <v>0</v>
@@ -50326,7 +50326,7 @@
         <v>43.75532310388828</v>
       </c>
       <c r="L648" t="n">
-        <v>20.02781641168289</v>
+        <v>19.91643454038997</v>
       </c>
       <c r="M648" t="n">
         <v>0</v>
@@ -50403,7 +50403,7 @@
         <v>32.96631187523404</v>
       </c>
       <c r="L649" t="n">
-        <v>19.6105702364395</v>
+        <v>19.49860724233983</v>
       </c>
       <c r="M649" t="n">
         <v>0</v>
@@ -50480,7 +50480,7 @@
         <v>48.53280087664614</v>
       </c>
       <c r="L650" t="n">
-        <v>19.47148817802503</v>
+        <v>19.35933147632312</v>
       </c>
       <c r="M650" t="n">
         <v>0</v>
@@ -50557,7 +50557,7 @@
         <v>38.86897610629407</v>
       </c>
       <c r="L651" t="n">
-        <v>19.33240611961057</v>
+        <v>19.22005571030641</v>
       </c>
       <c r="M651" t="n">
         <v>0</v>
@@ -50634,7 +50634,7 @@
         <v>34.83283807117657</v>
       </c>
       <c r="L652" t="n">
-        <v>17.38525730180807</v>
+        <v>17.27019498607242</v>
       </c>
       <c r="M652" t="n">
         <v>0</v>
@@ -50711,7 +50711,7 @@
         <v>42.65987069287667</v>
       </c>
       <c r="L653" t="n">
-        <v>15.71627260083449</v>
+        <v>15.59888579387187</v>
       </c>
       <c r="M653" t="n">
         <v>0</v>
@@ -50788,7 +50788,7 @@
         <v>42.73342991562381</v>
       </c>
       <c r="L654" t="n">
-        <v>15.57719054242003</v>
+        <v>15.45961002785515</v>
       </c>
       <c r="M654" t="n">
         <v>0</v>
@@ -50865,7 +50865,7 @@
         <v>57.76293823038397</v>
       </c>
       <c r="L655" t="n">
-        <v>15.43810848400556</v>
+        <v>15.32033426183844</v>
       </c>
       <c r="M655" t="n">
         <v>0</v>
@@ -50942,7 +50942,7 @@
         <v>36.87426823051388</v>
       </c>
       <c r="L656" t="n">
-        <v>15.2990264255911</v>
+        <v>15.18105849582173</v>
       </c>
       <c r="M656" t="n">
         <v>0</v>
@@ -51019,7 +51019,7 @@
         <v>40.26350195498721</v>
       </c>
       <c r="L657" t="n">
-        <v>14.74269819193324</v>
+        <v>14.62395543175488</v>
       </c>
       <c r="M657" t="n">
         <v>0</v>
@@ -51096,7 +51096,7 @@
         <v>47.28251599635329</v>
       </c>
       <c r="L658" t="n">
-        <v>14.32545201668985</v>
+        <v>14.20612813370473</v>
       </c>
       <c r="M658" t="n">
         <v>0</v>
@@ -51173,7 +51173,7 @@
         <v>40.15460982985823</v>
       </c>
       <c r="L659" t="n">
-        <v>14.04728789986092</v>
+        <v>13.92757660167131</v>
       </c>
       <c r="M659" t="n">
         <v>0</v>
@@ -51250,7 +51250,7 @@
         <v>48.28223368228404</v>
       </c>
       <c r="L660" t="n">
-        <v>13.90820584144645</v>
+        <v>13.7883008356546</v>
       </c>
       <c r="M660" t="n">
         <v>0</v>
@@ -51327,7 +51327,7 @@
         <v>36.79543035303525</v>
       </c>
       <c r="L661" t="n">
-        <v>13.76912378303199</v>
+        <v>13.64902506963788</v>
       </c>
       <c r="M661" t="n">
         <v>0</v>
@@ -51404,7 +51404,7 @@
         <v>54.76973749941583</v>
       </c>
       <c r="L662" t="n">
-        <v>13.35187760778859</v>
+        <v>13.23119777158774</v>
       </c>
       <c r="M662" t="n">
         <v>0</v>
@@ -51481,7 +51481,7 @@
         <v>66.37178139664164</v>
       </c>
       <c r="L663" t="n">
-        <v>13.07371349095967</v>
+        <v>12.95264623955432</v>
       </c>
       <c r="M663" t="n">
         <v>0</v>
@@ -51546,7 +51546,7 @@
         <v>-1.306873873971781</v>
       </c>
       <c r="H664" t="n">
-        <v>263.220498300555</v>
+        <v>263.2205288662585</v>
       </c>
       <c r="I664" t="n">
         <v>167.0916913788894</v>
@@ -51555,10 +51555,10 @@
         <v>5.57077520777971</v>
       </c>
       <c r="K664" t="n">
-        <v>49.21797472114364</v>
+        <v>49.21799204864055</v>
       </c>
       <c r="L664" t="n">
-        <v>12.79554937413074</v>
+        <v>12.67409470752089</v>
       </c>
       <c r="M664" t="n">
         <v>0</v>
@@ -51635,7 +51635,7 @@
         <v>58.56088764339577</v>
       </c>
       <c r="L665" t="n">
-        <v>12.65646731571627</v>
+        <v>12.53481894150418</v>
       </c>
       <c r="M665" t="n">
         <v>0</v>
@@ -51712,7 +51712,7 @@
         <v>47.61499707208878</v>
       </c>
       <c r="L666" t="n">
-        <v>12.51738525730181</v>
+        <v>12.39554317548746</v>
       </c>
       <c r="M666" t="n">
         <v>0</v>
@@ -51789,7 +51789,7 @@
         <v>46.3350369487252</v>
       </c>
       <c r="L667" t="n">
-        <v>12.10013908205841</v>
+        <v>11.97771587743733</v>
       </c>
       <c r="M667" t="n">
         <v>0</v>
@@ -51866,7 +51866,7 @@
         <v>36.2310776009575</v>
       </c>
       <c r="L668" t="n">
-        <v>11.96105702364395</v>
+        <v>11.83844011142061</v>
       </c>
       <c r="M668" t="n">
         <v>0</v>
@@ -51943,7 +51943,7 @@
         <v>40.9768513022093</v>
       </c>
       <c r="L669" t="n">
-        <v>11.54381084840056</v>
+        <v>11.42061281337047</v>
       </c>
       <c r="M669" t="n">
         <v>0</v>
@@ -52020,7 +52020,7 @@
         <v>57.99485069244555</v>
       </c>
       <c r="L670" t="n">
-        <v>11.40472878998609</v>
+        <v>11.28133704735376</v>
       </c>
       <c r="M670" t="n">
         <v>0</v>
@@ -52097,7 +52097,7 @@
         <v>57.71091157356194</v>
       </c>
       <c r="L671" t="n">
-        <v>11.26564673157163</v>
+        <v>11.14206128133705</v>
       </c>
       <c r="M671" t="n">
         <v>0</v>
@@ -52174,7 +52174,7 @@
         <v>61.20493214905422</v>
       </c>
       <c r="L672" t="n">
-        <v>10.43115438108484</v>
+        <v>10.30640668523677</v>
       </c>
       <c r="M672" t="n">
         <v>0</v>
@@ -52251,7 +52251,7 @@
         <v>57.66431501964082</v>
       </c>
       <c r="L673" t="n">
-        <v>9.735744089012517</v>
+        <v>9.610027855153204</v>
       </c>
       <c r="M673" t="n">
         <v>0</v>
@@ -52328,7 +52328,7 @@
         <v>53.88448056322686</v>
       </c>
       <c r="L674" t="n">
-        <v>9.596662030598054</v>
+        <v>9.470752089136489</v>
       </c>
       <c r="M674" t="n">
         <v>0</v>
@@ -52405,7 +52405,7 @@
         <v>46.25687319945795</v>
       </c>
       <c r="L675" t="n">
-        <v>8.205841446453407</v>
+        <v>8.07799442896936</v>
       </c>
       <c r="M675" t="n">
         <v>0</v>
@@ -52482,7 +52482,7 @@
         <v>48.75800091059928</v>
       </c>
       <c r="L676" t="n">
-        <v>7.927677329624479</v>
+        <v>7.799442896935934</v>
       </c>
       <c r="M676" t="n">
         <v>0</v>
@@ -52559,7 +52559,7 @@
         <v>62.74407546310177</v>
       </c>
       <c r="L677" t="n">
-        <v>7.510431154381085</v>
+        <v>7.381615598885793</v>
       </c>
       <c r="M677" t="n">
         <v>0</v>
@@ -52636,7 +52636,7 @@
         <v>53.27420020459441</v>
       </c>
       <c r="L678" t="n">
-        <v>7.37134909596662</v>
+        <v>7.242339832869081</v>
       </c>
       <c r="M678" t="n">
         <v>0</v>
@@ -52713,7 +52713,7 @@
         <v>63.78312685845005</v>
       </c>
       <c r="L679" t="n">
-        <v>7.093184979137692</v>
+        <v>6.963788300835655</v>
       </c>
       <c r="M679" t="n">
         <v>0</v>
@@ -52790,7 +52790,7 @@
         <v>47.65776690712897</v>
       </c>
       <c r="L680" t="n">
-        <v>6.954102920723226</v>
+        <v>6.824512534818941</v>
       </c>
       <c r="M680" t="n">
         <v>0</v>
@@ -52867,7 +52867,7 @@
         <v>92.85366771087055</v>
       </c>
       <c r="L681" t="n">
-        <v>6.815020862308763</v>
+        <v>6.685236768802229</v>
       </c>
       <c r="M681" t="n">
         <v>0</v>
@@ -52944,7 +52944,7 @@
         <v>48.06432274483032</v>
       </c>
       <c r="L682" t="n">
-        <v>6.675938803894297</v>
+        <v>6.545961002785515</v>
       </c>
       <c r="M682" t="n">
         <v>0</v>
@@ -53021,7 +53021,7 @@
         <v>82.27682721510652</v>
       </c>
       <c r="L683" t="n">
-        <v>6.536856745479833</v>
+        <v>6.406685236768802</v>
       </c>
       <c r="M683" t="n">
         <v>0</v>
@@ -53098,7 +53098,7 @@
         <v>54.16238372479112</v>
       </c>
       <c r="L684" t="n">
-        <v>6.397774687065369</v>
+        <v>6.267409470752089</v>
       </c>
       <c r="M684" t="n">
         <v>0</v>
@@ -53175,7 +53175,7 @@
         <v>72.07618350074405</v>
       </c>
       <c r="L685" t="n">
-        <v>6.258692628650904</v>
+        <v>6.128133704735376</v>
       </c>
       <c r="M685" t="n">
         <v>0</v>
@@ -53252,7 +53252,7 @@
         <v>64.53612629962741</v>
       </c>
       <c r="L686" t="n">
-        <v>6.11961057023644</v>
+        <v>5.988857938718663</v>
       </c>
       <c r="M686" t="n">
         <v>0</v>
@@ -53329,7 +53329,7 @@
         <v>80.59758317845593</v>
       </c>
       <c r="L687" t="n">
-        <v>5.563282336578582</v>
+        <v>5.43175487465181</v>
       </c>
       <c r="M687" t="n">
         <v>0</v>
@@ -53406,7 +53406,7 @@
         <v>83.10370608443895</v>
       </c>
       <c r="L688" t="n">
-        <v>5.424200278164117</v>
+        <v>5.292479108635098</v>
       </c>
       <c r="M688" t="n">
         <v>0</v>
@@ -53483,7 +53483,7 @@
         <v>75.84291445026152</v>
       </c>
       <c r="L689" t="n">
-        <v>5.285118219749652</v>
+        <v>5.153203342618385</v>
       </c>
       <c r="M689" t="n">
         <v>0</v>
@@ -53560,7 +53560,7 @@
         <v>54.68261054358889</v>
       </c>
       <c r="L690" t="n">
-        <v>5.146036161335187</v>
+        <v>5.013927576601671</v>
       </c>
       <c r="M690" t="n">
         <v>0</v>
@@ -53637,7 +53637,7 @@
         <v>64.28266972404097</v>
       </c>
       <c r="L691" t="n">
-        <v>5.006954102920723</v>
+        <v>4.874651810584958</v>
       </c>
       <c r="M691" t="n">
         <v>0</v>
@@ -53714,7 +53714,7 @@
         <v>79.15093763819281</v>
       </c>
       <c r="L692" t="n">
-        <v>4.867872044506258</v>
+        <v>4.735376044568245</v>
       </c>
       <c r="M692" t="n">
         <v>0</v>
@@ -53791,7 +53791,7 @@
         <v>74.21981481637241</v>
       </c>
       <c r="L693" t="n">
-        <v>4.728789986091794</v>
+        <v>4.596100278551532</v>
       </c>
       <c r="M693" t="n">
         <v>0</v>
@@ -53868,7 +53868,7 @@
         <v>87.39916770937965</v>
       </c>
       <c r="L694" t="n">
-        <v>4.58970792767733</v>
+        <v>4.456824512534819</v>
       </c>
       <c r="M694" t="n">
         <v>0</v>
@@ -53945,7 +53945,7 @@
         <v>71.14105696350248</v>
       </c>
       <c r="L695" t="n">
-        <v>4.450625869262865</v>
+        <v>4.317548746518105</v>
       </c>
       <c r="M695" t="n">
         <v>0</v>
@@ -54022,7 +54022,7 @@
         <v>75.93302735994276</v>
       </c>
       <c r="L696" t="n">
-        <v>4.3115438108484</v>
+        <v>4.178272980501393</v>
       </c>
       <c r="M696" t="n">
         <v>0</v>
@@ -54099,7 +54099,7 @@
         <v>65.55291982718052</v>
       </c>
       <c r="L697" t="n">
-        <v>4.172461752433936</v>
+        <v>4.03899721448468</v>
       </c>
       <c r="M697" t="n">
         <v>0</v>
@@ -54176,7 +54176,7 @@
         <v>89.00103040801768</v>
       </c>
       <c r="L698" t="n">
-        <v>4.033379694019471</v>
+        <v>3.899721448467967</v>
       </c>
       <c r="M698" t="n">
         <v>0</v>
@@ -54253,7 +54253,7 @@
         <v>74.89331505611085</v>
       </c>
       <c r="L699" t="n">
-        <v>3.894297635605007</v>
+        <v>3.760445682451254</v>
       </c>
       <c r="M699" t="n">
         <v>0</v>
@@ -54330,7 +54330,7 @@
         <v>93.63891487371374</v>
       </c>
       <c r="L700" t="n">
-        <v>3.755215577190543</v>
+        <v>3.62116991643454</v>
       </c>
       <c r="M700" t="n">
         <v>0</v>
@@ -54407,7 +54407,7 @@
         <v>79.66258269718519</v>
       </c>
       <c r="L701" t="n">
-        <v>3.616133518776078</v>
+        <v>3.481894150417828</v>
       </c>
       <c r="M701" t="n">
         <v>0</v>
@@ -54484,7 +54484,7 @@
         <v>96.14910681987747</v>
       </c>
       <c r="L702" t="n">
-        <v>3.337969401947149</v>
+        <v>3.203342618384401</v>
       </c>
       <c r="M702" t="n">
         <v>0</v>
@@ -54561,7 +54561,7 @@
         <v>89.76925437398296</v>
       </c>
       <c r="L703" t="n">
-        <v>3.198887343532685</v>
+        <v>3.064066852367688</v>
       </c>
       <c r="M703" t="n">
         <v>0</v>
@@ -54638,7 +54638,7 @@
         <v>74.78606832310204</v>
       </c>
       <c r="L704" t="n">
-        <v>3.05980528511822</v>
+        <v>2.924791086350975</v>
       </c>
       <c r="M704" t="n">
         <v>0</v>
@@ -54715,7 +54715,7 @@
         <v>104.8659986731956</v>
       </c>
       <c r="L705" t="n">
-        <v>2.642559109874826</v>
+        <v>2.506963788300836</v>
       </c>
       <c r="M705" t="n">
         <v>0</v>
@@ -54792,7 +54792,7 @@
         <v>141.9919372262585</v>
       </c>
       <c r="L706" t="n">
-        <v>2.503477051460361</v>
+        <v>2.367688022284122</v>
       </c>
       <c r="M706" t="n">
         <v>0</v>
@@ -54869,7 +54869,7 @@
         <v>92.89142850060479</v>
       </c>
       <c r="L707" t="n">
-        <v>2.364394993045897</v>
+        <v>2.22841225626741</v>
       </c>
       <c r="M707" t="n">
         <v>0</v>
@@ -54946,7 +54946,7 @@
         <v>79.6583251953125</v>
       </c>
       <c r="L708" t="n">
-        <v>2.086230876216968</v>
+        <v>1.949860724233983</v>
       </c>
       <c r="M708" t="n">
         <v>0</v>
@@ -54987,7 +54987,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>RPOWER</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -54996,41 +54996,41 @@
         </is>
       </c>
       <c r="C709" t="n">
-        <v>663.6500244140625</v>
+        <v>22.17000007629395</v>
       </c>
       <c r="D709" t="n">
-        <v>715.0910021972657</v>
+        <v>23.00280002593994</v>
       </c>
       <c r="E709" t="n">
-        <v>740.3006656901042</v>
+        <v>24.80266665140788</v>
       </c>
       <c r="F709" t="n">
-        <v>753.6144995117188</v>
+        <v>25.71715001106262</v>
       </c>
       <c r="G709" t="n">
-        <v>-1.862569935999792</v>
+        <v>-0.2490171818795295</v>
       </c>
       <c r="H709" t="n">
-        <v>1348.301810738845</v>
+        <v>50.72999954223633</v>
       </c>
       <c r="I709" t="n">
-        <v>628.25</v>
+        <v>20.17000007629395</v>
       </c>
       <c r="J709" t="n">
-        <v>5.634703448318734</v>
+        <v>9.915716373004013</v>
       </c>
       <c r="K709" t="n">
-        <v>103.1645839129234</v>
+        <v>128.8227305713055</v>
       </c>
       <c r="L709" t="n">
-        <v>1.947148817802503</v>
+        <v>1.671309192200557</v>
       </c>
       <c r="M709" t="n">
         <v>0</v>
       </c>
       <c r="N709" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/RAYMONDLSL/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/RPOWER/?exchange=NSE</t>
         </is>
       </c>
       <c r="O709" t="b">
@@ -55064,7 +55064,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>RPOWER</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -55073,41 +55073,41 @@
         </is>
       </c>
       <c r="C710" t="n">
-        <v>22.17000007629395</v>
+        <v>260.7999877929688</v>
       </c>
       <c r="D710" t="n">
-        <v>23.00280002593994</v>
+        <v>267.525998840332</v>
       </c>
       <c r="E710" t="n">
-        <v>24.80266665140788</v>
+        <v>291.3356668090821</v>
       </c>
       <c r="F710" t="n">
-        <v>25.71715001106262</v>
+        <v>306.2406502532959</v>
       </c>
       <c r="G710" t="n">
-        <v>-0.2490171818795295</v>
+        <v>-0.3794802733509073</v>
       </c>
       <c r="H710" t="n">
-        <v>50.72999954223633</v>
+        <v>639.4000244140625</v>
       </c>
       <c r="I710" t="n">
-        <v>20.17000007629395</v>
+        <v>229.0500030517578</v>
       </c>
       <c r="J710" t="n">
-        <v>9.915716373004013</v>
+        <v>13.86159542378895</v>
       </c>
       <c r="K710" t="n">
-        <v>128.8227305713055</v>
+        <v>145.1687324930546</v>
       </c>
       <c r="L710" t="n">
-        <v>1.668984700973574</v>
+        <v>1.532033426183844</v>
       </c>
       <c r="M710" t="n">
         <v>0</v>
       </c>
       <c r="N710" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/RPOWER/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/AWFIS/?exchange=NSE</t>
         </is>
       </c>
       <c r="O710" t="b">
@@ -55141,7 +55141,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>FIRSTCRY</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -55150,41 +55150,41 @@
         </is>
       </c>
       <c r="C711" t="n">
-        <v>260.7999877929688</v>
+        <v>180.1600036621094</v>
       </c>
       <c r="D711" t="n">
-        <v>267.525998840332</v>
+        <v>199.4949993896484</v>
       </c>
       <c r="E711" t="n">
-        <v>291.3356668090821</v>
+        <v>211.957466023763</v>
       </c>
       <c r="F711" t="n">
-        <v>306.2406502532959</v>
+        <v>218.7851493835449</v>
       </c>
       <c r="G711" t="n">
-        <v>-0.3794802733509073</v>
+        <v>-2.75366273477804</v>
       </c>
       <c r="H711" t="n">
-        <v>639.4000244140625</v>
+        <v>438.7000122070312</v>
       </c>
       <c r="I711" t="n">
-        <v>229.0500030517578</v>
+        <v>168.1499938964844</v>
       </c>
       <c r="J711" t="n">
-        <v>13.86159542378895</v>
+        <v>7.142438419009722</v>
       </c>
       <c r="K711" t="n">
-        <v>145.1687324930546</v>
+        <v>143.5057744724597</v>
       </c>
       <c r="L711" t="n">
-        <v>1.52990264255911</v>
+        <v>1.392757660167131</v>
       </c>
       <c r="M711" t="n">
         <v>0</v>
       </c>
       <c r="N711" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/AWFIS/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/FIRSTCRY/?exchange=NSE</t>
         </is>
       </c>
       <c r="O711" t="b">
@@ -55218,7 +55218,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>FIRSTCRY</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -55227,41 +55227,41 @@
         </is>
       </c>
       <c r="C712" t="n">
-        <v>180.1600036621094</v>
+        <v>342.5</v>
       </c>
       <c r="D712" t="n">
-        <v>199.4949993896484</v>
+        <v>350.391000366211</v>
       </c>
       <c r="E712" t="n">
-        <v>211.957466023763</v>
+        <v>386.8879996744791</v>
       </c>
       <c r="F712" t="n">
-        <v>218.7851493835449</v>
+        <v>405.3592497253418</v>
       </c>
       <c r="G712" t="n">
-        <v>-2.75366273477804</v>
+        <v>-4.761409722017184</v>
       </c>
       <c r="H712" t="n">
-        <v>438.7000122070312</v>
+        <v>606.8956852082865</v>
       </c>
       <c r="I712" t="n">
-        <v>168.1499938964844</v>
+        <v>326.057353105007</v>
       </c>
       <c r="J712" t="n">
-        <v>7.142438419009722</v>
+        <v>5.042869525379978</v>
       </c>
       <c r="K712" t="n">
-        <v>143.5057744724597</v>
+        <v>77.19582049876979</v>
       </c>
       <c r="L712" t="n">
-        <v>1.390820584144645</v>
+        <v>1.253481894150418</v>
       </c>
       <c r="M712" t="n">
         <v>0</v>
       </c>
       <c r="N712" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/FIRSTCRY/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/PATANJALI/?exchange=NSE</t>
         </is>
       </c>
       <c r="O712" t="b">
@@ -55295,7 +55295,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -55304,41 +55304,41 @@
         </is>
       </c>
       <c r="C713" t="n">
-        <v>342.5</v>
+        <v>181.1100006103516</v>
       </c>
       <c r="D713" t="n">
-        <v>350.391000366211</v>
+        <v>192.9324002075195</v>
       </c>
       <c r="E713" t="n">
-        <v>386.8879996744791</v>
+        <v>202.6216664632161</v>
       </c>
       <c r="F713" t="n">
-        <v>405.3592497253418</v>
+        <v>214.310350189209</v>
       </c>
       <c r="G713" t="n">
-        <v>-4.761409722017184</v>
+        <v>-2.614158802173083</v>
       </c>
       <c r="H713" t="n">
-        <v>606.8956852082865</v>
+        <v>405.3999938964844</v>
       </c>
       <c r="I713" t="n">
-        <v>326.057353105007</v>
+        <v>154.3600006103516</v>
       </c>
       <c r="J713" t="n">
-        <v>5.042869525379978</v>
+        <v>17.32961900377585</v>
       </c>
       <c r="K713" t="n">
-        <v>77.19582049876979</v>
+        <v>123.8418599360952</v>
       </c>
       <c r="L713" t="n">
-        <v>1.251738525730181</v>
+        <v>1.114206128133705</v>
       </c>
       <c r="M713" t="n">
         <v>0</v>
       </c>
       <c r="N713" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/PATANJALI/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/ZAGGLE/?exchange=NSE</t>
         </is>
       </c>
       <c r="O713" t="b">
@@ -55372,7 +55372,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>KEC</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -55381,41 +55381,41 @@
         </is>
       </c>
       <c r="C714" t="n">
-        <v>181.1100006103516</v>
+        <v>410.1000061035156</v>
       </c>
       <c r="D714" t="n">
-        <v>192.9324002075195</v>
+        <v>439.6080004882813</v>
       </c>
       <c r="E714" t="n">
-        <v>202.6216664632161</v>
+        <v>480.0740002441406</v>
       </c>
       <c r="F714" t="n">
-        <v>214.310350189209</v>
+        <v>500.5692500305176</v>
       </c>
       <c r="G714" t="n">
-        <v>-2.614158802173083</v>
+        <v>-3.802171309899194</v>
       </c>
       <c r="H714" t="n">
-        <v>405.3999938964844</v>
+        <v>927.0025895267679</v>
       </c>
       <c r="I714" t="n">
-        <v>154.3600006103516</v>
+        <v>399.5499877929688</v>
       </c>
       <c r="J714" t="n">
-        <v>17.32961900377585</v>
+        <v>2.640475192809544</v>
       </c>
       <c r="K714" t="n">
-        <v>123.8418599360952</v>
+        <v>126.0430567496207</v>
       </c>
       <c r="L714" t="n">
-        <v>1.112656467315716</v>
+        <v>0.9749303621169917</v>
       </c>
       <c r="M714" t="n">
         <v>0</v>
       </c>
       <c r="N714" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/ZAGGLE/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/KEC/?exchange=NSE</t>
         </is>
       </c>
       <c r="O714" t="b">
@@ -55449,7 +55449,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>KEC</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -55458,41 +55458,41 @@
         </is>
       </c>
       <c r="C715" t="n">
-        <v>410.1000061035156</v>
+        <v>272.1000061035156</v>
       </c>
       <c r="D715" t="n">
-        <v>439.6080004882813</v>
+        <v>274.002001953125</v>
       </c>
       <c r="E715" t="n">
-        <v>480.0740002441406</v>
+        <v>285.862333984375</v>
       </c>
       <c r="F715" t="n">
-        <v>500.5692500305176</v>
+        <v>341.6392507934571</v>
       </c>
       <c r="G715" t="n">
-        <v>-3.802171309899194</v>
+        <v>-16.70910755460974</v>
       </c>
       <c r="H715" t="n">
-        <v>927.0025895267679</v>
+        <v>795</v>
       </c>
       <c r="I715" t="n">
-        <v>399.5499877929688</v>
+        <v>249.6999969482422</v>
       </c>
       <c r="J715" t="n">
-        <v>2.640475192809544</v>
+        <v>8.970768694048692</v>
       </c>
       <c r="K715" t="n">
-        <v>126.0430567496207</v>
+        <v>192.1719890361033</v>
       </c>
       <c r="L715" t="n">
-        <v>0.9735744089012517</v>
+        <v>0.8356545961002786</v>
       </c>
       <c r="M715" t="n">
         <v>0</v>
       </c>
       <c r="N715" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/KEC/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/VEDL/?exchange=NSE</t>
         </is>
       </c>
       <c r="O715" t="b">
@@ -55526,7 +55526,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -55535,41 +55535,41 @@
         </is>
       </c>
       <c r="C716" t="n">
-        <v>272.1000061035156</v>
+        <v>160.2899932861328</v>
       </c>
       <c r="D716" t="n">
-        <v>274.002001953125</v>
+        <v>177.4578009033203</v>
       </c>
       <c r="E716" t="n">
-        <v>285.862333984375</v>
+        <v>195.1630675252279</v>
       </c>
       <c r="F716" t="n">
-        <v>341.6392507934571</v>
+        <v>200.4887508392334</v>
       </c>
       <c r="G716" t="n">
-        <v>-16.70910755460974</v>
+        <v>-2.334221250983326</v>
       </c>
       <c r="H716" t="n">
-        <v>795</v>
+        <v>375.5949132544453</v>
       </c>
       <c r="I716" t="n">
-        <v>249.6999969482422</v>
+        <v>159.9499969482422</v>
       </c>
       <c r="J716" t="n">
-        <v>8.970768694048692</v>
+        <v>0.2125641415302137</v>
       </c>
       <c r="K716" t="n">
-        <v>192.1719890361033</v>
+        <v>134.3221217708661</v>
       </c>
       <c r="L716" t="n">
-        <v>0.8344923504867872</v>
+        <v>0.6963788300835655</v>
       </c>
       <c r="M716" t="n">
         <v>0</v>
       </c>
       <c r="N716" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/VEDL/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/CRIZAC/?exchange=NSE</t>
         </is>
       </c>
       <c r="O716" t="b">
@@ -55603,7 +55603,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -55612,41 +55612,41 @@
         </is>
       </c>
       <c r="C717" t="n">
-        <v>160.2899932861328</v>
+        <v>575.4500122070312</v>
       </c>
       <c r="D717" t="n">
-        <v>177.4578009033203</v>
+        <v>603.4859997558593</v>
       </c>
       <c r="E717" t="n">
-        <v>195.1630675252279</v>
+        <v>647.134668375651</v>
       </c>
       <c r="F717" t="n">
-        <v>200.4887508392334</v>
+        <v>668.6882513427735</v>
       </c>
       <c r="G717" t="n">
-        <v>-2.334221250983326</v>
+        <v>-2.163072445331893</v>
       </c>
       <c r="H717" t="n">
-        <v>375.5949132544453</v>
+        <v>1313.886868193049</v>
       </c>
       <c r="I717" t="n">
-        <v>159.9499969482422</v>
+        <v>538.453356900547</v>
       </c>
       <c r="J717" t="n">
-        <v>0.2125641415302137</v>
+        <v>6.870911812946057</v>
       </c>
       <c r="K717" t="n">
-        <v>134.3221217708661</v>
+        <v>128.3233713305315</v>
       </c>
       <c r="L717" t="n">
-        <v>0.6954102920723227</v>
+        <v>0.5571030640668524</v>
       </c>
       <c r="M717" t="n">
         <v>0</v>
       </c>
       <c r="N717" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/CRIZAC/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/KPITTECH/?exchange=NSE</t>
         </is>
       </c>
       <c r="O717" t="b">
@@ -55680,7 +55680,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -55689,41 +55689,41 @@
         </is>
       </c>
       <c r="C718" t="n">
-        <v>575.4500122070312</v>
+        <v>279.7999877929688</v>
       </c>
       <c r="D718" t="n">
-        <v>603.4859997558593</v>
+        <v>302.3000006103516</v>
       </c>
       <c r="E718" t="n">
-        <v>647.134668375651</v>
+        <v>362.2456669108073</v>
       </c>
       <c r="F718" t="n">
-        <v>668.6882513427735</v>
+        <v>373.0854998779297</v>
       </c>
       <c r="G718" t="n">
-        <v>-2.163072445331893</v>
+        <v>-1.373645438004034</v>
       </c>
       <c r="H718" t="n">
-        <v>1313.886868193049</v>
+        <v>844.7000122070312</v>
       </c>
       <c r="I718" t="n">
-        <v>538.453356900547</v>
+        <v>275.2000122070312</v>
       </c>
       <c r="J718" t="n">
-        <v>6.870911812946057</v>
+        <v>1.671502682375237</v>
       </c>
       <c r="K718" t="n">
-        <v>128.3233713305315</v>
+        <v>201.8942276838291</v>
       </c>
       <c r="L718" t="n">
-        <v>0.5563282336578581</v>
+        <v>0.4178272980501393</v>
       </c>
       <c r="M718" t="n">
         <v>0</v>
       </c>
       <c r="N718" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/KPITTECH/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/OSWALPUMPS/?exchange=NSE</t>
         </is>
       </c>
       <c r="O718" t="b">
@@ -55757,7 +55757,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>ALOKINDS</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -55766,41 +55766,41 @@
         </is>
       </c>
       <c r="C719" t="n">
-        <v>279.7999877929688</v>
+        <v>7.880000114440918</v>
       </c>
       <c r="D719" t="n">
-        <v>302.3000006103516</v>
+        <v>10.80740003585816</v>
       </c>
       <c r="E719" t="n">
-        <v>362.2456669108073</v>
+        <v>11.95620003382365</v>
       </c>
       <c r="F719" t="n">
-        <v>373.0854998779297</v>
+        <v>12.42615003585815</v>
       </c>
       <c r="G719" t="n">
-        <v>-1.373645438004034</v>
+        <v>-3.310858922060478</v>
       </c>
       <c r="H719" t="n">
-        <v>844.7000122070312</v>
+        <v>19.34000015258789</v>
       </c>
       <c r="I719" t="n">
-        <v>275.2000122070312</v>
+        <v>7.059999942779541</v>
       </c>
       <c r="J719" t="n">
-        <v>1.671502682375237</v>
+        <v>11.61473340378727</v>
       </c>
       <c r="K719" t="n">
-        <v>201.8942276838291</v>
+        <v>145.4314704532216</v>
       </c>
       <c r="L719" t="n">
-        <v>0.4172461752433936</v>
+        <v>0.2785515320334262</v>
       </c>
       <c r="M719" t="n">
         <v>0</v>
       </c>
       <c r="N719" t="inlineStr">
         <is>
-          <t>https://www.tradingview.com/symbols/OSWALPUMPS/?exchange=NSE</t>
+          <t>https://www.tradingview.com/symbols/ALOKINDS/?exchange=NSE</t>
         </is>
       </c>
       <c r="O719" t="b">
@@ -55828,83 +55828,6 @@
         <v>0</v>
       </c>
       <c r="W719" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
-        <is>
-          <t>ALOKINDS</t>
-        </is>
-      </c>
-      <c r="B720" t="inlineStr">
-        <is>
-          <t>4h</t>
-        </is>
-      </c>
-      <c r="C720" t="n">
-        <v>7.880000114440918</v>
-      </c>
-      <c r="D720" t="n">
-        <v>10.80740003585816</v>
-      </c>
-      <c r="E720" t="n">
-        <v>11.95620003382365</v>
-      </c>
-      <c r="F720" t="n">
-        <v>12.42615003585815</v>
-      </c>
-      <c r="G720" t="n">
-        <v>-3.310858922060478</v>
-      </c>
-      <c r="H720" t="n">
-        <v>19.34000015258789</v>
-      </c>
-      <c r="I720" t="n">
-        <v>7.059999942779541</v>
-      </c>
-      <c r="J720" t="n">
-        <v>11.61473340378727</v>
-      </c>
-      <c r="K720" t="n">
-        <v>145.4314704532216</v>
-      </c>
-      <c r="L720" t="n">
-        <v>0.2781641168289291</v>
-      </c>
-      <c r="M720" t="n">
-        <v>0</v>
-      </c>
-      <c r="N720" t="inlineStr">
-        <is>
-          <t>https://www.tradingview.com/symbols/ALOKINDS/?exchange=NSE</t>
-        </is>
-      </c>
-      <c r="O720" t="b">
-        <v>0</v>
-      </c>
-      <c r="P720" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q720" t="b">
-        <v>0</v>
-      </c>
-      <c r="R720" t="b">
-        <v>0</v>
-      </c>
-      <c r="S720" t="b">
-        <v>0</v>
-      </c>
-      <c r="T720" t="b">
-        <v>0</v>
-      </c>
-      <c r="U720" t="b">
-        <v>0</v>
-      </c>
-      <c r="V720" t="b">
-        <v>0</v>
-      </c>
-      <c r="W720" t="b">
         <v>0</v>
       </c>
     </row>

--- a/output/minervini_4h.xlsx
+++ b/output/minervini_4h.xlsx
@@ -1268,10 +1268,10 @@
         <v>798.8499755859375</v>
       </c>
       <c r="I11" t="n">
-        <v>262.0239102537355</v>
+        <v>262.023880250306</v>
       </c>
       <c r="J11" t="n">
-        <v>182.1498187234342</v>
+        <v>182.1498510314138</v>
       </c>
       <c r="K11" t="n">
         <v>8.054915295040544</v>
@@ -1807,10 +1807,10 @@
         <v>1489.699951171875</v>
       </c>
       <c r="I18" t="n">
-        <v>651.3127246301497</v>
+        <v>651.3127841620155</v>
       </c>
       <c r="J18" t="n">
-        <v>122.96508209578</v>
+        <v>122.9650617161289</v>
       </c>
       <c r="K18" t="n">
         <v>2.582289027742957</v>
@@ -7428,10 +7428,10 @@
         <v>609</v>
       </c>
       <c r="I91" t="n">
-        <v>326.9901756501101</v>
+        <v>327.0499877929688</v>
       </c>
       <c r="J91" t="n">
-        <v>80.73937506684877</v>
+        <v>80.70632076406577</v>
       </c>
       <c r="K91" t="n">
         <v>3.045685279187826</v>
@@ -9122,10 +9122,10 @@
         <v>2983.800048828125</v>
       </c>
       <c r="I113" t="n">
-        <v>1175.257587358084</v>
+        <v>1175.257470329055</v>
       </c>
       <c r="J113" t="n">
-        <v>109.2307274975949</v>
+        <v>109.2307483322371</v>
       </c>
       <c r="K113" t="n">
         <v>21.34201093241663</v>
@@ -9353,10 +9353,10 @@
         <v>844</v>
       </c>
       <c r="I116" t="n">
-        <v>399.8349725758499</v>
+        <v>399.8350028638013</v>
       </c>
       <c r="J116" t="n">
-        <v>97.33141273686969</v>
+        <v>97.33139778879307</v>
       </c>
       <c r="K116" t="n">
         <v>6.970849176172367</v>
@@ -9430,10 +9430,10 @@
         <v>2539.60009765625</v>
       </c>
       <c r="I117" t="n">
-        <v>1167.643424163666</v>
+        <v>1167.643304709368</v>
       </c>
       <c r="J117" t="n">
-        <v>95.11950323875426</v>
+        <v>95.11952320021268</v>
       </c>
       <c r="K117" t="n">
         <v>11.46907971856157</v>
@@ -10431,10 +10431,10 @@
         <v>12865.82946046676</v>
       </c>
       <c r="I130" t="n">
-        <v>6492.523033421498</v>
+        <v>6492.522559926718</v>
       </c>
       <c r="J130" t="n">
-        <v>79.49878560320568</v>
+        <v>79.49879869391691</v>
       </c>
       <c r="K130" t="n">
         <v>10.3983993518685</v>
@@ -13123,7 +13123,7 @@
         <v>4.78796537344095</v>
       </c>
       <c r="H165" t="n">
-        <v>209.3573902779376</v>
+        <v>209.3574059154358</v>
       </c>
       <c r="I165" t="n">
         <v>115.0300392216107</v>
@@ -13132,7 +13132,7 @@
         <v>48.22215236450007</v>
       </c>
       <c r="K165" t="n">
-        <v>22.79025822752938</v>
+        <v>22.79026739908259</v>
       </c>
       <c r="L165" t="n">
         <v>71.58774373259052</v>
@@ -18051,7 +18051,7 @@
         <v>5.56592835043388</v>
       </c>
       <c r="H229" t="n">
-        <v>1423.548053270148</v>
+        <v>1423.547927723126</v>
       </c>
       <c r="I229" t="n">
         <v>905.5050975494345</v>
@@ -18060,7 +18060,7 @@
         <v>45.7529120929187</v>
       </c>
       <c r="K229" t="n">
-        <v>7.860888059077009</v>
+        <v>7.86087854649804</v>
       </c>
       <c r="L229" t="n">
         <v>63.50974930362116</v>
@@ -20515,7 +20515,7 @@
         <v>0.6702086201100244</v>
       </c>
       <c r="H261" t="n">
-        <v>198.2251721274962</v>
+        <v>198.2251564414815</v>
       </c>
       <c r="I261" t="n">
         <v>164.6038301743624</v>
@@ -20524,7 +20524,7 @@
         <v>15.67166674967189</v>
       </c>
       <c r="K261" t="n">
-        <v>4.109862648034635</v>
+        <v>4.109854409581271</v>
       </c>
       <c r="L261" t="n">
         <v>51.39275766016713</v>
@@ -22520,10 +22520,10 @@
         <v>359.3387168134344</v>
       </c>
       <c r="I287" t="n">
-        <v>206.1211021779015</v>
+        <v>206.1210871445057</v>
       </c>
       <c r="J287" t="n">
-        <v>45.4484691888624</v>
+        <v>45.44847979711435</v>
       </c>
       <c r="K287" t="n">
         <v>19.85948347055337</v>
@@ -25138,10 +25138,10 @@
         <v>2765.379504159864</v>
       </c>
       <c r="I321" t="n">
-        <v>1963.170361427068</v>
+        <v>1963.170239604111</v>
       </c>
       <c r="J321" t="n">
-        <v>16.39336274101999</v>
+        <v>16.39336996371688</v>
       </c>
       <c r="K321" t="n">
         <v>21.02317304857171</v>
@@ -26293,10 +26293,10 @@
         <v>758.8333740234375</v>
       </c>
       <c r="I336" t="n">
-        <v>238.6845018119064</v>
+        <v>238.684486798652</v>
       </c>
       <c r="J336" t="n">
-        <v>118.5102023104845</v>
+        <v>118.5102160547764</v>
       </c>
       <c r="K336" t="n">
         <v>45.49580898938863</v>
@@ -26755,10 +26755,10 @@
         <v>1093.53919041171</v>
       </c>
       <c r="I342" t="n">
-        <v>491.2850236715819</v>
+        <v>491.2850813456647</v>
       </c>
       <c r="J342" t="n">
-        <v>54.78794906546609</v>
+        <v>54.78793089423857</v>
       </c>
       <c r="K342" t="n">
         <v>43.80158759389907</v>
@@ -28061,7 +28061,7 @@
         <v>2.187140415571798</v>
       </c>
       <c r="H359" t="n">
-        <v>561.4379586860567</v>
+        <v>561.4378970396333</v>
       </c>
       <c r="I359" t="n">
         <v>420.1655789001589</v>
@@ -28070,7 +28070,7 @@
         <v>20.90471602403978</v>
       </c>
       <c r="K359" t="n">
-        <v>10.51928320591669</v>
+        <v>10.51927107079396</v>
       </c>
       <c r="L359" t="n">
         <v>47.21448467966574</v>
@@ -28908,7 +28908,7 @@
         <v>3.453185077430687</v>
       </c>
       <c r="H370" t="n">
-        <v>1045.658313207837</v>
+        <v>1045.658437762529</v>
       </c>
       <c r="I370" t="n">
         <v>666.0087356197063</v>
@@ -28917,7 +28917,7 @@
         <v>29.8631651744466</v>
       </c>
       <c r="K370" t="n">
-        <v>20.89932751663768</v>
+        <v>20.89934191768852</v>
       </c>
       <c r="L370" t="n">
         <v>37.04735376044568</v>
@@ -31834,7 +31834,7 @@
         <v>1.497014507617345</v>
       </c>
       <c r="H408" t="n">
-        <v>3039.742679715149</v>
+        <v>3039.742428602358</v>
       </c>
       <c r="I408" t="n">
         <v>2053.692522278021</v>
@@ -31843,7 +31843,7 @@
         <v>20.51463269947789</v>
       </c>
       <c r="K408" t="n">
-        <v>22.81788604909691</v>
+        <v>22.81787590312558</v>
       </c>
       <c r="L408" t="n">
         <v>39.27576601671309</v>
@@ -33297,7 +33297,7 @@
         <v>-1.091562196651175</v>
       </c>
       <c r="H427" t="n">
-        <v>1766.733188761222</v>
+        <v>1766.733060850261</v>
       </c>
       <c r="I427" t="n">
         <v>919.3268967152227</v>
@@ -33306,7 +33306,7 @@
         <v>48.60872188699585</v>
       </c>
       <c r="K427" t="n">
-        <v>29.31732190780603</v>
+        <v>29.31731254527008</v>
       </c>
       <c r="L427" t="n">
         <v>75.90529247910864</v>
@@ -34917,10 +34917,10 @@
         <v>286.0804516993438</v>
       </c>
       <c r="I448" t="n">
-        <v>171.952833032562</v>
+        <v>171.9528178807998</v>
       </c>
       <c r="J448" t="n">
-        <v>27.27908970764499</v>
+        <v>27.2791009229453</v>
       </c>
       <c r="K448" t="n">
         <v>30.71390427740537</v>
@@ -35610,10 +35610,10 @@
         <v>386.0870554430863</v>
       </c>
       <c r="I457" t="n">
-        <v>282.670901059285</v>
+        <v>282.6708709611926</v>
       </c>
       <c r="J457" t="n">
-        <v>14.44404032665245</v>
+        <v>14.44405251236969</v>
       </c>
       <c r="K457" t="n">
         <v>19.34684866865111</v>
@@ -35915,7 +35915,7 @@
         <v>1.937363239293077</v>
       </c>
       <c r="H461" t="n">
-        <v>1341.921447537333</v>
+        <v>1341.921323996723</v>
       </c>
       <c r="I461" t="n">
         <v>885.652283987356</v>
@@ -35924,7 +35924,7 @@
         <v>23.81834218829759</v>
       </c>
       <c r="K461" t="n">
-        <v>22.37109952700069</v>
+        <v>22.37108826121443</v>
       </c>
       <c r="L461" t="n">
         <v>35.0974930362117</v>
@@ -36072,10 +36072,10 @@
         <v>45150.8475731383</v>
       </c>
       <c r="I463" t="n">
-        <v>29525.27549507192</v>
+        <v>29525.27356749276</v>
       </c>
       <c r="J463" t="n">
-        <v>22.94550818351841</v>
+        <v>22.94551621010616</v>
       </c>
       <c r="K463" t="n">
         <v>24.38250020148292</v>
@@ -37689,10 +37689,10 @@
         <v>272.3321550846217</v>
       </c>
       <c r="I484" t="n">
-        <v>150.869488714561</v>
+        <v>150.8694736101529</v>
       </c>
       <c r="J484" t="n">
-        <v>30.94761521487579</v>
+        <v>30.94762832479239</v>
       </c>
       <c r="K484" t="n">
         <v>37.84782266149374</v>
@@ -38610,7 +38610,7 @@
         <v>1.868406815897994</v>
       </c>
       <c r="H496" t="n">
-        <v>859.7877679261235</v>
+        <v>859.7877065596524</v>
       </c>
       <c r="I496" t="n">
         <v>502</v>
@@ -38619,7 +38619,7 @@
         <v>24.27290350317479</v>
       </c>
       <c r="K496" t="n">
-        <v>37.81963638270347</v>
+        <v>37.81962654596813</v>
       </c>
       <c r="L496" t="n">
         <v>40.38997214484679</v>
@@ -39457,7 +39457,7 @@
         <v>-1.391412847565288</v>
       </c>
       <c r="H507" t="n">
-        <v>23.83526224893035</v>
+        <v>23.83526024888653</v>
       </c>
       <c r="I507" t="n">
         <v>18.76000022888184</v>
@@ -39466,7 +39466,7 @@
         <v>4.744133149200302</v>
       </c>
       <c r="K507" t="n">
-        <v>21.29904687862339</v>
+        <v>21.29903670028312</v>
       </c>
       <c r="L507" t="n">
         <v>30.9192200557103</v>
@@ -41693,10 +41693,10 @@
         <v>872.0426229622601</v>
       </c>
       <c r="I536" t="n">
-        <v>406.1171468902937</v>
+        <v>406.117116732523</v>
       </c>
       <c r="J536" t="n">
-        <v>23.56040409407345</v>
+        <v>23.56041326952107</v>
       </c>
       <c r="K536" t="n">
         <v>73.78291035791038</v>
@@ -42309,10 +42309,10 @@
         <v>387.7999877929688</v>
       </c>
       <c r="I544" t="n">
-        <v>221.246969139635</v>
+        <v>221.2469540684675</v>
       </c>
       <c r="J544" t="n">
-        <v>23.41411448698288</v>
+        <v>23.41412289385472</v>
       </c>
       <c r="K544" t="n">
         <v>42.02527197584256</v>
@@ -42537,7 +42537,7 @@
         <v>-0.02402849407694418</v>
       </c>
       <c r="H547" t="n">
-        <v>87.39771312453149</v>
+        <v>87.39772087555167</v>
       </c>
       <c r="I547" t="n">
         <v>71.42454681386315</v>
@@ -42546,7 +42546,7 @@
         <v>6.7560151256014</v>
       </c>
       <c r="K547" t="n">
-        <v>14.61995163872982</v>
+        <v>14.61996180400218</v>
       </c>
       <c r="L547" t="n">
         <v>46.23955431754874</v>
@@ -42617,10 +42617,10 @@
         <v>472.8081629796919</v>
       </c>
       <c r="I548" t="n">
-        <v>366.4404365248346</v>
+        <v>366.44040619655</v>
       </c>
       <c r="J548" t="n">
-        <v>10.61825216334826</v>
+        <v>10.61826131862089</v>
       </c>
       <c r="K548" t="n">
         <v>16.6419528457955</v>
@@ -42771,10 +42771,10 @@
         <v>409.9712889887167</v>
       </c>
       <c r="I550" t="n">
-        <v>309.8384816659088</v>
+        <v>309.838511773213</v>
       </c>
       <c r="J550" t="n">
-        <v>7.313977983705233</v>
+        <v>7.3139675559035</v>
       </c>
       <c r="K550" t="n">
         <v>23.29963578608019</v>
@@ -44154,7 +44154,7 @@
         <v>-0.06088461488257257</v>
       </c>
       <c r="H568" t="n">
-        <v>155.8999783750524</v>
+        <v>155.8999606999571</v>
       </c>
       <c r="I568" t="n">
         <v>112.8155071321618</v>
@@ -44163,7 +44163,7 @@
         <v>5.402179793251238</v>
       </c>
       <c r="K568" t="n">
-        <v>31.10753811601292</v>
+        <v>31.10752325175028</v>
       </c>
       <c r="L568" t="n">
         <v>25.90529247910863</v>
@@ -44462,16 +44462,16 @@
         <v>0.9253055751860639</v>
       </c>
       <c r="H572" t="n">
-        <v>239.2186883393384</v>
+        <v>239.2187037807859</v>
       </c>
       <c r="I572" t="n">
-        <v>156.7443123050878</v>
+        <v>156.7442971017576</v>
       </c>
       <c r="J572" t="n">
-        <v>14.96429713985419</v>
+        <v>14.96430829075539</v>
       </c>
       <c r="K572" t="n">
-        <v>32.75177158190954</v>
+        <v>32.75178015097045</v>
       </c>
       <c r="L572" t="n">
         <v>24.09470752089137</v>
@@ -45771,7 +45771,7 @@
         <v>0.4879661801902468</v>
       </c>
       <c r="H589" t="n">
-        <v>408.5542740377988</v>
+        <v>408.554305468849</v>
       </c>
       <c r="I589" t="n">
         <v>243.9284560598348</v>
@@ -45780,7 +45780,7 @@
         <v>11.118641986764</v>
       </c>
       <c r="K589" t="n">
-        <v>50.73023148403812</v>
+        <v>50.73024308007263</v>
       </c>
       <c r="L589" t="n">
         <v>16.85236768802228</v>
@@ -48315,10 +48315,10 @@
         <v>306.197022156633</v>
       </c>
       <c r="I622" t="n">
-        <v>219.1296348793021</v>
+        <v>219.1296196581114</v>
       </c>
       <c r="J622" t="n">
-        <v>7.082729374204</v>
+        <v>7.082736812388979</v>
       </c>
       <c r="K622" t="n">
         <v>30.49095679572507</v>
@@ -49008,10 +49008,10 @@
         <v>476.8288845013619</v>
       </c>
       <c r="I631" t="n">
-        <v>317.6634042148347</v>
+        <v>317.6633741663369</v>
       </c>
       <c r="J631" t="n">
-        <v>11.94238977021871</v>
+        <v>11.94240035910281</v>
       </c>
       <c r="K631" t="n">
         <v>34.09136004417175</v>
@@ -50699,7 +50699,7 @@
         <v>-0.670059023922831</v>
       </c>
       <c r="H653" t="n">
-        <v>93.44221530383422</v>
+        <v>93.44222215601812</v>
       </c>
       <c r="I653" t="n">
         <v>62.68610889438828</v>
@@ -50708,7 +50708,7 @@
         <v>4.488859103302256</v>
       </c>
       <c r="K653" t="n">
-        <v>42.65987069287667</v>
+        <v>42.65988115422614</v>
       </c>
       <c r="L653" t="n">
         <v>15.59888579387187</v>
@@ -51472,10 +51472,10 @@
         <v>1282.80960014975</v>
       </c>
       <c r="I663" t="n">
-        <v>743.4273285628773</v>
+        <v>743.4272688553443</v>
       </c>
       <c r="J663" t="n">
-        <v>3.715582972109588</v>
+        <v>3.715591301911103</v>
       </c>
       <c r="K663" t="n">
         <v>66.37178139664164</v>
@@ -51546,7 +51546,7 @@
         <v>-1.306873873971781</v>
       </c>
       <c r="H664" t="n">
-        <v>263.2205288662585</v>
+        <v>263.220498300555</v>
       </c>
       <c r="I664" t="n">
         <v>167.0916913788894</v>
@@ -51555,7 +51555,7 @@
         <v>5.57077520777971</v>
       </c>
       <c r="K664" t="n">
-        <v>49.21799204864055</v>
+        <v>49.21797472114364</v>
       </c>
       <c r="L664" t="n">
         <v>12.67409470752089</v>
@@ -52624,7 +52624,7 @@
         <v>-1.130736103623231</v>
       </c>
       <c r="H678" t="n">
-        <v>729.6618113637422</v>
+        <v>729.6617501297184</v>
       </c>
       <c r="I678" t="n">
         <v>470.7000122070312</v>
@@ -52633,7 +52633,7 @@
         <v>1.136599840066377</v>
       </c>
       <c r="K678" t="n">
-        <v>53.27420020459441</v>
+        <v>53.27418734165452</v>
       </c>
       <c r="L678" t="n">
         <v>7.242339832869081</v>

--- a/output/minervini_4h.xlsx
+++ b/output/minervini_4h.xlsx
@@ -1268,10 +1268,10 @@
         <v>812.7999877929688</v>
       </c>
       <c r="I11" t="n">
-        <v>262.023880250306</v>
+        <v>262.0239102537355</v>
       </c>
       <c r="J11" t="n">
-        <v>207.1857510258829</v>
+        <v>207.185715851131</v>
       </c>
       <c r="K11" t="n">
         <v>0.9814838041106055</v>
@@ -1576,10 +1576,10 @@
         <v>1981.800048828125</v>
       </c>
       <c r="I15" t="n">
-        <v>821.6033372206257</v>
+        <v>821.6033975811163</v>
       </c>
       <c r="J15" t="n">
-        <v>139.6533595714039</v>
+        <v>139.6533419648623</v>
       </c>
       <c r="K15" t="n">
         <v>0.6500786606462583</v>
@@ -14974,10 +14974,10 @@
         <v>2983.800048828125</v>
       </c>
       <c r="I189" t="n">
-        <v>1175.257587358084</v>
+        <v>1175.257470329055</v>
       </c>
       <c r="J189" t="n">
-        <v>106.5419469276021</v>
+        <v>106.5419674945026</v>
       </c>
       <c r="K189" t="n">
         <v>22.92165151474006</v>
@@ -18590,7 +18590,7 @@
         <v>4.734258279664272</v>
       </c>
       <c r="H236" t="n">
-        <v>1423.547927723126</v>
+        <v>1423.548053270148</v>
       </c>
       <c r="I236" t="n">
         <v>905.5050975494345</v>
@@ -18599,7 +18599,7 @@
         <v>38.13285559773889</v>
       </c>
       <c r="K236" t="n">
-        <v>13.81099073803589</v>
+        <v>13.81100077537336</v>
       </c>
       <c r="L236" t="n">
         <v>57.30180806675938</v>
@@ -19206,7 +19206,7 @@
         <v>1.167893784225127</v>
       </c>
       <c r="H244" t="n">
-        <v>6552.654707500795</v>
+        <v>6552.654210942315</v>
       </c>
       <c r="I244" t="n">
         <v>4229.809203861739</v>
@@ -19215,7 +19215,7 @@
         <v>30.40777335686897</v>
       </c>
       <c r="K244" t="n">
-        <v>18.79359513235668</v>
+        <v>18.79358613020876</v>
       </c>
       <c r="L244" t="n">
         <v>53.40751043115438</v>
@@ -23829,10 +23829,10 @@
         <v>2295</v>
       </c>
       <c r="I304" t="n">
-        <v>1174.091384580817</v>
+        <v>1174.091262727543</v>
       </c>
       <c r="J304" t="n">
-        <v>65.6515029371794</v>
+        <v>65.65152012935054</v>
       </c>
       <c r="K304" t="n">
         <v>18.0009240162055</v>
@@ -23903,7 +23903,7 @@
         <v>-0.7562071761744504</v>
       </c>
       <c r="H305" t="n">
-        <v>1766.733060850261</v>
+        <v>1766.733188761222</v>
       </c>
       <c r="I305" t="n">
         <v>941.3310566553616</v>
@@ -23912,7 +23912,7 @@
         <v>50.21282788906125</v>
       </c>
       <c r="K305" t="n">
-        <v>24.94576102194206</v>
+        <v>24.94577006797893</v>
       </c>
       <c r="L305" t="n">
         <v>78.02503477051459</v>
@@ -23983,10 +23983,10 @@
         <v>359.3387168134344</v>
       </c>
       <c r="I306" t="n">
-        <v>206.1210871445057</v>
+        <v>206.1211021779015</v>
       </c>
       <c r="J306" t="n">
-        <v>47.97127466447581</v>
+        <v>47.97126387222441</v>
       </c>
       <c r="K306" t="n">
         <v>17.8159727257162</v>
@@ -27448,10 +27448,10 @@
         <v>1093.53919041171</v>
       </c>
       <c r="I351" t="n">
-        <v>491.2850236715819</v>
+        <v>491.2850813456647</v>
       </c>
       <c r="J351" t="n">
-        <v>46.35088906773652</v>
+        <v>46.35087188697202</v>
       </c>
       <c r="K351" t="n">
         <v>52.09168155934773</v>
@@ -28674,7 +28674,7 @@
         <v>352.1795004272461</v>
       </c>
       <c r="G367" t="n">
-        <v>2.055944153445211</v>
+        <v>2.057644732547237</v>
       </c>
       <c r="H367" t="n">
         <v>428.7550602808859</v>
@@ -33377,10 +33377,10 @@
         <v>2765.379504159864</v>
       </c>
       <c r="I428" t="n">
-        <v>1963.170361427068</v>
+        <v>1963.170239604111</v>
       </c>
       <c r="J428" t="n">
-        <v>10.28080102157911</v>
+        <v>10.28080786496588</v>
       </c>
       <c r="K428" t="n">
         <v>27.73115492655261</v>
@@ -33451,7 +33451,7 @@
         <v>1.113228537833733</v>
       </c>
       <c r="H429" t="n">
-        <v>1341.921447537333</v>
+        <v>1341.921323996723</v>
       </c>
       <c r="I429" t="n">
         <v>885.652283987356</v>
@@ -33460,7 +33460,7 @@
         <v>22.49728748280979</v>
       </c>
       <c r="K429" t="n">
-        <v>23.69079337629138</v>
+        <v>23.69078198901084</v>
       </c>
       <c r="L429" t="n">
         <v>37.41307371349096</v>
@@ -34221,7 +34221,7 @@
         <v>1.496835511224126</v>
       </c>
       <c r="H439" t="n">
-        <v>796.6711586352184</v>
+        <v>796.6710965617623</v>
       </c>
       <c r="I439" t="n">
         <v>553.7186859929476</v>
@@ -34230,7 +34230,7 @@
         <v>20.85559493210862</v>
       </c>
       <c r="K439" t="n">
-        <v>19.04828812058528</v>
+        <v>19.04827884481495</v>
       </c>
       <c r="L439" t="n">
         <v>32.5452016689847</v>
@@ -34606,7 +34606,7 @@
         <v>2.730303167690584</v>
       </c>
       <c r="H444" t="n">
-        <v>1045.658437762529</v>
+        <v>1045.658313207837</v>
       </c>
       <c r="I444" t="n">
         <v>666.0087356197063</v>
@@ -34615,7 +34615,7 @@
         <v>22.20560795749122</v>
       </c>
       <c r="K444" t="n">
-        <v>28.4750468603699</v>
+        <v>28.4750315569311</v>
       </c>
       <c r="L444" t="n">
         <v>28.2336578581363</v>
@@ -36146,7 +36146,7 @@
         <v>1.428076696871261</v>
       </c>
       <c r="H464" t="n">
-        <v>848.8262434052705</v>
+        <v>848.8263047717415</v>
       </c>
       <c r="I464" t="n">
         <v>495.5999980879241</v>
@@ -36155,7 +36155,7 @@
         <v>24.09201016398978</v>
       </c>
       <c r="K464" t="n">
-        <v>38.02052738297081</v>
+        <v>38.02053736125879</v>
       </c>
       <c r="L464" t="n">
         <v>47.14881780250348</v>
@@ -36377,7 +36377,7 @@
         <v>-0.3915922555835727</v>
       </c>
       <c r="H467" t="n">
-        <v>87.39771312453149</v>
+        <v>87.39772087555167</v>
       </c>
       <c r="I467" t="n">
         <v>71.42454681386315</v>
@@ -36386,7 +36386,7 @@
         <v>6.93802153546601</v>
       </c>
       <c r="K467" t="n">
-        <v>14.42487073488403</v>
+        <v>14.42488088285532</v>
       </c>
       <c r="L467" t="n">
         <v>43.81084840055633</v>
@@ -37070,7 +37070,7 @@
         <v>0.2257809181191783</v>
       </c>
       <c r="H476" t="n">
-        <v>45150.85152546577</v>
+        <v>45150.8475731383</v>
       </c>
       <c r="I476" t="n">
         <v>29525.27549507192</v>
@@ -37079,7 +37079,7 @@
         <v>19.77872994242777</v>
       </c>
       <c r="K476" t="n">
-        <v>27.67100671699638</v>
+        <v>27.67099554117998</v>
       </c>
       <c r="L476" t="n">
         <v>36.02225312934632</v>
@@ -37378,7 +37378,7 @@
         <v>0.6258221333816261</v>
       </c>
       <c r="H480" t="n">
-        <v>3039.742428602358</v>
+        <v>3039.742679715149</v>
       </c>
       <c r="I480" t="n">
         <v>2053.692522278021</v>
@@ -37387,7 +37387,7 @@
         <v>13.89241449861769</v>
       </c>
       <c r="K480" t="n">
-        <v>29.9590606499512</v>
+        <v>29.95907138585501</v>
       </c>
       <c r="L480" t="n">
         <v>33.24061196105703</v>
@@ -37532,7 +37532,7 @@
         <v>1.093959384662413</v>
       </c>
       <c r="H482" t="n">
-        <v>272.0997840702363</v>
+        <v>272.099752952214</v>
       </c>
       <c r="I482" t="n">
         <v>173.9540675101702</v>
@@ -37541,7 +37541,7 @@
         <v>20.38235533059107</v>
       </c>
       <c r="K482" t="n">
-        <v>29.93638284314208</v>
+        <v>29.93636798328736</v>
       </c>
       <c r="L482" t="n">
         <v>32.82336578581363</v>
@@ -39768,10 +39768,10 @@
         <v>872.0425606177564</v>
       </c>
       <c r="I511" t="n">
-        <v>406.1171468902937</v>
+        <v>406.117116732523</v>
       </c>
       <c r="J511" t="n">
-        <v>21.52897053772853</v>
+        <v>21.52897956232433</v>
       </c>
       <c r="K511" t="n">
         <v>76.68778891421132</v>
@@ -40769,10 +40769,10 @@
         <v>409.9712889887167</v>
       </c>
       <c r="I524" t="n">
-        <v>309.8384816659088</v>
+        <v>309.838511773213</v>
       </c>
       <c r="J524" t="n">
-        <v>7.604449939172286</v>
+        <v>7.604439483145109</v>
       </c>
       <c r="K524" t="n">
         <v>22.96679558908645</v>
@@ -44231,7 +44231,7 @@
         <v>-0.1040948054730095</v>
       </c>
       <c r="H569" t="n">
-        <v>124.8273017901132</v>
+        <v>124.8273096544699</v>
       </c>
       <c r="I569" t="n">
         <v>76.65010804466255</v>
@@ -44240,7 +44240,7 @@
         <v>8.153796048890971</v>
       </c>
       <c r="K569" t="n">
-        <v>50.57575330821413</v>
+        <v>50.57576279477218</v>
       </c>
       <c r="L569" t="n">
         <v>14.60361613351878</v>
@@ -44302,10 +44302,10 @@
         <v>1207.062000325521</v>
       </c>
       <c r="F570" t="n">
-        <v>1213.843000488281</v>
+        <v>1213.849500732422</v>
       </c>
       <c r="G570" t="n">
-        <v>-0.7207672150070565</v>
+        <v>-0.7207633830707882</v>
       </c>
       <c r="H570" t="n">
         <v>1608.140814494163</v>
@@ -47391,10 +47391,10 @@
         <v>555.1842484654879</v>
       </c>
       <c r="I610" t="n">
-        <v>379.7399306767125</v>
+        <v>379.7398698331913</v>
       </c>
       <c r="J610" t="n">
-        <v>9.680327601519156</v>
+        <v>9.680345174963145</v>
       </c>
       <c r="K610" t="n">
         <v>33.29753864717597</v>
@@ -48001,10 +48001,10 @@
         <v>1067.022500610351</v>
       </c>
       <c r="G618" t="n">
-        <v>-1.738917251107475</v>
+        <v>-1.740726971624584</v>
       </c>
       <c r="H618" t="n">
-        <v>1400.476774401248</v>
+        <v>1400.476649260813</v>
       </c>
       <c r="I618" t="n">
         <v>941.5197177909594</v>
@@ -48013,7 +48013,7 @@
         <v>6.211264735511857</v>
       </c>
       <c r="K618" t="n">
-        <v>40.04767744012483</v>
+        <v>40.04766492608125</v>
       </c>
       <c r="L618" t="n">
         <v>23.64394993045897</v>
@@ -48931,10 +48931,10 @@
         <v>1282.80960014975</v>
       </c>
       <c r="I630" t="n">
-        <v>743.4272688553443</v>
+        <v>743.4273285628773</v>
       </c>
       <c r="J630" t="n">
-        <v>2.975774479148008</v>
+        <v>2.975766208764052</v>
       </c>
       <c r="K630" t="n">
         <v>67.56705905619663</v>
@@ -50006,7 +50006,7 @@
         <v>-3.454114502984706</v>
       </c>
       <c r="H644" t="n">
-        <v>3859.801118967803</v>
+        <v>3859.800859322344</v>
       </c>
       <c r="I644" t="n">
         <v>2401.113876815865</v>
@@ -50015,7 +50015,7 @@
         <v>9.32426093347274</v>
       </c>
       <c r="K644" t="n">
-        <v>47.04004262734487</v>
+        <v>47.04003273608927</v>
       </c>
       <c r="L644" t="n">
         <v>15.15994436717663</v>
@@ -50314,7 +50314,7 @@
         <v>-1.864524900783326</v>
       </c>
       <c r="H648" t="n">
-        <v>1486.026544311489</v>
+        <v>1486.026668543064</v>
       </c>
       <c r="I648" t="n">
         <v>863.7720549794727</v>
@@ -50323,7 +50323,7 @@
         <v>12.54705669277125</v>
       </c>
       <c r="K648" t="n">
-        <v>52.8597960183308</v>
+        <v>52.85980879738461</v>
       </c>
       <c r="L648" t="n">
         <v>13.76912378303199</v>
@@ -50927,7 +50927,7 @@
         <v>793.3935000610352</v>
       </c>
       <c r="G656" t="n">
-        <v>-3.671887008891817</v>
+        <v>-3.671916240405337</v>
       </c>
       <c r="H656" t="n">
         <v>1022.200012207031</v>
@@ -52470,7 +52470,7 @@
         <v>-1.713938762266543</v>
       </c>
       <c r="H676" t="n">
-        <v>729.6617501297184</v>
+        <v>729.6618113637422</v>
       </c>
       <c r="I676" t="n">
         <v>462.1499938964844</v>
@@ -52479,7 +52479,7 @@
         <v>0.1622849745548161</v>
       </c>
       <c r="K676" t="n">
-        <v>57.62837756547656</v>
+        <v>57.62839079382496</v>
       </c>
       <c r="L676" t="n">
         <v>7.649513212795549</v>
